--- a/public/kotoba_mokuzai.xlsx
+++ b/public/kotoba_mokuzai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\mokuzai_flashcard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E6D1DE-0754-4316-A2BC-314F5387D0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B2E126-30C3-4CBC-A66C-AFD5601B08B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="1253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="1669">
   <si>
     <t>第１章</t>
   </si>
@@ -3779,6 +3779,1254 @@
   </si>
   <si>
     <t>arti</t>
+  </si>
+  <si>
+    <t>強さ</t>
+  </si>
+  <si>
+    <t>つよさ</t>
+  </si>
+  <si>
+    <t>kekuatan</t>
+  </si>
+  <si>
+    <t>力</t>
+  </si>
+  <si>
+    <t>ちから</t>
+  </si>
+  <si>
+    <t>gaya, tenaga</t>
+  </si>
+  <si>
+    <t>加える</t>
+  </si>
+  <si>
+    <t>くわえる</t>
+  </si>
+  <si>
+    <t>memberikan, menerapkan</t>
+  </si>
+  <si>
+    <t>方法</t>
+  </si>
+  <si>
+    <t>ほうほう</t>
+  </si>
+  <si>
+    <t>metode, cara</t>
+  </si>
+  <si>
+    <t>方向</t>
+  </si>
+  <si>
+    <t>ほうこう</t>
+  </si>
+  <si>
+    <t>arah</t>
+  </si>
+  <si>
+    <t>圧縮強さ</t>
+  </si>
+  <si>
+    <t>あっしゅくつよさ</t>
+  </si>
+  <si>
+    <t>kekuatan tekan</t>
+  </si>
+  <si>
+    <t>引張強さ</t>
+  </si>
+  <si>
+    <t>ひっぱりつよさ</t>
+  </si>
+  <si>
+    <t>kekuatan tarik</t>
+  </si>
+  <si>
+    <t>曲げ強さ</t>
+  </si>
+  <si>
+    <t>まげつよさ</t>
+  </si>
+  <si>
+    <t>kekuatan lentur</t>
+  </si>
+  <si>
+    <t>せん断強さ</t>
+  </si>
+  <si>
+    <t>せんだんつよさ</t>
+  </si>
+  <si>
+    <t>kekuatan geser</t>
+  </si>
+  <si>
+    <t>割裂強さ</t>
+  </si>
+  <si>
+    <t>かつれつつよさ</t>
+  </si>
+  <si>
+    <t>kekuatan belah</t>
+  </si>
+  <si>
+    <t>表す</t>
+  </si>
+  <si>
+    <t>あらわす</t>
+  </si>
+  <si>
+    <t>menyatakan, menunjukkan</t>
+  </si>
+  <si>
+    <t>berikut</t>
+  </si>
+  <si>
+    <t>関係する</t>
+  </si>
+  <si>
+    <t>かんけいする</t>
+  </si>
+  <si>
+    <t>berhubungan dengan</t>
+  </si>
+  <si>
+    <t>密度</t>
+  </si>
+  <si>
+    <t>みつど</t>
+  </si>
+  <si>
+    <t>densitas, massa jenis</t>
+  </si>
+  <si>
+    <t>一般に</t>
+  </si>
+  <si>
+    <t>いっぱんに</t>
+  </si>
+  <si>
+    <t>pada umumnya</t>
+  </si>
+  <si>
+    <t>densitas</t>
+  </si>
+  <si>
+    <t>大きい</t>
+  </si>
+  <si>
+    <t>おおきい</t>
+  </si>
+  <si>
+    <t>besar</t>
+  </si>
+  <si>
+    <t>大きくなる</t>
+  </si>
+  <si>
+    <t>おおきくなる</t>
+  </si>
+  <si>
+    <t>menjadi lebih besar</t>
+  </si>
+  <si>
+    <t>数％</t>
+  </si>
+  <si>
+    <t>すうパーセント</t>
+  </si>
+  <si>
+    <t>beberapa persen</t>
+  </si>
+  <si>
+    <t>前後</t>
+  </si>
+  <si>
+    <t>ぜんご</t>
+  </si>
+  <si>
+    <t>menjadi paling besar</t>
+  </si>
+  <si>
+    <t>繊維飽和点</t>
+  </si>
+  <si>
+    <t>せんいほうわてん</t>
+  </si>
+  <si>
+    <t>titik jenuh serat</t>
+  </si>
+  <si>
+    <t>以上</t>
+  </si>
+  <si>
+    <t>いじょう</t>
+  </si>
+  <si>
+    <t>lebih dari</t>
+  </si>
+  <si>
+    <t>一定</t>
+  </si>
+  <si>
+    <t>いってい</t>
+  </si>
+  <si>
+    <t>tetap, konstan</t>
+  </si>
+  <si>
+    <t>arah serat</t>
+  </si>
+  <si>
+    <t>圧縮</t>
+  </si>
+  <si>
+    <t>あっしゅく</t>
+  </si>
+  <si>
+    <t>kompresi, tekan</t>
+  </si>
+  <si>
+    <t>強い</t>
+  </si>
+  <si>
+    <t>つよい</t>
+  </si>
+  <si>
+    <t>kuat</t>
+  </si>
+  <si>
+    <t>横方向</t>
+  </si>
+  <si>
+    <t>よこほうこう</t>
+  </si>
+  <si>
+    <t>arah melintang</t>
+  </si>
+  <si>
+    <t>半径方向</t>
+  </si>
+  <si>
+    <t>はんけいほうこう</t>
+  </si>
+  <si>
+    <t>arah radial</t>
+  </si>
+  <si>
+    <t>外</t>
+  </si>
+  <si>
+    <t>そと</t>
+  </si>
+  <si>
+    <t>luar</t>
+  </si>
+  <si>
+    <t>向かう</t>
+  </si>
+  <si>
+    <t>むかう</t>
+  </si>
+  <si>
+    <t>menuju</t>
+  </si>
+  <si>
+    <t>lebih... (dalam perbandingan)</t>
+  </si>
+  <si>
+    <t>arah tangensial</t>
+  </si>
+  <si>
+    <t>lingkaran tahun</t>
+  </si>
+  <si>
+    <t>接する</t>
+  </si>
+  <si>
+    <t>せっする</t>
+  </si>
+  <si>
+    <t>bersentuhan, menyinggung</t>
+  </si>
+  <si>
+    <t>節</t>
+  </si>
+  <si>
+    <t>ふし</t>
+  </si>
+  <si>
+    <t>mata kayu, simpul kayu</t>
+  </si>
+  <si>
+    <t>mata kayu</t>
+  </si>
+  <si>
+    <t>周辺</t>
+  </si>
+  <si>
+    <t>しゅうへん</t>
+  </si>
+  <si>
+    <t>繊維</t>
+  </si>
+  <si>
+    <t>せんい</t>
+  </si>
+  <si>
+    <t>serat</t>
+  </si>
+  <si>
+    <t>乱れ</t>
+  </si>
+  <si>
+    <t>みだれ</t>
+  </si>
+  <si>
+    <t>ketidakteraturan</t>
+  </si>
+  <si>
+    <t>小さくなる</t>
+  </si>
+  <si>
+    <t>ちいさくなる</t>
+  </si>
+  <si>
+    <t>menjadi lebih kecil</t>
+  </si>
+  <si>
+    <t>圧縮強度</t>
+  </si>
+  <si>
+    <t>あっしゅくきょうど</t>
+  </si>
+  <si>
+    <t>kuat tekan</t>
+  </si>
+  <si>
+    <t>引張強度</t>
+  </si>
+  <si>
+    <t>ひっぱりきょうど</t>
+  </si>
+  <si>
+    <t>kuat tarik</t>
+  </si>
+  <si>
+    <t>影響</t>
+  </si>
+  <si>
+    <t>えいきょう</t>
+  </si>
+  <si>
+    <t>pengaruh</t>
+  </si>
+  <si>
+    <t>及ぼす</t>
+  </si>
+  <si>
+    <t>およぼす</t>
+  </si>
+  <si>
+    <t>memberikan, menimbulkan</t>
+  </si>
+  <si>
+    <t>温度</t>
+  </si>
+  <si>
+    <t>おんど</t>
+  </si>
+  <si>
+    <t>suhu</t>
+  </si>
+  <si>
+    <t>樹幹内</t>
+  </si>
+  <si>
+    <t>じゅかんない</t>
+  </si>
+  <si>
+    <t>di dalam batang pohon</t>
+  </si>
+  <si>
+    <t>部位</t>
+  </si>
+  <si>
+    <t>ぶい</t>
+  </si>
+  <si>
+    <t>bagian, posisi</t>
+  </si>
+  <si>
+    <t>晩材率</t>
+  </si>
+  <si>
+    <t>ばんざいりつ</t>
+  </si>
+  <si>
+    <t>persentase kayu akhir (latewood)</t>
+  </si>
+  <si>
+    <t>平均年輪幅</t>
+  </si>
+  <si>
+    <t>へいきんねんりんはば</t>
+  </si>
+  <si>
+    <t>lebar rata-rata lingkaran tahun</t>
+  </si>
+  <si>
+    <t>寸法</t>
+  </si>
+  <si>
+    <t>すんぽう</t>
+  </si>
+  <si>
+    <t>dimensi, ukuran</t>
+  </si>
+  <si>
+    <t>あて材</t>
+  </si>
+  <si>
+    <t>あてざい</t>
+  </si>
+  <si>
+    <t>kayu reaksi (reaction wood)</t>
+  </si>
+  <si>
+    <t>腐れ</t>
+  </si>
+  <si>
+    <t>くされ</t>
+  </si>
+  <si>
+    <t>pembusukan</t>
+  </si>
+  <si>
+    <t>cacat, kelemahan</t>
+  </si>
+  <si>
+    <t>影響する</t>
+  </si>
+  <si>
+    <t>えいきょうする</t>
+  </si>
+  <si>
+    <t>mempengaruhi</t>
+  </si>
+  <si>
+    <t>作業安全</t>
+  </si>
+  <si>
+    <t>さぎょうあんぜん</t>
+  </si>
+  <si>
+    <t>keselamatan kerja</t>
+  </si>
+  <si>
+    <t>industri kayu</t>
+  </si>
+  <si>
+    <t>労働災害</t>
+  </si>
+  <si>
+    <t>ろうどうさいがい</t>
+  </si>
+  <si>
+    <t>kecelakaan kerja</t>
+  </si>
+  <si>
+    <t>発生状況</t>
+  </si>
+  <si>
+    <t>はっせいじょうきょう</t>
+  </si>
+  <si>
+    <t>kondisi/keadaan terjadinya</t>
+  </si>
+  <si>
+    <t>死傷者数</t>
+  </si>
+  <si>
+    <t>ししょうしゃすう</t>
+  </si>
+  <si>
+    <t>jumlah korban meninggal dan luka</t>
+  </si>
+  <si>
+    <t>年間</t>
+  </si>
+  <si>
+    <t>ねんかん</t>
+  </si>
+  <si>
+    <t>per tahun</t>
+  </si>
+  <si>
+    <t>件</t>
+  </si>
+  <si>
+    <t>けん</t>
+  </si>
+  <si>
+    <t>kasus, kejadian</t>
+  </si>
+  <si>
+    <t>死亡災害</t>
+  </si>
+  <si>
+    <t>しぼうさいがい</t>
+  </si>
+  <si>
+    <t>kecelakaan fatal</t>
+  </si>
+  <si>
+    <t>kasus</t>
+  </si>
+  <si>
+    <t>安全</t>
+  </si>
+  <si>
+    <t>あんぜん</t>
+  </si>
+  <si>
+    <t>keamanan, keselamatan</t>
+  </si>
+  <si>
+    <t>安全対策</t>
+  </si>
+  <si>
+    <t>あんぜんたいさく</t>
+  </si>
+  <si>
+    <t>tindakan keselamatan</t>
+  </si>
+  <si>
+    <t>推進</t>
+  </si>
+  <si>
+    <t>すいしん</t>
+  </si>
+  <si>
+    <t>pendorongan, pengembangan</t>
+  </si>
+  <si>
+    <t>件数</t>
+  </si>
+  <si>
+    <t>けんすう</t>
+  </si>
+  <si>
+    <t>jumlah kasus</t>
+  </si>
+  <si>
+    <t>減る</t>
+  </si>
+  <si>
+    <t>へる</t>
+  </si>
+  <si>
+    <t>berkurang</t>
+  </si>
+  <si>
+    <t>発生率</t>
+  </si>
+  <si>
+    <t>はっせいりつ</t>
+  </si>
+  <si>
+    <t>tingkat kejadian</t>
+  </si>
+  <si>
+    <t>他</t>
+  </si>
+  <si>
+    <t>ほか</t>
+  </si>
+  <si>
+    <t>lain</t>
+  </si>
+  <si>
+    <t>倍</t>
+  </si>
+  <si>
+    <t>ばい</t>
+  </si>
+  <si>
+    <t>kali lipat</t>
+  </si>
+  <si>
+    <t>高い</t>
+  </si>
+  <si>
+    <t>たかい</t>
+  </si>
+  <si>
+    <t>tinggi</t>
+  </si>
+  <si>
+    <t>改善</t>
+  </si>
+  <si>
+    <t>かいぜん</t>
+  </si>
+  <si>
+    <t>perbaikan</t>
+  </si>
+  <si>
+    <t>事故</t>
+  </si>
+  <si>
+    <t>じこ</t>
+  </si>
+  <si>
+    <t>kecelakaan</t>
+  </si>
+  <si>
+    <t>約半分</t>
+  </si>
+  <si>
+    <t>やくはんぶん</t>
+  </si>
+  <si>
+    <t>sekitar setengah</t>
+  </si>
+  <si>
+    <t>切れ</t>
+  </si>
+  <si>
+    <t>きれ</t>
+  </si>
+  <si>
+    <t>luka karena benda tajam/terpotong</t>
+  </si>
+  <si>
+    <t>こすれ</t>
+  </si>
+  <si>
+    <t>gesekan</t>
+  </si>
+  <si>
+    <t>挟まれ</t>
+  </si>
+  <si>
+    <t>はさまれ</t>
+  </si>
+  <si>
+    <t>terjepit</t>
+  </si>
+  <si>
+    <t>巻き込まれ</t>
+  </si>
+  <si>
+    <t>まきこまれ</t>
+  </si>
+  <si>
+    <t>tersangkut/terseret ke mesin</t>
+  </si>
+  <si>
+    <t>木材加工</t>
+  </si>
+  <si>
+    <t>もくざいかこう</t>
+  </si>
+  <si>
+    <t>pengolahan kayu</t>
+  </si>
+  <si>
+    <t>作業</t>
+  </si>
+  <si>
+    <t>さぎょう</t>
+  </si>
+  <si>
+    <t>pekerjaan, operasi kerja</t>
+  </si>
+  <si>
+    <t>発生する</t>
+  </si>
+  <si>
+    <t>はっせいする</t>
+  </si>
+  <si>
+    <t>terjadi</t>
+  </si>
+  <si>
+    <t>高速</t>
+  </si>
+  <si>
+    <t>こうそく</t>
+  </si>
+  <si>
+    <t>berkecepatan tinggi</t>
+  </si>
+  <si>
+    <t>回転する</t>
+  </si>
+  <si>
+    <t>かいてんする</t>
+  </si>
+  <si>
+    <t>berputar</t>
+  </si>
+  <si>
+    <t>工具</t>
+  </si>
+  <si>
+    <t>こうぐ</t>
+  </si>
+  <si>
+    <t>alat kerja, perkakas</t>
+  </si>
+  <si>
+    <t>触れる</t>
+  </si>
+  <si>
+    <t>ふれる</t>
+  </si>
+  <si>
+    <t>menyentuh</t>
+  </si>
+  <si>
+    <t>alat kerja</t>
+  </si>
+  <si>
+    <t>putaran</t>
+  </si>
+  <si>
+    <t>bahan kayu</t>
+  </si>
+  <si>
+    <t>送る</t>
+  </si>
+  <si>
+    <t>おくる</t>
+  </si>
+  <si>
+    <t>mengirim, mendorong</t>
+  </si>
+  <si>
+    <t>装置</t>
+  </si>
+  <si>
+    <t>そうち</t>
+  </si>
+  <si>
+    <t>perangkat, alat</t>
+  </si>
+  <si>
+    <t>起きる</t>
+  </si>
+  <si>
+    <t>おきる</t>
+  </si>
+  <si>
+    <t>pekerjaan</t>
+  </si>
+  <si>
+    <t>十分</t>
+  </si>
+  <si>
+    <t>じゅうぶん</t>
+  </si>
+  <si>
+    <t>cukup, memadai</t>
+  </si>
+  <si>
+    <t>注意</t>
+  </si>
+  <si>
+    <t>ちゅうい</t>
+  </si>
+  <si>
+    <t>perhatian, kewaspadaan</t>
+  </si>
+  <si>
+    <t>diperlukan</t>
+  </si>
+  <si>
+    <t>lainnya</t>
+  </si>
+  <si>
+    <t>terseret/tertarik ke mesin</t>
+  </si>
+  <si>
+    <t>飛来</t>
+  </si>
+  <si>
+    <t>ひらい</t>
+  </si>
+  <si>
+    <t>benda yang terbang/meluncur</t>
+  </si>
+  <si>
+    <t>落下</t>
+  </si>
+  <si>
+    <t>らっか</t>
+  </si>
+  <si>
+    <t>jatuh</t>
+  </si>
+  <si>
+    <t>転倒</t>
+  </si>
+  <si>
+    <t>てんとう</t>
+  </si>
+  <si>
+    <t>terjatuh</t>
+  </si>
+  <si>
+    <t>墜落</t>
+  </si>
+  <si>
+    <t>ついらく</t>
+  </si>
+  <si>
+    <t>jatuh dari ketinggian</t>
+  </si>
+  <si>
+    <t>転落</t>
+  </si>
+  <si>
+    <t>てんらく</t>
+  </si>
+  <si>
+    <t>terperosok/jatuh</t>
+  </si>
+  <si>
+    <t>terpotong</t>
+  </si>
+  <si>
+    <t>tergesek</t>
+  </si>
+  <si>
+    <t>型別</t>
+  </si>
+  <si>
+    <t>かたべつ</t>
+  </si>
+  <si>
+    <t>berdasarkan jenis</t>
+  </si>
+  <si>
+    <t>keselamatan, aman</t>
+  </si>
+  <si>
+    <t>配慮</t>
+  </si>
+  <si>
+    <t>はいりょ</t>
+  </si>
+  <si>
+    <t>perhatian, pertimbangan</t>
+  </si>
+  <si>
+    <t>服装</t>
+  </si>
+  <si>
+    <t>ふくそう</t>
+  </si>
+  <si>
+    <t>pakaian</t>
+  </si>
+  <si>
+    <t>keselamatan</t>
+  </si>
+  <si>
+    <t>pekerjaan, aktivitas kerja</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>ないよう</t>
+  </si>
+  <si>
+    <t>isi, jenis pekerjaan</t>
+  </si>
+  <si>
+    <t>合わせる</t>
+  </si>
+  <si>
+    <t>あわせる</t>
+  </si>
+  <si>
+    <t>menyesuaikan</t>
+  </si>
+  <si>
+    <t>選ぶ</t>
+  </si>
+  <si>
+    <t>えらぶ</t>
+  </si>
+  <si>
+    <t>memilih</t>
+  </si>
+  <si>
+    <t>perlu</t>
+  </si>
+  <si>
+    <t>袖締まり</t>
+  </si>
+  <si>
+    <t>そでじまり</t>
+  </si>
+  <si>
+    <t>bagian ujung lengan baju yang pas/tidak longgar</t>
+  </si>
+  <si>
+    <t>裾締まり</t>
+  </si>
+  <si>
+    <t>すそじまり</t>
+  </si>
+  <si>
+    <t>bagian bawah pakaian yang pas/tidak longgar</t>
+  </si>
+  <si>
+    <t>作業服</t>
+  </si>
+  <si>
+    <t>さぎょうふく</t>
+  </si>
+  <si>
+    <t>pakaian kerja</t>
+  </si>
+  <si>
+    <t>着用</t>
+  </si>
+  <si>
+    <t>ちゃくよう</t>
+  </si>
+  <si>
+    <t>memakai</t>
+  </si>
+  <si>
+    <t>特に</t>
+  </si>
+  <si>
+    <t>とくに</t>
+  </si>
+  <si>
+    <t>歯</t>
+  </si>
+  <si>
+    <t>は</t>
+  </si>
+  <si>
+    <t>mata gergaji</t>
+  </si>
+  <si>
+    <t>巻き込まれる</t>
+  </si>
+  <si>
+    <t>まきこまれる</t>
+  </si>
+  <si>
+    <t>terseret/tertarik ke dalam mesin</t>
+  </si>
+  <si>
+    <t>衣類</t>
+  </si>
+  <si>
+    <t>いるい</t>
+  </si>
+  <si>
+    <t>紐</t>
+  </si>
+  <si>
+    <t>ひも</t>
+  </si>
+  <si>
+    <t>tali</t>
+  </si>
+  <si>
+    <t>perhatian, waspada</t>
+  </si>
+  <si>
+    <t>手袋</t>
+  </si>
+  <si>
+    <t>てぶくろ</t>
+  </si>
+  <si>
+    <t>sarung tangan</t>
+  </si>
+  <si>
+    <t>前掛け</t>
+  </si>
+  <si>
+    <t>まえかけ</t>
+  </si>
+  <si>
+    <t>celemek/apron</t>
+  </si>
+  <si>
+    <t>手ぬぐい</t>
+  </si>
+  <si>
+    <t>てぬぐい</t>
+  </si>
+  <si>
+    <t>handuk kain tradisional Jepang</t>
+  </si>
+  <si>
+    <t>作業帽</t>
+  </si>
+  <si>
+    <t>さぎょうぼう</t>
+  </si>
+  <si>
+    <t>topi kerja</t>
+  </si>
+  <si>
+    <t>保護</t>
+  </si>
+  <si>
+    <t>ほご</t>
+  </si>
+  <si>
+    <t>perlindungan</t>
+  </si>
+  <si>
+    <t>保護メガネ</t>
+  </si>
+  <si>
+    <t>ほごメガネ</t>
+  </si>
+  <si>
+    <t>kacamata pelindung</t>
+  </si>
+  <si>
+    <t>マスク</t>
+  </si>
+  <si>
+    <t>masker</t>
+  </si>
+  <si>
+    <t>安全靴</t>
+  </si>
+  <si>
+    <t>あんぜんぐつ</t>
+  </si>
+  <si>
+    <t>sepatu keselamatan</t>
+  </si>
+  <si>
+    <t>耳栓</t>
+  </si>
+  <si>
+    <t>みみせん</t>
+  </si>
+  <si>
+    <t>penyumbat telinga</t>
+  </si>
+  <si>
+    <t>保護具</t>
+  </si>
+  <si>
+    <t>ほごぐ</t>
+  </si>
+  <si>
+    <t>alat pelindung diri (APD)</t>
+  </si>
+  <si>
+    <t>正しく</t>
+  </si>
+  <si>
+    <t>ただしく</t>
+  </si>
+  <si>
+    <t>dengan benar</t>
+  </si>
+  <si>
+    <t>着用する</t>
+  </si>
+  <si>
+    <t>ちゃくようする</t>
+  </si>
+  <si>
+    <t>リスクアセスメント</t>
+  </si>
+  <si>
+    <t>penilaian risiko (risk assessment)</t>
+  </si>
+  <si>
+    <t>作業場</t>
+  </si>
+  <si>
+    <t>さぎょうじょう</t>
+  </si>
+  <si>
+    <t>tempat kerja</t>
+  </si>
+  <si>
+    <t>危ない</t>
+  </si>
+  <si>
+    <t>あぶない</t>
+  </si>
+  <si>
+    <t>berbahaya</t>
+  </si>
+  <si>
+    <t>見つけ出す</t>
+  </si>
+  <si>
+    <t>みつけだす</t>
+  </si>
+  <si>
+    <t>menemukan</t>
+  </si>
+  <si>
+    <t>被害</t>
+  </si>
+  <si>
+    <t>ひがい</t>
+  </si>
+  <si>
+    <t>kerugian, dampak</t>
+  </si>
+  <si>
+    <t>大きさ</t>
+  </si>
+  <si>
+    <t>おおきさ</t>
+  </si>
+  <si>
+    <t>besarnya</t>
+  </si>
+  <si>
+    <t>災害</t>
+  </si>
+  <si>
+    <t>さいがい</t>
+  </si>
+  <si>
+    <t>kecelakaan, bencana</t>
+  </si>
+  <si>
+    <t>可能性</t>
+  </si>
+  <si>
+    <t>かのうせい</t>
+  </si>
+  <si>
+    <t>kemungkinan</t>
+  </si>
+  <si>
+    <t>高さ</t>
+  </si>
+  <si>
+    <t>たかさ</t>
+  </si>
+  <si>
+    <t>tingkat ketinggian</t>
+  </si>
+  <si>
+    <t>優先度</t>
+  </si>
+  <si>
+    <t>ゆうせんど</t>
+  </si>
+  <si>
+    <t>tingkat prioritas</t>
+  </si>
+  <si>
+    <t>判定する</t>
+  </si>
+  <si>
+    <t>はんていする</t>
+  </si>
+  <si>
+    <t>menilai, menentukan</t>
+  </si>
+  <si>
+    <t>prioritas</t>
+  </si>
+  <si>
+    <t>減らす</t>
+  </si>
+  <si>
+    <t>へらす</t>
+  </si>
+  <si>
+    <t>mengurangi</t>
+  </si>
+  <si>
+    <t>検討する</t>
+  </si>
+  <si>
+    <t>けんとうする</t>
+  </si>
+  <si>
+    <t>mempertimbangkan, mengkaji</t>
+  </si>
+  <si>
+    <t>明確化</t>
+  </si>
+  <si>
+    <t>めいかくか</t>
+  </si>
+  <si>
+    <t>memperjelas, klarifikasi</t>
+  </si>
+  <si>
+    <t>働く</t>
+  </si>
+  <si>
+    <t>はたらく</t>
+  </si>
+  <si>
+    <t>bekerja</t>
+  </si>
+  <si>
+    <t>人たち</t>
+  </si>
+  <si>
+    <t>ひとたち</t>
+  </si>
+  <si>
+    <t>orang-orang</t>
+  </si>
+  <si>
+    <t>認識</t>
+  </si>
+  <si>
+    <t>にんしき</t>
+  </si>
+  <si>
+    <t>kesadaran, pemahaman</t>
+  </si>
+  <si>
+    <t>共有</t>
+  </si>
+  <si>
+    <t>きょうゆう</t>
+  </si>
+  <si>
+    <t>berbagi, saling memahami</t>
+  </si>
+  <si>
+    <t>効果</t>
+  </si>
+  <si>
+    <t>こうか</t>
+  </si>
+  <si>
+    <t>efek, manfaat</t>
+  </si>
+  <si>
+    <t>期待する</t>
+  </si>
+  <si>
+    <t>きたいする</t>
+  </si>
+  <si>
+    <t>mengharapkan</t>
   </si>
 </sst>
 </file>
@@ -3865,7 +5113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3882,6 +5130,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4100,7 +5351,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G559"/>
+  <dimension ref="A1:G777"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
@@ -4122,7 +5373,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="13">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4136,7 +5387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="13">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4150,7 +5401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="13">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -4164,7 +5415,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" ht="13">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -4178,7 +5429,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" ht="13">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -4192,7 +5443,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" ht="13">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -4206,7 +5457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" ht="13">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -4220,7 +5471,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" ht="13">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -4234,7 +5485,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" ht="13">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -4248,7 +5499,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" ht="13">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -4262,7 +5513,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="13">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -4276,7 +5527,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" ht="13">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -4290,7 +5541,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" ht="13">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -4304,7 +5555,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" ht="13">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -4318,7 +5569,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" ht="13">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -4332,7 +5583,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" ht="13">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -12005,6 +13256,3058 @@
       </c>
       <c r="D559" s="1" t="s">
         <v>1248</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A560" s="1">
+        <v>10</v>
+      </c>
+      <c r="B560" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C560" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D560" s="12" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A561" s="1">
+        <v>10</v>
+      </c>
+      <c r="B561" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C561" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D561" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A562" s="1">
+        <v>10</v>
+      </c>
+      <c r="B562" s="12" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C562" s="12" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D562" s="12" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A563" s="1">
+        <v>10</v>
+      </c>
+      <c r="B563" s="12" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C563" s="12" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D563" s="12" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A564" s="1">
+        <v>10</v>
+      </c>
+      <c r="B564" s="12" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C564" s="12" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D564" s="12" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A565" s="1">
+        <v>10</v>
+      </c>
+      <c r="B565" s="12" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C565" s="12" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D565" s="12" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A566" s="1">
+        <v>10</v>
+      </c>
+      <c r="B566" s="12" t="s">
+        <v>934</v>
+      </c>
+      <c r="C566" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="D566" s="12" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A567" s="1">
+        <v>10</v>
+      </c>
+      <c r="B567" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C567" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D567" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A568" s="1">
+        <v>10</v>
+      </c>
+      <c r="B568" s="12" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C568" s="12" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D568" s="12" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A569" s="1">
+        <v>10</v>
+      </c>
+      <c r="B569" s="12" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C569" s="12" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D569" s="12" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A570" s="1">
+        <v>10</v>
+      </c>
+      <c r="B570" s="12" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C570" s="12" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D570" s="12" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A571" s="1">
+        <v>10</v>
+      </c>
+      <c r="B571" s="12" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C571" s="12" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D571" s="12" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A572" s="1">
+        <v>10</v>
+      </c>
+      <c r="B572" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C572" s="12" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D572" s="12" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A573" s="1">
+        <v>10</v>
+      </c>
+      <c r="B573" s="12" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C573" s="12" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D573" s="12" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A574" s="1">
+        <v>10</v>
+      </c>
+      <c r="B574" s="12" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C574" s="12" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D574" s="12" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A575" s="1">
+        <v>10</v>
+      </c>
+      <c r="B575" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C575" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D575" s="12" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A576" s="1">
+        <v>10</v>
+      </c>
+      <c r="B576" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C576" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D576" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A577" s="1">
+        <v>10</v>
+      </c>
+      <c r="B577" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C577" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D577" s="12" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A578" s="1">
+        <v>10</v>
+      </c>
+      <c r="B578" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C578" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D578" s="12" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A579" s="1">
+        <v>10</v>
+      </c>
+      <c r="B579" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C579" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D579" s="12" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A580" s="1">
+        <v>10</v>
+      </c>
+      <c r="B580" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C580" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D580" s="12" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A581" s="1">
+        <v>10</v>
+      </c>
+      <c r="B581" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C581" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D581" s="12" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A582" s="1">
+        <v>10</v>
+      </c>
+      <c r="B582" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C582" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D582" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A583" s="1">
+        <v>10</v>
+      </c>
+      <c r="B583" s="12" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C583" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D583" s="12" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A584" s="1">
+        <v>10</v>
+      </c>
+      <c r="B584" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C584" s="12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D584" s="12" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A585" s="1">
+        <v>10</v>
+      </c>
+      <c r="B585" s="12" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C585" s="12" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D585" s="12" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A586" s="1">
+        <v>10</v>
+      </c>
+      <c r="B586" s="12" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C586" s="12" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D586" s="12" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A587" s="1">
+        <v>10</v>
+      </c>
+      <c r="B587" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="C587" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="D587" s="12" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A588" s="1">
+        <v>10</v>
+      </c>
+      <c r="B588" s="12" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C588" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D588" s="12" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A589" s="1">
+        <v>10</v>
+      </c>
+      <c r="B589" s="12" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C589" s="12" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D589" s="12" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A590" s="1">
+        <v>10</v>
+      </c>
+      <c r="B590" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C590" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D590" s="12" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A591" s="1">
+        <v>10</v>
+      </c>
+      <c r="B591" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C591" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D591" s="12" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A592" s="1">
+        <v>10</v>
+      </c>
+      <c r="B592" s="12" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C592" s="12" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D592" s="12" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A593" s="1">
+        <v>10</v>
+      </c>
+      <c r="B593" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="C593" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D593" s="12" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A594" s="1">
+        <v>10</v>
+      </c>
+      <c r="B594" s="12" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C594" s="12" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D594" s="12" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A595" s="1">
+        <v>10</v>
+      </c>
+      <c r="B595" s="12" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C595" s="12" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D595" s="12" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A596" s="1">
+        <v>10</v>
+      </c>
+      <c r="B596" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="C596" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D596" s="12" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A597" s="1">
+        <v>10</v>
+      </c>
+      <c r="B597" s="12" t="s">
+        <v>765</v>
+      </c>
+      <c r="C597" s="12" t="s">
+        <v>766</v>
+      </c>
+      <c r="D597" s="12" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A598" s="1">
+        <v>10</v>
+      </c>
+      <c r="B598" s="12" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C598" s="12" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D598" s="12" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A599" s="1">
+        <v>10</v>
+      </c>
+      <c r="B599" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="C599" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="D599" s="12" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A600" s="1">
+        <v>10</v>
+      </c>
+      <c r="B600" s="12" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C600" s="12" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D600" s="12" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A601" s="1">
+        <v>10</v>
+      </c>
+      <c r="B601" s="12" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C601" s="12" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D601" s="12" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A602" s="1">
+        <v>10</v>
+      </c>
+      <c r="B602" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C602" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D602" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A603" s="1">
+        <v>10</v>
+      </c>
+      <c r="B603" s="12" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C603" s="12" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D603" s="12" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A604" s="1">
+        <v>10</v>
+      </c>
+      <c r="B604" s="12" t="s">
+        <v>783</v>
+      </c>
+      <c r="C604" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="D604" s="12" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A605" s="1">
+        <v>10</v>
+      </c>
+      <c r="B605" s="12" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C605" s="12" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D605" s="12" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A606" s="1">
+        <v>10</v>
+      </c>
+      <c r="B606" s="12" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C606" s="12" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D606" s="12" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A607" s="1">
+        <v>10</v>
+      </c>
+      <c r="B607" s="12" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C607" s="12" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D607" s="12" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A608" s="1">
+        <v>10</v>
+      </c>
+      <c r="B608" s="12" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C608" s="12" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D608" s="12" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A609" s="1">
+        <v>10</v>
+      </c>
+      <c r="B609" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="C609" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="D609" s="12" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A610" s="1">
+        <v>10</v>
+      </c>
+      <c r="B610" s="12" t="s">
+        <v>810</v>
+      </c>
+      <c r="C610" s="12" t="s">
+        <v>811</v>
+      </c>
+      <c r="D610" s="12" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A611" s="1">
+        <v>10</v>
+      </c>
+      <c r="B611" s="12" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C611" s="12" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D611" s="12" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A612" s="1">
+        <v>10</v>
+      </c>
+      <c r="B612" s="12" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C612" s="12" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D612" s="12" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A613" s="1">
+        <v>10</v>
+      </c>
+      <c r="B613" s="12" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C613" s="12" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D613" s="12" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A614" s="1">
+        <v>10</v>
+      </c>
+      <c r="B614" s="12" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C614" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D614" s="12" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A615" s="1">
+        <v>10</v>
+      </c>
+      <c r="B615" s="12" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C615" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D615" s="12" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A616" s="1">
+        <v>10</v>
+      </c>
+      <c r="B616" s="12" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C616" s="12" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D616" s="12" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A617" s="1">
+        <v>10</v>
+      </c>
+      <c r="B617" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C617" s="12" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D617" s="12" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A618" s="1">
+        <v>10</v>
+      </c>
+      <c r="B618" s="12" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C618" s="12" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D618" s="12" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A619" s="1">
+        <v>10</v>
+      </c>
+      <c r="B619" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C619" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D619" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A620" s="1">
+        <v>10</v>
+      </c>
+      <c r="B620" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C620" s="12" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D620" s="12" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A621" s="1">
+        <v>10</v>
+      </c>
+      <c r="B621" s="12" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C621" s="12" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D621" s="12" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A622" s="1">
+        <v>10</v>
+      </c>
+      <c r="B622" s="12" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C622" s="12" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D622" s="12" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A623" s="1">
+        <v>10</v>
+      </c>
+      <c r="B623" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C623" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D623" s="12" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A624" s="1">
+        <v>10</v>
+      </c>
+      <c r="B624" s="12" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C624" s="12" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D624" s="12" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A625" s="1">
+        <v>10</v>
+      </c>
+      <c r="B625" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C625" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D625" s="12" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A626" s="1">
+        <v>10</v>
+      </c>
+      <c r="B626" s="12" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C626" s="12" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D626" s="12" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A627" s="1">
+        <v>10</v>
+      </c>
+      <c r="B627" s="12" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C627" s="12" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D627" s="12" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A628" s="1">
+        <v>10</v>
+      </c>
+      <c r="B628" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C628" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D628" s="12" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A629" s="1">
+        <v>10</v>
+      </c>
+      <c r="B629" s="12" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C629" s="12" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D629" s="12" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A630" s="1">
+        <v>10</v>
+      </c>
+      <c r="B630" s="12" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C630" s="12" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D630" s="12" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A631" s="1">
+        <v>10</v>
+      </c>
+      <c r="B631" s="12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C631" s="12" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D631" s="12" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A632" s="1">
+        <v>10</v>
+      </c>
+      <c r="B632" s="12" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C632" s="12" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D632" s="12" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A633" s="1">
+        <v>10</v>
+      </c>
+      <c r="B633" s="12" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C633" s="12" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D633" s="12" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A634" s="1">
+        <v>10</v>
+      </c>
+      <c r="B634" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C634" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D634" s="12" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A635" s="1">
+        <v>10</v>
+      </c>
+      <c r="B635" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C635" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D635" s="12" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A636" s="1">
+        <v>10</v>
+      </c>
+      <c r="B636" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C636" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D636" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A637" s="1">
+        <v>10</v>
+      </c>
+      <c r="B637" s="12" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C637" s="12" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D637" s="12" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A638" s="1">
+        <v>11</v>
+      </c>
+      <c r="B638" s="12" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C638" s="12" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D638" s="12" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A639" s="1">
+        <v>11</v>
+      </c>
+      <c r="B639" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C639" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D639" s="12" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A640" s="1">
+        <v>11</v>
+      </c>
+      <c r="B640" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C640" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D640" s="12" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A641" s="1">
+        <v>11</v>
+      </c>
+      <c r="B641" s="12" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C641" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D641" s="12" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A642" s="1">
+        <v>11</v>
+      </c>
+      <c r="B642" s="12" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C642" s="12" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D642" s="12" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A643" s="1">
+        <v>11</v>
+      </c>
+      <c r="B643" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C643" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D643" s="12" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A644" s="1">
+        <v>11</v>
+      </c>
+      <c r="B644" s="12" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C644" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D644" s="12" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A645" s="1">
+        <v>11</v>
+      </c>
+      <c r="B645" s="12" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C645" s="12" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D645" s="12" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A646" s="1">
+        <v>11</v>
+      </c>
+      <c r="B646" s="12" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C646" s="12" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D646" s="12" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A647" s="1">
+        <v>11</v>
+      </c>
+      <c r="B647" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C647" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D647" s="12" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A648" s="1">
+        <v>11</v>
+      </c>
+      <c r="B648" s="12" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C648" s="12" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D648" s="12" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A649" s="1">
+        <v>11</v>
+      </c>
+      <c r="B649" s="12" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C649" s="12" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D649" s="12" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A650" s="1">
+        <v>11</v>
+      </c>
+      <c r="B650" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C650" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D650" s="12" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A651" s="1">
+        <v>11</v>
+      </c>
+      <c r="B651" s="12" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C651" s="12" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D651" s="12" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A652" s="1">
+        <v>11</v>
+      </c>
+      <c r="B652" s="12" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C652" s="12" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D652" s="12" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A653" s="1">
+        <v>11</v>
+      </c>
+      <c r="B653" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C653" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D653" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A654" s="1">
+        <v>11</v>
+      </c>
+      <c r="B654" s="12" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C654" s="12" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D654" s="12" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A655" s="1">
+        <v>11</v>
+      </c>
+      <c r="B655" s="12" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C655" s="12" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D655" s="12" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A656" s="1">
+        <v>11</v>
+      </c>
+      <c r="B656" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="C656" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="D656" s="12" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A657" s="1">
+        <v>11</v>
+      </c>
+      <c r="B657" s="12" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C657" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D657" s="12" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A658" s="1">
+        <v>11</v>
+      </c>
+      <c r="B658" s="12" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C658" s="12" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D658" s="12" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A659" s="1">
+        <v>11</v>
+      </c>
+      <c r="B659" s="12" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C659" s="12" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D659" s="12" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A660" s="1">
+        <v>11</v>
+      </c>
+      <c r="B660" s="12" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C660" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D660" s="12" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A661" s="1">
+        <v>11</v>
+      </c>
+      <c r="B661" s="12" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C661" s="12" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D661" s="12" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A662" s="1">
+        <v>11</v>
+      </c>
+      <c r="B662" s="12" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C662" s="12" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D662" s="12" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A663" s="1">
+        <v>11</v>
+      </c>
+      <c r="B663" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="C663" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="D663" s="12" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A664" s="1">
+        <v>11</v>
+      </c>
+      <c r="B664" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C664" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D664" s="12" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A665" s="1">
+        <v>11</v>
+      </c>
+      <c r="B665" s="12" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C665" s="12" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D665" s="12" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A666" s="1">
+        <v>11</v>
+      </c>
+      <c r="B666" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C666" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D666" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A667" s="1">
+        <v>11</v>
+      </c>
+      <c r="B667" s="12" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C667" s="12" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D667" s="12" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A668" s="1">
+        <v>11</v>
+      </c>
+      <c r="B668" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C668" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D668" s="12" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A669" s="1">
+        <v>11</v>
+      </c>
+      <c r="B669" s="12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C669" s="12" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D669" s="12" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A670" s="1">
+        <v>11</v>
+      </c>
+      <c r="B670" s="12" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C670" s="12" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D670" s="12" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A671" s="1">
+        <v>11</v>
+      </c>
+      <c r="B671" s="12" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C671" s="12" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D671" s="12" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A672" s="1">
+        <v>11</v>
+      </c>
+      <c r="B672" s="12" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C672" s="12" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D672" s="12" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A673" s="1">
+        <v>11</v>
+      </c>
+      <c r="B673" s="12" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C673" s="12" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D673" s="12" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A674" s="1">
+        <v>11</v>
+      </c>
+      <c r="B674" s="12" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C674" s="12" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D674" s="12" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A675" s="1">
+        <v>11</v>
+      </c>
+      <c r="B675" s="12" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C675" s="12" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D675" s="12" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A676" s="1">
+        <v>11</v>
+      </c>
+      <c r="B676" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C676" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D676" s="12" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A677" s="1">
+        <v>11</v>
+      </c>
+      <c r="B677" s="12" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C677" s="12" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D677" s="12" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A678" s="1">
+        <v>11</v>
+      </c>
+      <c r="B678" s="12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C678" s="12" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D678" s="12" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A679" s="1">
+        <v>11</v>
+      </c>
+      <c r="B679" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C679" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D679" s="12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A680" s="1">
+        <v>11</v>
+      </c>
+      <c r="B680" s="12" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C680" s="12" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D680" s="12" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A681" s="1">
+        <v>11</v>
+      </c>
+      <c r="B681" s="12" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C681" s="12" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D681" s="12" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A682" s="1">
+        <v>11</v>
+      </c>
+      <c r="B682" s="12" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C682" s="12" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D682" s="12" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A683" s="1">
+        <v>11</v>
+      </c>
+      <c r="B683" s="12" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C683" s="12" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D683" s="12" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A684" s="1">
+        <v>11</v>
+      </c>
+      <c r="B684" s="12" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C684" s="12" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D684" s="12" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A685" s="1">
+        <v>11</v>
+      </c>
+      <c r="B685" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="C685" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="D685" s="12" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A686" s="1">
+        <v>11</v>
+      </c>
+      <c r="B686" s="12" t="s">
+        <v>960</v>
+      </c>
+      <c r="C686" s="12" t="s">
+        <v>961</v>
+      </c>
+      <c r="D686" s="12" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A687" s="1">
+        <v>11</v>
+      </c>
+      <c r="B687" s="12" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C687" s="12" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D687" s="12" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A688" s="1">
+        <v>11</v>
+      </c>
+      <c r="B688" s="12" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C688" s="12" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D688" s="12" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A689" s="1">
+        <v>11</v>
+      </c>
+      <c r="B689" s="12" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C689" s="12" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D689" s="12" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A690" s="1">
+        <v>11</v>
+      </c>
+      <c r="B690" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C690" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D690" s="12" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A691" s="1">
+        <v>11</v>
+      </c>
+      <c r="B691" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C691" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="D691" s="12" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A692" s="1">
+        <v>11</v>
+      </c>
+      <c r="B692" s="12" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C692" s="12" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D692" s="12" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A693" s="1">
+        <v>11</v>
+      </c>
+      <c r="B693" s="12" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C693" s="12" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D693" s="12" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A694" s="1">
+        <v>11</v>
+      </c>
+      <c r="B694" s="12" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C694" s="12" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D694" s="12" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A695" s="1">
+        <v>11</v>
+      </c>
+      <c r="B695" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C695" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D695" s="12" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A696" s="1">
+        <v>11</v>
+      </c>
+      <c r="B696" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C696" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D696" s="12" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A697" s="1">
+        <v>11</v>
+      </c>
+      <c r="B697" s="12" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C697" s="12" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D697" s="12" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A698" s="1">
+        <v>11</v>
+      </c>
+      <c r="B698" s="12" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C698" s="12" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D698" s="12" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A699" s="1">
+        <v>11</v>
+      </c>
+      <c r="B699" s="12" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C699" s="12" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D699" s="12" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A700" s="1">
+        <v>11</v>
+      </c>
+      <c r="B700" s="12" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C700" s="12" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D700" s="12" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A701" s="1">
+        <v>11</v>
+      </c>
+      <c r="B701" s="12" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C701" s="12" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D701" s="12" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A702" s="1">
+        <v>11</v>
+      </c>
+      <c r="B702" s="12" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C702" s="12" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D702" s="12" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A703" s="1">
+        <v>11</v>
+      </c>
+      <c r="B703" s="12" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C703" s="12" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D703" s="12" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A704" s="1">
+        <v>11</v>
+      </c>
+      <c r="B704" s="12" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C704" s="12" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D704" s="12" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A705" s="1">
+        <v>11</v>
+      </c>
+      <c r="B705" s="12" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C705" s="12" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D705" s="12" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A706" s="1">
+        <v>11</v>
+      </c>
+      <c r="B706" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C706" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D706" s="12" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A707" s="1">
+        <v>11</v>
+      </c>
+      <c r="B707" s="12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C707" s="12" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D707" s="12" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A708" s="1">
+        <v>11</v>
+      </c>
+      <c r="B708" s="12" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C708" s="12" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D708" s="12" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A709" s="1">
+        <v>11</v>
+      </c>
+      <c r="B709" s="12" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C709" s="12" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D709" s="12" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A710" s="1">
+        <v>12</v>
+      </c>
+      <c r="B710" s="12" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C710" s="12" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D710" s="12" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A711" s="1">
+        <v>12</v>
+      </c>
+      <c r="B711" s="12" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C711" s="12" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D711" s="12" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A712" s="1">
+        <v>12</v>
+      </c>
+      <c r="B712" s="12" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C712" s="12" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D712" s="12" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A713" s="1">
+        <v>12</v>
+      </c>
+      <c r="B713" s="12" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C713" s="12" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D713" s="12" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A714" s="1">
+        <v>12</v>
+      </c>
+      <c r="B714" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C714" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D714" s="12" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A715" s="1">
+        <v>12</v>
+      </c>
+      <c r="B715" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C715" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="D715" s="12" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A716" s="1">
+        <v>12</v>
+      </c>
+      <c r="B716" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C716" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D716" s="12" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A717" s="1">
+        <v>12</v>
+      </c>
+      <c r="B717" s="12" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C717" s="12" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D717" s="12" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A718" s="1">
+        <v>12</v>
+      </c>
+      <c r="B718" s="12" t="s">
+        <v>813</v>
+      </c>
+      <c r="C718" s="12" t="s">
+        <v>814</v>
+      </c>
+      <c r="D718" s="12" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A719" s="1">
+        <v>12</v>
+      </c>
+      <c r="B719" s="12" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C719" s="12" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D719" s="12" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A720" s="1">
+        <v>12</v>
+      </c>
+      <c r="B720" s="12" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C720" s="12" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D720" s="12" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A721" s="1">
+        <v>12</v>
+      </c>
+      <c r="B721" s="12" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C721" s="12" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D721" s="12" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A722" s="1">
+        <v>12</v>
+      </c>
+      <c r="B722" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C722" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D722" s="12" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A723" s="1">
+        <v>12</v>
+      </c>
+      <c r="B723" s="12" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C723" s="12" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D723" s="12" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A724" s="1">
+        <v>12</v>
+      </c>
+      <c r="B724" s="12" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C724" s="12" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D724" s="12" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A725" s="1">
+        <v>12</v>
+      </c>
+      <c r="B725" s="12" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C725" s="12" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D725" s="12" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A726" s="1">
+        <v>12</v>
+      </c>
+      <c r="B726" s="12" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C726" s="12" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D726" s="12" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A727" s="1">
+        <v>12</v>
+      </c>
+      <c r="B727" s="12" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C727" s="12" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D727" s="12" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A728" s="1">
+        <v>12</v>
+      </c>
+      <c r="B728" s="12" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C728" s="12" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D728" s="12" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A729" s="1">
+        <v>12</v>
+      </c>
+      <c r="B729" s="12" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C729" s="12" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D729" s="12" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A730" s="1">
+        <v>12</v>
+      </c>
+      <c r="B730" s="12" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C730" s="12" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D730" s="12" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A731" s="1">
+        <v>12</v>
+      </c>
+      <c r="B731" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C731" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D731" s="12" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A732" s="1">
+        <v>12</v>
+      </c>
+      <c r="B732" s="12" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C732" s="12" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D732" s="12" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A733" s="1">
+        <v>12</v>
+      </c>
+      <c r="B733" s="12" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C733" s="12" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D733" s="12" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A734" s="1">
+        <v>12</v>
+      </c>
+      <c r="B734" s="12" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C734" s="12" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D734" s="12" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A735" s="1">
+        <v>12</v>
+      </c>
+      <c r="B735" s="12" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C735" s="12" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D735" s="12" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A736" s="1">
+        <v>12</v>
+      </c>
+      <c r="B736" s="12" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C736" s="12" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D736" s="12" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A737" s="1">
+        <v>12</v>
+      </c>
+      <c r="B737" s="12" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C737" s="12" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D737" s="12" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A738" s="1">
+        <v>12</v>
+      </c>
+      <c r="B738" s="12" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C738" s="12" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D738" s="12" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="739" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A739" s="1">
+        <v>12</v>
+      </c>
+      <c r="B739" s="12" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C739" s="12" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D739" s="12" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A740" s="1">
+        <v>12</v>
+      </c>
+      <c r="B740" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C740" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D740" s="12" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A741" s="1">
+        <v>12</v>
+      </c>
+      <c r="B741" s="12" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C741" s="12" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D741" s="12" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A742" s="1">
+        <v>12</v>
+      </c>
+      <c r="B742" s="12" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C742" s="12" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D742" s="12" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="743" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A743" s="1">
+        <v>12</v>
+      </c>
+      <c r="B743" s="12" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C743" s="12" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D743" s="12" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A744" s="1">
+        <v>12</v>
+      </c>
+      <c r="B744" s="12" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C744" s="12" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D744" s="12" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="745" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A745" s="1">
+        <v>12</v>
+      </c>
+      <c r="B745" s="12" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C745" s="12" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D745" s="12" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="746" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A746" s="1">
+        <v>12</v>
+      </c>
+      <c r="B746" s="12" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C746" s="12" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D746" s="12" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="747" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A747" s="1">
+        <v>12</v>
+      </c>
+      <c r="B747" s="12" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C747" s="12" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D747" s="12" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="748" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A748" s="1">
+        <v>12</v>
+      </c>
+      <c r="B748" s="12" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C748" s="12" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D748" s="12" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="749" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A749" s="1">
+        <v>12</v>
+      </c>
+      <c r="B749" s="12" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C749" s="12" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D749" s="12" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="750" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A750" s="1">
+        <v>12</v>
+      </c>
+      <c r="B750" s="12" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C750" s="12" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D750" s="12" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="751" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A751" s="1">
+        <v>12</v>
+      </c>
+      <c r="B751" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C751" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D751" s="12" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="752" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A752" s="1">
+        <v>12</v>
+      </c>
+      <c r="B752" s="12" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C752" s="12" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D752" s="12" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A753" s="1">
+        <v>12</v>
+      </c>
+      <c r="B753" s="12" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C753" s="12" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D753" s="12" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="754" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A754" s="1">
+        <v>12</v>
+      </c>
+      <c r="B754" s="12" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C754" s="12" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D754" s="12" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="755" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A755" s="1">
+        <v>12</v>
+      </c>
+      <c r="B755" s="12" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C755" s="12" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D755" s="12" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="756" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A756" s="1">
+        <v>12</v>
+      </c>
+      <c r="B756" s="12" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C756" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D756" s="12" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="757" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A757" s="1">
+        <v>12</v>
+      </c>
+      <c r="B757" s="12" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C757" s="12" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D757" s="12" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="758" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A758" s="1">
+        <v>12</v>
+      </c>
+      <c r="B758" s="12" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C758" s="12" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D758" s="12" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="759" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A759" s="1">
+        <v>12</v>
+      </c>
+      <c r="B759" s="12" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C759" s="12" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D759" s="12" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="760" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A760" s="1">
+        <v>12</v>
+      </c>
+      <c r="B760" s="12" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C760" s="12" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D760" s="12" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="761" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A761" s="1">
+        <v>12</v>
+      </c>
+      <c r="B761" s="12" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C761" s="12" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D761" s="12" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="762" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A762" s="1">
+        <v>12</v>
+      </c>
+      <c r="B762" s="12" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C762" s="12" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D762" s="12" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="763" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A763" s="1">
+        <v>12</v>
+      </c>
+      <c r="B763" s="12" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C763" s="12" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D763" s="12" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="764" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A764" s="1">
+        <v>12</v>
+      </c>
+      <c r="B764" s="12" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C764" s="12" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D764" s="12" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="765" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A765" s="1">
+        <v>12</v>
+      </c>
+      <c r="B765" s="12" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C765" s="12" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D765" s="12" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="766" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A766" s="1">
+        <v>12</v>
+      </c>
+      <c r="B766" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C766" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D766" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="767" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A767" s="1">
+        <v>12</v>
+      </c>
+      <c r="B767" s="12" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C767" s="12" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D767" s="12" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="768" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A768" s="1">
+        <v>12</v>
+      </c>
+      <c r="B768" s="12" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C768" s="12" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D768" s="12" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="769" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A769" s="1">
+        <v>12</v>
+      </c>
+      <c r="B769" s="12" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C769" s="12" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D769" s="12" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="770" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A770" s="1">
+        <v>12</v>
+      </c>
+      <c r="B770" s="12" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C770" s="12" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D770" s="12" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="771" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A771" s="1">
+        <v>12</v>
+      </c>
+      <c r="B771" s="12" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C771" s="12" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D771" s="12" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="772" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A772" s="1">
+        <v>12</v>
+      </c>
+      <c r="B772" s="12" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C772" s="12" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D772" s="12" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="773" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A773" s="1">
+        <v>12</v>
+      </c>
+      <c r="B773" s="12" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C773" s="12" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D773" s="12" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="774" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A774" s="1">
+        <v>12</v>
+      </c>
+      <c r="B774" s="12" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C774" s="12" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D774" s="12" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="775" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A775" s="1">
+        <v>12</v>
+      </c>
+      <c r="B775" s="12" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C775" s="12" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D775" s="12" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="776" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A776" s="1">
+        <v>12</v>
+      </c>
+      <c r="B776" s="12" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C776" s="12" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D776" s="12" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="777" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A777" s="1">
+        <v>12</v>
+      </c>
+      <c r="B777" s="12" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C777" s="12" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D777" s="12" t="s">
+        <v>1668</v>
       </c>
     </row>
   </sheetData>

--- a/public/kotoba_mokuzai.xlsx
+++ b/public/kotoba_mokuzai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\mokuzai_flashcard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B2E126-30C3-4CBC-A66C-AFD5601B08B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DEB2AA-4956-4E1A-8868-BD6790E5E2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3355" uniqueCount="2188">
   <si>
     <t>第１章</t>
   </si>
@@ -5027,6 +5027,1563 @@
   </si>
   <si>
     <t>mengharapkan</t>
+  </si>
+  <si>
+    <t>安全装置</t>
+  </si>
+  <si>
+    <t>あんぜんそうち</t>
+  </si>
+  <si>
+    <t>perangkat/pengaman keselamatan</t>
+  </si>
+  <si>
+    <t>原理</t>
+  </si>
+  <si>
+    <t>げんり</t>
+  </si>
+  <si>
+    <t>prinsip</t>
+  </si>
+  <si>
+    <t>perangkat keselamatan</t>
+  </si>
+  <si>
+    <t>設備</t>
+  </si>
+  <si>
+    <t>せつび</t>
+  </si>
+  <si>
+    <t>fasilitas, peralatan</t>
+  </si>
+  <si>
+    <t>考え方</t>
+  </si>
+  <si>
+    <t>かんがえかた</t>
+  </si>
+  <si>
+    <t>cara berpikir, konsep</t>
+  </si>
+  <si>
+    <t>基づく</t>
+  </si>
+  <si>
+    <t>もとづく</t>
+  </si>
+  <si>
+    <t>berdasarkan</t>
+  </si>
+  <si>
+    <t>設計</t>
+  </si>
+  <si>
+    <t>せっけい</t>
+  </si>
+  <si>
+    <t>perancangan, desain</t>
+  </si>
+  <si>
+    <t>人間</t>
+  </si>
+  <si>
+    <t>にんげん</t>
+  </si>
+  <si>
+    <t>manusia</t>
+  </si>
+  <si>
+    <t>過ち</t>
+  </si>
+  <si>
+    <t>あやまち</t>
+  </si>
+  <si>
+    <t>kesalahan</t>
+  </si>
+  <si>
+    <t>犯す</t>
+  </si>
+  <si>
+    <t>おかす</t>
+  </si>
+  <si>
+    <t>melakukan (kesalahan)</t>
+  </si>
+  <si>
+    <t>存在</t>
+  </si>
+  <si>
+    <t>そんざい</t>
+  </si>
+  <si>
+    <t>keberadaan</t>
+  </si>
+  <si>
+    <t>立つ</t>
+  </si>
+  <si>
+    <t>たつ</t>
+  </si>
+  <si>
+    <t>berdiri (dalam ungkapan ～に立って = berdasarkan)</t>
+  </si>
+  <si>
+    <t>perancangan</t>
+  </si>
+  <si>
+    <t>konsep</t>
+  </si>
+  <si>
+    <t>回転部</t>
+  </si>
+  <si>
+    <t>かいてんぶ</t>
+  </si>
+  <si>
+    <t>bagian yang berputar</t>
+  </si>
+  <si>
+    <t>tangan</t>
+  </si>
+  <si>
+    <t>隔離</t>
+  </si>
+  <si>
+    <t>かくり</t>
+  </si>
+  <si>
+    <t>mengisolasi, memisahkan</t>
+  </si>
+  <si>
+    <t>修理</t>
+  </si>
+  <si>
+    <t>しゅうり</t>
+  </si>
+  <si>
+    <t>動作部</t>
+  </si>
+  <si>
+    <t>どうさぶ</t>
+  </si>
+  <si>
+    <t>bagian yang bergerak/beroperasi</t>
+  </si>
+  <si>
+    <t>電気回路</t>
+  </si>
+  <si>
+    <t>でんきかいろ</t>
+  </si>
+  <si>
+    <t>rangkaian listrik</t>
+  </si>
+  <si>
+    <t>遮断</t>
+  </si>
+  <si>
+    <t>しゃだん</t>
+  </si>
+  <si>
+    <t>memutus, memutus aliran</t>
+  </si>
+  <si>
+    <t>例</t>
+  </si>
+  <si>
+    <t>れい</t>
+  </si>
+  <si>
+    <t>contoh</t>
+  </si>
+  <si>
+    <t>該当する</t>
+  </si>
+  <si>
+    <t>がいとうする</t>
+  </si>
+  <si>
+    <t>termasuk, sesuai</t>
+  </si>
+  <si>
+    <t>何</t>
+  </si>
+  <si>
+    <t>なに</t>
+  </si>
+  <si>
+    <t>sesuatu</t>
+  </si>
+  <si>
+    <t>異常</t>
+  </si>
+  <si>
+    <t>kelainan, abnormalitas</t>
+  </si>
+  <si>
+    <t>失敗</t>
+  </si>
+  <si>
+    <t>しっぱい</t>
+  </si>
+  <si>
+    <t>kegagalan</t>
+  </si>
+  <si>
+    <t>安全側</t>
+  </si>
+  <si>
+    <t>あんぜんがわ</t>
+  </si>
+  <si>
+    <t>sisi yang aman</t>
+  </si>
+  <si>
+    <t>作動</t>
+  </si>
+  <si>
+    <t>さどう</t>
+  </si>
+  <si>
+    <t>beroperasi</t>
+  </si>
+  <si>
+    <t>bencana/kecelakaan</t>
+  </si>
+  <si>
+    <t>至る</t>
+  </si>
+  <si>
+    <t>いたる</t>
+  </si>
+  <si>
+    <t>sampai pada, berakibat</t>
+  </si>
+  <si>
+    <t>機械全体</t>
+  </si>
+  <si>
+    <t>きかいぜんたい</t>
+  </si>
+  <si>
+    <t>keseluruhan mesin</t>
+  </si>
+  <si>
+    <t>保つ</t>
+  </si>
+  <si>
+    <t>たもつ</t>
+  </si>
+  <si>
+    <t>menjaga, mempertahankan</t>
+  </si>
+  <si>
+    <t>木材加工機械</t>
+  </si>
+  <si>
+    <t>もくざいかこうきかい</t>
+  </si>
+  <si>
+    <t>mesin pengolahan kayu</t>
+  </si>
+  <si>
+    <t>pisau/pemotong</t>
+  </si>
+  <si>
+    <t>接触予防装置</t>
+  </si>
+  <si>
+    <t>せっしょくよぼうそうち</t>
+  </si>
+  <si>
+    <t>alat pencegah kontak</t>
+  </si>
+  <si>
+    <t>飛び散り</t>
+  </si>
+  <si>
+    <t>とびちり</t>
+  </si>
+  <si>
+    <t>beterbangan, terpental</t>
+  </si>
+  <si>
+    <t>防止装置</t>
+  </si>
+  <si>
+    <t>ぼうしそうち</t>
+  </si>
+  <si>
+    <t>alat pencegah</t>
+  </si>
+  <si>
+    <t>点検</t>
+  </si>
+  <si>
+    <t>てんけん</t>
+  </si>
+  <si>
+    <t>pemeriksaan</t>
+  </si>
+  <si>
+    <t>動く</t>
+  </si>
+  <si>
+    <t>うごく</t>
+  </si>
+  <si>
+    <t>bergerak</t>
+  </si>
+  <si>
+    <t>機構</t>
+  </si>
+  <si>
+    <t>mekanisme</t>
+  </si>
+  <si>
+    <t>作業者</t>
+  </si>
+  <si>
+    <t>さぎょうしゃ</t>
+  </si>
+  <si>
+    <t>pekerja</t>
+  </si>
+  <si>
+    <t>身体</t>
+  </si>
+  <si>
+    <t>からだ</t>
+  </si>
+  <si>
+    <t>tubuh</t>
+  </si>
+  <si>
+    <t>守る</t>
+  </si>
+  <si>
+    <t>まもる</t>
+  </si>
+  <si>
+    <t>melindungi</t>
+  </si>
+  <si>
+    <t>penting</t>
+  </si>
+  <si>
+    <t>取り外す</t>
+  </si>
+  <si>
+    <t>とりはずす</t>
+  </si>
+  <si>
+    <t>melepas</t>
+  </si>
+  <si>
+    <t>使用</t>
+  </si>
+  <si>
+    <t>しよう</t>
+  </si>
+  <si>
+    <t>pemeriksaan, inspeksi</t>
+  </si>
+  <si>
+    <t>mata pisau, alat pemotong</t>
+  </si>
+  <si>
+    <t>不具合</t>
+  </si>
+  <si>
+    <t>ふぐあい</t>
+  </si>
+  <si>
+    <t>kerusakan, gangguan</t>
+  </si>
+  <si>
+    <t>発生</t>
+  </si>
+  <si>
+    <t>はっせい</t>
+  </si>
+  <si>
+    <t>terjadi, timbul</t>
+  </si>
+  <si>
+    <t>定期的</t>
+  </si>
+  <si>
+    <t>ていきてき</t>
+  </si>
+  <si>
+    <t>secara berkala</t>
+  </si>
+  <si>
+    <t>整備</t>
+  </si>
+  <si>
+    <t>せいび</t>
+  </si>
+  <si>
+    <t>perawatan, pemeliharaan</t>
+  </si>
+  <si>
+    <t>適切</t>
+  </si>
+  <si>
+    <t>てきせつ</t>
+  </si>
+  <si>
+    <t>tepat, sesuai</t>
+  </si>
+  <si>
+    <t>kerusakan</t>
+  </si>
+  <si>
+    <t>pencegahan</t>
+  </si>
+  <si>
+    <t>重要</t>
+  </si>
+  <si>
+    <t>じゅうよう</t>
+  </si>
+  <si>
+    <t>kelainan, kondisi abnormal</t>
+  </si>
+  <si>
+    <t>mengetahui</t>
+  </si>
+  <si>
+    <t>調整</t>
+  </si>
+  <si>
+    <t>ちょうせい</t>
+  </si>
+  <si>
+    <t>penyetelan, penyesuaian</t>
+  </si>
+  <si>
+    <t>perawatan</t>
+  </si>
+  <si>
+    <t>掃除</t>
+  </si>
+  <si>
+    <t>そうじ</t>
+  </si>
+  <si>
+    <t>pembersihan</t>
+  </si>
+  <si>
+    <t>電源</t>
+  </si>
+  <si>
+    <t>でんげん</t>
+  </si>
+  <si>
+    <t>sumber listrik, daya</t>
+  </si>
+  <si>
+    <t>完全</t>
+  </si>
+  <si>
+    <t>かんぜん</t>
+  </si>
+  <si>
+    <t>sepenuhnya</t>
+  </si>
+  <si>
+    <t>停止</t>
+  </si>
+  <si>
+    <t>ていし</t>
+  </si>
+  <si>
+    <t>berhenti</t>
+  </si>
+  <si>
+    <t>突然</t>
+  </si>
+  <si>
+    <t>とつぜん</t>
+  </si>
+  <si>
+    <t>tiba-tiba</t>
+  </si>
+  <si>
+    <t>動き出す</t>
+  </si>
+  <si>
+    <t>うごきだす</t>
+  </si>
+  <si>
+    <t>mulai bergerak</t>
+  </si>
+  <si>
+    <t>徹底する</t>
+  </si>
+  <si>
+    <t>てっていする</t>
+  </si>
+  <si>
+    <t>menerapkan secara menyeluruh</t>
+  </si>
+  <si>
+    <t>活動</t>
+  </si>
+  <si>
+    <t>かつどう</t>
+  </si>
+  <si>
+    <t>kegiatan</t>
+  </si>
+  <si>
+    <t>整理</t>
+  </si>
+  <si>
+    <t>せいり</t>
+  </si>
+  <si>
+    <t>merapikan, memilah barang yang diperlukan dan tidak diperlukan</t>
+  </si>
+  <si>
+    <t>整頓</t>
+  </si>
+  <si>
+    <t>せいとん</t>
+  </si>
+  <si>
+    <t>menata dengan rapi</t>
+  </si>
+  <si>
+    <t>清潔</t>
+  </si>
+  <si>
+    <t>せいけつ</t>
+  </si>
+  <si>
+    <t>menjaga kebersihan</t>
+  </si>
+  <si>
+    <t>清掃</t>
+  </si>
+  <si>
+    <t>せいそう</t>
+  </si>
+  <si>
+    <t>membersihkan</t>
+  </si>
+  <si>
+    <t>日常的</t>
+  </si>
+  <si>
+    <t>にちじょうてき</t>
+  </si>
+  <si>
+    <t>sehari-hari, rutin</t>
+  </si>
+  <si>
+    <t>事業場</t>
+  </si>
+  <si>
+    <t>じぎょうじょう</t>
+  </si>
+  <si>
+    <t>tempat kerja, lokasi usaha</t>
+  </si>
+  <si>
+    <t>置く</t>
+  </si>
+  <si>
+    <t>おく</t>
+  </si>
+  <si>
+    <t>meletakkan</t>
+  </si>
+  <si>
+    <t>tempat</t>
+  </si>
+  <si>
+    <t>物</t>
+  </si>
+  <si>
+    <t>もの</t>
+  </si>
+  <si>
+    <t>barang</t>
+  </si>
+  <si>
+    <t>確保</t>
+  </si>
+  <si>
+    <t>かくほ</t>
+  </si>
+  <si>
+    <t>mengamankan, memastikan tersedia</t>
+  </si>
+  <si>
+    <t>接触事故</t>
+  </si>
+  <si>
+    <t>せっしょくじこ</t>
+  </si>
+  <si>
+    <t>kecelakaan akibat kontak/tabrakan</t>
+  </si>
+  <si>
+    <t>床</t>
+  </si>
+  <si>
+    <t>ゆか</t>
+  </si>
+  <si>
+    <t>lantai</t>
+  </si>
+  <si>
+    <t>のこ屑</t>
+  </si>
+  <si>
+    <t>のこくず</t>
+  </si>
+  <si>
+    <t>serbuk gergaji</t>
+  </si>
+  <si>
+    <t>端材</t>
+  </si>
+  <si>
+    <t>はざい</t>
+  </si>
+  <si>
+    <t>potongan sisa kayu</t>
+  </si>
+  <si>
+    <t>樹皮</t>
+  </si>
+  <si>
+    <t>じゅひ</t>
+  </si>
+  <si>
+    <t>kulit kayu</t>
+  </si>
+  <si>
+    <t>転倒事故</t>
+  </si>
+  <si>
+    <t>てんとうじこ</t>
+  </si>
+  <si>
+    <t>kecelakaan karena terjatuh</t>
+  </si>
+  <si>
+    <t>作業前</t>
+  </si>
+  <si>
+    <t>さぎょうまえ</t>
+  </si>
+  <si>
+    <t>sebelum bekerja</t>
+  </si>
+  <si>
+    <t>準備</t>
+  </si>
+  <si>
+    <t>じゅんび</t>
+  </si>
+  <si>
+    <t>persiapan</t>
+  </si>
+  <si>
+    <t>作業後</t>
+  </si>
+  <si>
+    <t>さぎょうご</t>
+  </si>
+  <si>
+    <t>setelah bekerja</t>
+  </si>
+  <si>
+    <t>片づけ</t>
+  </si>
+  <si>
+    <t>かたづけ</t>
+  </si>
+  <si>
+    <t>merapikan</t>
+  </si>
+  <si>
+    <t>日常業務</t>
+  </si>
+  <si>
+    <t>にちじょうぎょうむ</t>
+  </si>
+  <si>
+    <t>pekerjaan sehari-hari</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>なか</t>
+  </si>
+  <si>
+    <t>di dalam</t>
+  </si>
+  <si>
+    <t>第2章</t>
+  </si>
+  <si>
+    <t>だいにしょう</t>
+  </si>
+  <si>
+    <t>Bab 2</t>
+  </si>
+  <si>
+    <t>produk kayu gergajian (sawn lumber)</t>
+  </si>
+  <si>
+    <t>produk kayu gergajian</t>
+  </si>
+  <si>
+    <t>sebagian besar</t>
+  </si>
+  <si>
+    <t>土台</t>
+  </si>
+  <si>
+    <t>どだい</t>
+  </si>
+  <si>
+    <t>fondasi dasar, balok dasar</t>
+  </si>
+  <si>
+    <t>梁桁</t>
+  </si>
+  <si>
+    <t>はりけた</t>
+  </si>
+  <si>
+    <t>balok dan girder</t>
+  </si>
+  <si>
+    <t>bahan untuk pengemasan</t>
+  </si>
+  <si>
+    <t>土木建築用材</t>
+  </si>
+  <si>
+    <t>どぼくけんちくようざい</t>
+  </si>
+  <si>
+    <t>bahan konstruksi sipil dan bangunan</t>
+  </si>
+  <si>
+    <t>家具</t>
+  </si>
+  <si>
+    <t>かぐ</t>
+  </si>
+  <si>
+    <t>furnitur</t>
+  </si>
+  <si>
+    <t>建具用材</t>
+  </si>
+  <si>
+    <t>たてぐようざい</t>
+  </si>
+  <si>
+    <t>bahan untuk pintu, jendela, dan kusen</t>
+  </si>
+  <si>
+    <t>規格</t>
+  </si>
+  <si>
+    <t>きかく</t>
+  </si>
+  <si>
+    <t>standar</t>
+  </si>
+  <si>
+    <t>造作用製材</t>
+  </si>
+  <si>
+    <t>ぞうさくようせいざい</t>
+  </si>
+  <si>
+    <t>kayu gergajian untuk pekerjaan interior</t>
+  </si>
+  <si>
+    <t>目視等級区分構造用製材</t>
+  </si>
+  <si>
+    <t>もくしとうきゅうくぶんこうぞうようせいざい</t>
+  </si>
+  <si>
+    <t>kayu struktur dengan penggolongan mutu melalui pemeriksaan visual</t>
+  </si>
+  <si>
+    <t>機械等級区分構造用製材</t>
+  </si>
+  <si>
+    <t>きかいとうきゅうくぶんこうぞうようせいざい</t>
+  </si>
+  <si>
+    <t>kayu struktur dengan penggolongan mutu menggunakan mesin</t>
+  </si>
+  <si>
+    <t>下地用製材</t>
+  </si>
+  <si>
+    <t>したじようせいざい</t>
+  </si>
+  <si>
+    <t>kayu gergajian untuk dasar/lapisan bawah</t>
+  </si>
+  <si>
+    <t>広葉樹製材</t>
+  </si>
+  <si>
+    <t>こうようじゅせいざい</t>
+  </si>
+  <si>
+    <t>kayu gergajian dari pohon berdaun lebar</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>くぶん</t>
+  </si>
+  <si>
+    <t>klasifikasi</t>
+  </si>
+  <si>
+    <t>横断面</t>
+  </si>
+  <si>
+    <t>おうだんめん</t>
+  </si>
+  <si>
+    <t>penampang melintang</t>
+  </si>
+  <si>
+    <t>形</t>
+  </si>
+  <si>
+    <t>かたち</t>
+  </si>
+  <si>
+    <t>bentuk</t>
+  </si>
+  <si>
+    <t>板類</t>
+  </si>
+  <si>
+    <t>いたるい</t>
+  </si>
+  <si>
+    <t>papan</t>
+  </si>
+  <si>
+    <t>木口</t>
+  </si>
+  <si>
+    <t>こぐち</t>
+  </si>
+  <si>
+    <t>ujung potongan kayu</t>
+  </si>
+  <si>
+    <t>短辺</t>
+  </si>
+  <si>
+    <t>たんぺん</t>
+  </si>
+  <si>
+    <t>sisi pendek</t>
+  </si>
+  <si>
+    <t>未満</t>
+  </si>
+  <si>
+    <t>みまん</t>
+  </si>
+  <si>
+    <t>kurang dari</t>
+  </si>
+  <si>
+    <t>ujung kayu</t>
+  </si>
+  <si>
+    <t>長辺</t>
+  </si>
+  <si>
+    <t>ちょうへん</t>
+  </si>
+  <si>
+    <t>sisi panjang</t>
+  </si>
+  <si>
+    <t>kali</t>
+  </si>
+  <si>
+    <t>lebih dari atau sama dengan</t>
+  </si>
+  <si>
+    <t>角類</t>
+  </si>
+  <si>
+    <t>かくるい</t>
+  </si>
+  <si>
+    <t>balok persegi</t>
+  </si>
+  <si>
+    <t>円柱類</t>
+  </si>
+  <si>
+    <t>えんちゅうるい</t>
+  </si>
+  <si>
+    <t>kayu berbentuk silinder</t>
+  </si>
+  <si>
+    <t>構造用</t>
+  </si>
+  <si>
+    <t>こうぞうよう</t>
+  </si>
+  <si>
+    <t>untuk struktur</t>
+  </si>
+  <si>
+    <t>形状</t>
+  </si>
+  <si>
+    <t>けいじょう</t>
+  </si>
+  <si>
+    <t>円形</t>
+  </si>
+  <si>
+    <t>えんけい</t>
+  </si>
+  <si>
+    <t>berbentuk lingkaran</t>
+  </si>
+  <si>
+    <t>直径</t>
+  </si>
+  <si>
+    <t>ちょっけい</t>
+  </si>
+  <si>
+    <t>diameter</t>
+  </si>
+  <si>
+    <t>長さ方向</t>
+  </si>
+  <si>
+    <t>ながさほうこう</t>
+  </si>
+  <si>
+    <t>arah panjang</t>
+  </si>
+  <si>
+    <t>tetap</t>
+  </si>
+  <si>
+    <t>以下</t>
+  </si>
+  <si>
+    <t>いか</t>
+  </si>
+  <si>
+    <t>berikut ini</t>
+  </si>
+  <si>
+    <t>kayu gergajian untuk interior</t>
+  </si>
+  <si>
+    <t>pohon berdaun jarum</t>
+  </si>
+  <si>
+    <t>敷居</t>
+  </si>
+  <si>
+    <t>しきい</t>
+  </si>
+  <si>
+    <t>ambang bawah pintu</t>
+  </si>
+  <si>
+    <t>鴨居</t>
+  </si>
+  <si>
+    <t>かもい</t>
+  </si>
+  <si>
+    <t>ambang atas pintu geser</t>
+  </si>
+  <si>
+    <t>壁</t>
+  </si>
+  <si>
+    <t>かべ</t>
+  </si>
+  <si>
+    <t>dinding</t>
+  </si>
+  <si>
+    <t>bangunan</t>
+  </si>
+  <si>
+    <t>内装</t>
+  </si>
+  <si>
+    <t>ないそう</t>
+  </si>
+  <si>
+    <t>interior</t>
+  </si>
+  <si>
+    <t>構造用製材</t>
+  </si>
+  <si>
+    <t>こうぞうようせいざい</t>
+  </si>
+  <si>
+    <t>kayu struktur</t>
+  </si>
+  <si>
+    <t>構造物</t>
+  </si>
+  <si>
+    <t>こうぞうぶつ</t>
+  </si>
+  <si>
+    <t>struktur bangunan</t>
+  </si>
+  <si>
+    <t>構造耐力上主要</t>
+  </si>
+  <si>
+    <t>こうぞうたいりょくじょうしゅよう</t>
+  </si>
+  <si>
+    <t>bagian utama penahan beban</t>
+  </si>
+  <si>
+    <t>cacat</t>
+  </si>
+  <si>
+    <t>目視</t>
+  </si>
+  <si>
+    <t>もくし</t>
+  </si>
+  <si>
+    <t>pemeriksaan visual</t>
+  </si>
+  <si>
+    <t>測定</t>
+  </si>
+  <si>
+    <t>そくてい</t>
+  </si>
+  <si>
+    <t>pengukuran</t>
+  </si>
+  <si>
+    <t>等級区分</t>
+  </si>
+  <si>
+    <t>とうきゅうくぶん</t>
+  </si>
+  <si>
+    <t>klasifikasi mutu</t>
+  </si>
+  <si>
+    <t>kayu struktur dengan grading visual</t>
+  </si>
+  <si>
+    <t>ヤング係数</t>
+  </si>
+  <si>
+    <t>ヤングけいすう</t>
+  </si>
+  <si>
+    <t>modulus Young</t>
+  </si>
+  <si>
+    <t>mengukur</t>
+  </si>
+  <si>
+    <t>kayu struktur dengan grading mesin</t>
+  </si>
+  <si>
+    <t>kayu struktur grading visual</t>
+  </si>
+  <si>
+    <t>横架材</t>
+  </si>
+  <si>
+    <t>おうかざい</t>
+  </si>
+  <si>
+    <t>balok horizontal</t>
+  </si>
+  <si>
+    <t>曲げ性能</t>
+  </si>
+  <si>
+    <t>まげせいのう</t>
+  </si>
+  <si>
+    <t>kemampuan menahan lentur</t>
+  </si>
+  <si>
+    <t>digunakan</t>
+  </si>
+  <si>
+    <t>甲種構造材</t>
+  </si>
+  <si>
+    <t>こうしゅこうぞうざい</t>
+  </si>
+  <si>
+    <t>kayu struktur tipe A</t>
+  </si>
+  <si>
+    <t>柱材</t>
+  </si>
+  <si>
+    <t>はしらざい</t>
+  </si>
+  <si>
+    <t>bahan tiang</t>
+  </si>
+  <si>
+    <t>圧縮性能</t>
+  </si>
+  <si>
+    <t>あっしゅくせいのう</t>
+  </si>
+  <si>
+    <t>kemampuan menahan tekan</t>
+  </si>
+  <si>
+    <t>乙種構造材</t>
+  </si>
+  <si>
+    <t>おつしゅこうぞうざい</t>
+  </si>
+  <si>
+    <t>kayu struktur tipe B</t>
+  </si>
+  <si>
+    <t>membagi</t>
+  </si>
+  <si>
+    <t>ukuran</t>
+  </si>
+  <si>
+    <t>割れ</t>
+  </si>
+  <si>
+    <t>われ</t>
+  </si>
+  <si>
+    <t>retak</t>
+  </si>
+  <si>
+    <t>曲がり</t>
+  </si>
+  <si>
+    <t>まがり</t>
+  </si>
+  <si>
+    <t>kelengkungan</t>
+  </si>
+  <si>
+    <t>級</t>
+  </si>
+  <si>
+    <t>きゅう</t>
+  </si>
+  <si>
+    <t>tingkat</t>
+  </si>
+  <si>
+    <t>等級</t>
+  </si>
+  <si>
+    <t>とうきゅう</t>
+  </si>
+  <si>
+    <t>kelas mutu</t>
+  </si>
+  <si>
+    <t>kayu struktur grading mesin</t>
+  </si>
+  <si>
+    <t>曲げ</t>
+  </si>
+  <si>
+    <t>まげ</t>
+  </si>
+  <si>
+    <t>pembengkokan</t>
+  </si>
+  <si>
+    <t>一本</t>
+  </si>
+  <si>
+    <t>いっぽん</t>
+  </si>
+  <si>
+    <t>satu batang</t>
+  </si>
+  <si>
+    <t>段階</t>
+  </si>
+  <si>
+    <t>だんかい</t>
+  </si>
+  <si>
+    <t>tingkat, tahap</t>
+  </si>
+  <si>
+    <t>曲げ強度</t>
+  </si>
+  <si>
+    <t>まげきょうど</t>
+  </si>
+  <si>
+    <t>高くなる</t>
+  </si>
+  <si>
+    <t>たかくなる</t>
+  </si>
+  <si>
+    <t>menjadi lebih tinggi</t>
+  </si>
+  <si>
+    <t>kayu gergajian untuk lapisan dasar</t>
+  </si>
+  <si>
+    <t>pohon berdaun jarum (konifer)</t>
+  </si>
+  <si>
+    <t>屋根</t>
+  </si>
+  <si>
+    <t>やね</t>
+  </si>
+  <si>
+    <t>atap</t>
+  </si>
+  <si>
+    <t>下地</t>
+  </si>
+  <si>
+    <t>したじ</t>
+  </si>
+  <si>
+    <t>lapisan dasar, bagian penopang di balik permukaan</t>
+  </si>
+  <si>
+    <t>外部</t>
+  </si>
+  <si>
+    <t>がいぶ</t>
+  </si>
+  <si>
+    <t>bagian luar</t>
+  </si>
+  <si>
+    <t>使われる</t>
+  </si>
+  <si>
+    <t>つかわれる</t>
+  </si>
+  <si>
+    <t>商取引</t>
+  </si>
+  <si>
+    <t>しょうとりひき</t>
+  </si>
+  <si>
+    <t>transaksi perdagangan</t>
+  </si>
+  <si>
+    <t>慣習</t>
+  </si>
+  <si>
+    <t>かんしゅう</t>
+  </si>
+  <si>
+    <t>kebiasaan, praktik umum</t>
+  </si>
+  <si>
+    <t>羽柄材</t>
+  </si>
+  <si>
+    <t>はがらざい</t>
+  </si>
+  <si>
+    <t>kayu berpenampang kecil untuk konstruksi</t>
+  </si>
+  <si>
+    <t>垂木</t>
+  </si>
+  <si>
+    <t>たるき</t>
+  </si>
+  <si>
+    <t>kaso (rafter)</t>
+  </si>
+  <si>
+    <t>貫</t>
+  </si>
+  <si>
+    <t>ぬき</t>
+  </si>
+  <si>
+    <t>balok pengikat horizontal</t>
+  </si>
+  <si>
+    <t>野地板</t>
+  </si>
+  <si>
+    <t>のじいた</t>
+  </si>
+  <si>
+    <t>papan alas atap</t>
+  </si>
+  <si>
+    <t>小断面</t>
+  </si>
+  <si>
+    <t>しょうだんめん</t>
+  </si>
+  <si>
+    <t>penampang kecil</t>
+  </si>
+  <si>
+    <t>総称</t>
+  </si>
+  <si>
+    <t>そうしょう</t>
+  </si>
+  <si>
+    <t>sebutan umum, istilah kolektif</t>
+  </si>
+  <si>
+    <t>板割</t>
+  </si>
+  <si>
+    <t>いたわり</t>
+  </si>
+  <si>
+    <t>papan tebal (hasil pembelahan)</t>
+  </si>
+  <si>
+    <t>kelompok papan</t>
+  </si>
+  <si>
+    <t>厚板</t>
+  </si>
+  <si>
+    <t>あついた</t>
+  </si>
+  <si>
+    <t>papan tebal</t>
+  </si>
+  <si>
+    <t>相当する</t>
+  </si>
+  <si>
+    <t>そうとうする</t>
+  </si>
+  <si>
+    <t>setara dengan</t>
+  </si>
+  <si>
+    <t>小割材</t>
+  </si>
+  <si>
+    <t>こわりざい</t>
+  </si>
+  <si>
+    <t>kayu berukuran kecil</t>
+  </si>
+  <si>
+    <t>kayu persegi/balok</t>
+  </si>
+  <si>
+    <t>kaso</t>
+  </si>
+  <si>
+    <t>ke bawah, atau lebih kecil dari</t>
+  </si>
+  <si>
+    <t>istilah umum</t>
+  </si>
+  <si>
+    <t>たいこ材</t>
+  </si>
+  <si>
+    <t>たいこざい</t>
+  </si>
+  <si>
+    <t>balok hasil dua sisi kayu bulat digergaji rata</t>
+  </si>
+  <si>
+    <t>相対する</t>
+  </si>
+  <si>
+    <t>あいたいする</t>
+  </si>
+  <si>
+    <t>saling berhadapan</t>
+  </si>
+  <si>
+    <t>二方</t>
+  </si>
+  <si>
+    <t>にほう</t>
+  </si>
+  <si>
+    <t>dua sisi</t>
+  </si>
+  <si>
+    <t>挽く</t>
+  </si>
+  <si>
+    <t>ひく</t>
+  </si>
+  <si>
+    <t>menggergaji</t>
+  </si>
+  <si>
+    <t>根太</t>
+  </si>
+  <si>
+    <t>ねだ</t>
+  </si>
+  <si>
+    <t>balok lantai (floor joist)</t>
+  </si>
+  <si>
+    <t>小屋梁</t>
+  </si>
+  <si>
+    <t>こやばり</t>
+  </si>
+  <si>
+    <t>balok atap</t>
+  </si>
+  <si>
+    <t>用いられる</t>
+  </si>
+  <si>
+    <t>もちいられる</t>
+  </si>
+  <si>
+    <t>半割</t>
+  </si>
+  <si>
+    <t>はんわり</t>
+  </si>
+  <si>
+    <t>dibelah menjadi dua</t>
+  </si>
+  <si>
+    <t>二つ割</t>
+  </si>
+  <si>
+    <t>ふたつわり</t>
+  </si>
+  <si>
+    <t>dibelah menjadi dua bagian</t>
+  </si>
+  <si>
+    <t>三つ割</t>
+  </si>
+  <si>
+    <t>みつわり</t>
+  </si>
+  <si>
+    <t>dibelah menjadi tiga bagian</t>
+  </si>
+  <si>
+    <t>kayu persegi</t>
+  </si>
+  <si>
+    <t>筋違い</t>
+  </si>
+  <si>
+    <t>すじかい</t>
+  </si>
+  <si>
+    <t>balok diagonal (bracing)</t>
+  </si>
+  <si>
+    <t>間柱</t>
+  </si>
+  <si>
+    <t>まばしら</t>
+  </si>
+  <si>
+    <t>tiang antara (stud)</t>
+  </si>
+  <si>
+    <t>大角</t>
+  </si>
+  <si>
+    <t>だいかく</t>
+  </si>
+  <si>
+    <t>balok besar</t>
+  </si>
+  <si>
+    <t>中角</t>
+  </si>
+  <si>
+    <t>ちゅうかく</t>
+  </si>
+  <si>
+    <t>balok sedang</t>
+  </si>
+  <si>
+    <t>小角</t>
+  </si>
+  <si>
+    <t>こかく</t>
+  </si>
+  <si>
+    <t>balok kecil</t>
+  </si>
+  <si>
+    <t>輸入製材品</t>
+  </si>
+  <si>
+    <t>ゆにゅうせいざいひん</t>
+  </si>
+  <si>
+    <t>kayu gergajian impor</t>
+  </si>
+  <si>
+    <t>角材</t>
+  </si>
+  <si>
+    <t>かくざい</t>
   </si>
 </sst>
 </file>
@@ -5351,7 +6908,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G777"/>
+  <dimension ref="A1:G1118"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
@@ -16310,6 +17867,4780 @@
         <v>1668</v>
       </c>
     </row>
+    <row r="778" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A778" s="1">
+        <v>13</v>
+      </c>
+      <c r="B778" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C778" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D778" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A779" s="1">
+        <v>13</v>
+      </c>
+      <c r="B779" s="12" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C779" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D779" s="12" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A780" s="1">
+        <v>13</v>
+      </c>
+      <c r="B780" s="12" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C780" s="12" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D780" s="12" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A781" s="1">
+        <v>13</v>
+      </c>
+      <c r="B781" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C781" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D781" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A782" s="1">
+        <v>13</v>
+      </c>
+      <c r="B782" s="12" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C782" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D782" s="12" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A783" s="1">
+        <v>13</v>
+      </c>
+      <c r="B783" s="12" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C783" s="12" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D783" s="12" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A784" s="1">
+        <v>13</v>
+      </c>
+      <c r="B784" s="12" t="s">
+        <v>934</v>
+      </c>
+      <c r="C784" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="D784" s="12" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A785" s="1">
+        <v>13</v>
+      </c>
+      <c r="B785" s="12" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C785" s="12" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D785" s="12" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A786" s="1">
+        <v>13</v>
+      </c>
+      <c r="B786" s="12" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C786" s="12" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D786" s="12" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A787" s="1">
+        <v>13</v>
+      </c>
+      <c r="B787" s="12" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C787" s="12" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D787" s="12" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A788" s="1">
+        <v>13</v>
+      </c>
+      <c r="B788" s="12" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C788" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D788" s="12" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A789" s="1">
+        <v>13</v>
+      </c>
+      <c r="B789" s="12" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C789" s="12" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D789" s="12" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A790" s="1">
+        <v>13</v>
+      </c>
+      <c r="B790" s="12" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C790" s="12" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D790" s="12" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A791" s="1">
+        <v>13</v>
+      </c>
+      <c r="B791" s="12" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C791" s="12" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D791" s="12" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A792" s="1">
+        <v>13</v>
+      </c>
+      <c r="B792" s="12" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C792" s="12" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D792" s="12" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A793" s="1">
+        <v>13</v>
+      </c>
+      <c r="B793" s="12" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C793" s="12" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D793" s="12" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A794" s="1">
+        <v>13</v>
+      </c>
+      <c r="B794" s="12" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C794" s="12" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D794" s="12" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A795" s="1">
+        <v>13</v>
+      </c>
+      <c r="B795" s="12" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C795" s="12" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D795" s="12" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A796" s="1">
+        <v>13</v>
+      </c>
+      <c r="B796" s="12" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C796" s="12" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D796" s="12" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A797" s="1">
+        <v>13</v>
+      </c>
+      <c r="B797" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C797" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="D797" s="12" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A798" s="1">
+        <v>13</v>
+      </c>
+      <c r="B798" s="12" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C798" s="12" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D798" s="12" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A799" s="1">
+        <v>13</v>
+      </c>
+      <c r="B799" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C799" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D799" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A800" s="1">
+        <v>13</v>
+      </c>
+      <c r="B800" s="12" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C800" s="12" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D800" s="12" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A801" s="1">
+        <v>13</v>
+      </c>
+      <c r="B801" s="12" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C801" s="12" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D801" s="12" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A802" s="1">
+        <v>13</v>
+      </c>
+      <c r="B802" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C802" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D802" s="12" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A803" s="1">
+        <v>13</v>
+      </c>
+      <c r="B803" s="12" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C803" s="12" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D803" s="12" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A804" s="1">
+        <v>13</v>
+      </c>
+      <c r="B804" s="12" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C804" s="12" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D804" s="12" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A805" s="1">
+        <v>13</v>
+      </c>
+      <c r="B805" s="12" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C805" s="12" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D805" s="12" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A806" s="1">
+        <v>13</v>
+      </c>
+      <c r="B806" s="12" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C806" s="12" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D806" s="12" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A807" s="1">
+        <v>13</v>
+      </c>
+      <c r="B807" s="12" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C807" s="12" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D807" s="12" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A808" s="1">
+        <v>13</v>
+      </c>
+      <c r="B808" s="12" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C808" s="12" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D808" s="12" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A809" s="1">
+        <v>13</v>
+      </c>
+      <c r="B809" s="12" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C809" s="12" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D809" s="12" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A810" s="1">
+        <v>13</v>
+      </c>
+      <c r="B810" s="12" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C810" s="12" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D810" s="12" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A811" s="1">
+        <v>13</v>
+      </c>
+      <c r="B811" s="12" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C811" s="12" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D811" s="12" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A812" s="1">
+        <v>13</v>
+      </c>
+      <c r="B812" s="12" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C812" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D812" s="12" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A813" s="1">
+        <v>13</v>
+      </c>
+      <c r="B813" s="12" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C813" s="12" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D813" s="12" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A814" s="1">
+        <v>13</v>
+      </c>
+      <c r="B814" s="12" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C814" s="12" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D814" s="12" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A815" s="1">
+        <v>13</v>
+      </c>
+      <c r="B815" s="12" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C815" s="12" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D815" s="12" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A816" s="1">
+        <v>13</v>
+      </c>
+      <c r="B816" s="12" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C816" s="12" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D816" s="12" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A817" s="1">
+        <v>13</v>
+      </c>
+      <c r="B817" s="12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C817" s="12" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D817" s="12" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A818" s="1">
+        <v>13</v>
+      </c>
+      <c r="B818" s="12" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C818" s="12" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D818" s="12" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A819" s="1">
+        <v>13</v>
+      </c>
+      <c r="B819" s="12" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C819" s="12" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D819" s="12" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A820" s="1">
+        <v>13</v>
+      </c>
+      <c r="B820" s="12" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C820" s="12" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D820" s="12" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A821" s="1">
+        <v>13</v>
+      </c>
+      <c r="B821" s="12" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C821" s="12" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D821" s="12" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A822" s="1">
+        <v>13</v>
+      </c>
+      <c r="B822" s="12" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C822" s="12" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D822" s="12" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A823" s="1">
+        <v>13</v>
+      </c>
+      <c r="B823" s="12" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C823" s="12" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D823" s="12" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A824" s="1">
+        <v>13</v>
+      </c>
+      <c r="B824" s="12" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C824" s="12" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D824" s="12" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A825" s="1">
+        <v>13</v>
+      </c>
+      <c r="B825" s="12" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C825" s="12" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D825" s="12" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A826" s="1">
+        <v>13</v>
+      </c>
+      <c r="B826" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="C826" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="D826" s="12" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A827" s="1">
+        <v>13</v>
+      </c>
+      <c r="B827" s="12" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C827" s="12" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D827" s="12" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A828" s="1">
+        <v>13</v>
+      </c>
+      <c r="B828" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C828" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D828" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A829" s="1">
+        <v>13</v>
+      </c>
+      <c r="B829" s="12" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C829" s="12" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D829" s="12" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A830" s="1">
+        <v>13</v>
+      </c>
+      <c r="B830" s="12" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C830" s="12" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D830" s="12" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A831" s="1">
+        <v>13</v>
+      </c>
+      <c r="B831" s="12" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C831" s="12" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D831" s="12" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A832" s="1">
+        <v>13</v>
+      </c>
+      <c r="B832" s="12" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C832" s="12" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D832" s="12" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A833" s="1">
+        <v>13</v>
+      </c>
+      <c r="B833" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C833" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D833" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A834" s="1">
+        <v>13</v>
+      </c>
+      <c r="B834" s="12" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C834" s="12" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D834" s="12" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A835" s="1">
+        <v>13</v>
+      </c>
+      <c r="B835" s="12" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C835" s="12" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D835" s="12" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A836" s="1">
+        <v>13</v>
+      </c>
+      <c r="B836" s="12" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C836" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D836" s="12" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A837" s="1">
+        <v>13</v>
+      </c>
+      <c r="B837" s="12" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C837" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D837" s="12" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A838" s="1">
+        <v>13</v>
+      </c>
+      <c r="B838" s="12" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C838" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D838" s="12" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A839" s="1">
+        <v>13</v>
+      </c>
+      <c r="B839" s="12" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C839" s="12" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D839" s="12" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A840" s="1">
+        <v>13</v>
+      </c>
+      <c r="B840" s="12" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C840" s="12" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D840" s="12" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A841" s="1">
+        <v>13</v>
+      </c>
+      <c r="B841" s="12" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C841" s="12" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D841" s="12" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A842" s="1">
+        <v>13</v>
+      </c>
+      <c r="B842" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C842" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D842" s="12" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A843" s="1">
+        <v>13</v>
+      </c>
+      <c r="B843" s="12" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C843" s="12" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D843" s="12" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A844" s="1">
+        <v>13</v>
+      </c>
+      <c r="B844" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C844" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D844" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A845" s="1">
+        <v>13</v>
+      </c>
+      <c r="B845" s="12" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C845" s="12" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D845" s="12" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A846" s="1">
+        <v>14</v>
+      </c>
+      <c r="B846" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C846" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D846" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A847" s="1">
+        <v>14</v>
+      </c>
+      <c r="B847" s="12" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C847" s="12" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D847" s="12" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A848" s="1">
+        <v>14</v>
+      </c>
+      <c r="B848" s="12" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C848" s="12" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D848" s="12" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A849" s="1">
+        <v>14</v>
+      </c>
+      <c r="B849" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C849" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D849" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A850" s="1">
+        <v>14</v>
+      </c>
+      <c r="B850" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="C850" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="D850" s="12" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A851" s="1">
+        <v>14</v>
+      </c>
+      <c r="B851" s="12" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C851" s="12" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D851" s="12" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A852" s="1">
+        <v>14</v>
+      </c>
+      <c r="B852" s="12" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C852" s="12" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D852" s="12" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A853" s="1">
+        <v>14</v>
+      </c>
+      <c r="B853" s="12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C853" s="12" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D853" s="12" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A854" s="1">
+        <v>14</v>
+      </c>
+      <c r="B854" s="12" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C854" s="12" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D854" s="12" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A855" s="1">
+        <v>14</v>
+      </c>
+      <c r="B855" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C855" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D855" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A856" s="1">
+        <v>14</v>
+      </c>
+      <c r="B856" s="12" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C856" s="12" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D856" s="12" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A857" s="1">
+        <v>14</v>
+      </c>
+      <c r="B857" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="C857" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="D857" s="12" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A858" s="1">
+        <v>14</v>
+      </c>
+      <c r="B858" s="12" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C858" s="12" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D858" s="12" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A859" s="1">
+        <v>14</v>
+      </c>
+      <c r="B859" s="12" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C859" s="12" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D859" s="12" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A860" s="1">
+        <v>14</v>
+      </c>
+      <c r="B860" s="12" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C860" s="12" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D860" s="12" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A861" s="1">
+        <v>14</v>
+      </c>
+      <c r="B861" s="12" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C861" s="12" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D861" s="12" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A862" s="1">
+        <v>14</v>
+      </c>
+      <c r="B862" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C862" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="D862" s="12" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A863" s="1">
+        <v>14</v>
+      </c>
+      <c r="B863" s="12" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C863" s="12" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D863" s="12" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A864" s="1">
+        <v>14</v>
+      </c>
+      <c r="B864" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C864" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D864" s="12" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A865" s="1">
+        <v>14</v>
+      </c>
+      <c r="B865" s="12" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C865" s="12" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D865" s="12" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A866" s="1">
+        <v>14</v>
+      </c>
+      <c r="B866" s="12" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C866" s="12" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D866" s="12" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A867" s="1">
+        <v>14</v>
+      </c>
+      <c r="B867" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C867" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D867" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A868" s="1">
+        <v>14</v>
+      </c>
+      <c r="B868" s="12" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C868" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D868" s="12" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A869" s="1">
+        <v>14</v>
+      </c>
+      <c r="B869" s="12" t="s">
+        <v>917</v>
+      </c>
+      <c r="C869" s="12" t="s">
+        <v>918</v>
+      </c>
+      <c r="D869" s="12" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A870" s="1">
+        <v>14</v>
+      </c>
+      <c r="B870" s="12" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C870" s="12" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D870" s="12" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A871" s="1">
+        <v>14</v>
+      </c>
+      <c r="B871" s="12" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C871" s="12" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D871" s="12" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A872" s="1">
+        <v>14</v>
+      </c>
+      <c r="B872" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C872" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D872" s="12" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A873" s="1">
+        <v>14</v>
+      </c>
+      <c r="B873" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C873" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D873" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A874" s="1">
+        <v>14</v>
+      </c>
+      <c r="B874" s="12" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C874" s="12" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D874" s="12" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A875" s="1">
+        <v>14</v>
+      </c>
+      <c r="B875" s="12" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C875" s="12" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D875" s="12" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A876" s="1">
+        <v>14</v>
+      </c>
+      <c r="B876" s="12" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C876" s="12" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D876" s="12" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A877" s="1">
+        <v>14</v>
+      </c>
+      <c r="B877" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C877" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="D877" s="12" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A878" s="1">
+        <v>14</v>
+      </c>
+      <c r="B878" s="12" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C878" s="12" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D878" s="12" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A879" s="1">
+        <v>14</v>
+      </c>
+      <c r="B879" s="12" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C879" s="12" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D879" s="12" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A880" s="1">
+        <v>14</v>
+      </c>
+      <c r="B880" s="12" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C880" s="12" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D880" s="12" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A881" s="1">
+        <v>14</v>
+      </c>
+      <c r="B881" s="12" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C881" s="12" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D881" s="12" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A882" s="1">
+        <v>14</v>
+      </c>
+      <c r="B882" s="12" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C882" s="12" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D882" s="12" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A883" s="1">
+        <v>14</v>
+      </c>
+      <c r="B883" s="12" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C883" s="12" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D883" s="12" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A884" s="1">
+        <v>14</v>
+      </c>
+      <c r="B884" s="12" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C884" s="12" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D884" s="12" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A885" s="1">
+        <v>14</v>
+      </c>
+      <c r="B885" s="12" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C885" s="12" t="s">
+        <v>1841</v>
+      </c>
+      <c r="D885" s="12" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A886" s="1">
+        <v>14</v>
+      </c>
+      <c r="B886" s="12" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C886" s="12" t="s">
+        <v>1844</v>
+      </c>
+      <c r="D886" s="12" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A887" s="1">
+        <v>14</v>
+      </c>
+      <c r="B887" s="12" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C887" s="12" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D887" s="12" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A888" s="1">
+        <v>14</v>
+      </c>
+      <c r="B888" s="12" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C888" s="12" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D888" s="12" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A889" s="1">
+        <v>14</v>
+      </c>
+      <c r="B889" s="12" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C889" s="12" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D889" s="12" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A890" s="1">
+        <v>14</v>
+      </c>
+      <c r="B890" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C890" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="D890" s="12" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A891" s="1">
+        <v>14</v>
+      </c>
+      <c r="B891" s="12" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C891" s="12" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D891" s="12" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A892" s="1">
+        <v>14</v>
+      </c>
+      <c r="B892" s="12" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C892" s="12" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D892" s="12" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A893" s="1">
+        <v>14</v>
+      </c>
+      <c r="B893" s="12" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C893" s="12" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D893" s="12" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A894" s="1">
+        <v>14</v>
+      </c>
+      <c r="B894" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C894" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="D894" s="12" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A895" s="1">
+        <v>14</v>
+      </c>
+      <c r="B895" s="12" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C895" s="12" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D895" s="12" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A896" s="1">
+        <v>14</v>
+      </c>
+      <c r="B896" s="12" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C896" s="12" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D896" s="12" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A897" s="1">
+        <v>14</v>
+      </c>
+      <c r="B897" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C897" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D897" s="12" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A898" s="1">
+        <v>14</v>
+      </c>
+      <c r="B898" s="12" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C898" s="12" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D898" s="12" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A899" s="1">
+        <v>14</v>
+      </c>
+      <c r="B899" s="12" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C899" s="12" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D899" s="12" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A900" s="1">
+        <v>14</v>
+      </c>
+      <c r="B900" s="12" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C900" s="12" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D900" s="12" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A901" s="1">
+        <v>14</v>
+      </c>
+      <c r="B901" s="12" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C901" s="12" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D901" s="12" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A902" s="1">
+        <v>14</v>
+      </c>
+      <c r="B902" s="12" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C902" s="12" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D902" s="12" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A903" s="1">
+        <v>14</v>
+      </c>
+      <c r="B903" s="12" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C903" s="12" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D903" s="12" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A904" s="1">
+        <v>14</v>
+      </c>
+      <c r="B904" s="12" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C904" s="12" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D904" s="12" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A905" s="1">
+        <v>14</v>
+      </c>
+      <c r="B905" s="12" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C905" s="12" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D905" s="12" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="906" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A906" s="1">
+        <v>14</v>
+      </c>
+      <c r="B906" s="12" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C906" s="12" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D906" s="12" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="907" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A907" s="1">
+        <v>14</v>
+      </c>
+      <c r="B907" s="12" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C907" s="12" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D907" s="12" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="908" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A908" s="1">
+        <v>14</v>
+      </c>
+      <c r="B908" s="12" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C908" s="12" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D908" s="12" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="909" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A909" s="1">
+        <v>14</v>
+      </c>
+      <c r="B909" s="12" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C909" s="12" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D909" s="12" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="910" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A910" s="1">
+        <v>14</v>
+      </c>
+      <c r="B910" s="12" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C910" s="12" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D910" s="12" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="911" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A911" s="1">
+        <v>14</v>
+      </c>
+      <c r="B911" s="12" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C911" s="12" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D911" s="12" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="912" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A912" s="1">
+        <v>14</v>
+      </c>
+      <c r="B912" s="12" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C912" s="12" t="s">
+        <v>1902</v>
+      </c>
+      <c r="D912" s="12" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="913" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A913" s="1">
+        <v>14</v>
+      </c>
+      <c r="B913" s="12" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C913" s="12" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D913" s="12" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="914" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A914" s="1">
+        <v>14</v>
+      </c>
+      <c r="B914" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C914" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="D914" s="12" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="915" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A915" s="1">
+        <v>14</v>
+      </c>
+      <c r="B915" s="12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C915" s="12" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D915" s="12" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="916" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A916" s="1">
+        <v>14</v>
+      </c>
+      <c r="B916" s="12" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C916" s="12" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D916" s="12" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="917" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A917" s="1">
+        <v>14</v>
+      </c>
+      <c r="B917" s="12" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C917" s="12" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D917" s="12" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="918" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A918" s="1">
+        <v>15</v>
+      </c>
+      <c r="B918" s="12" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C918" s="12" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D918" s="12" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="919" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A919" s="1">
+        <v>15</v>
+      </c>
+      <c r="B919" s="12" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C919" s="12" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D919" s="12" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="920" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A920" s="1">
+        <v>15</v>
+      </c>
+      <c r="B920" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="C920" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="D920" s="12" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="921" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A921" s="1">
+        <v>15</v>
+      </c>
+      <c r="B921" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C921" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D921" s="12" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="922" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A922" s="1">
+        <v>15</v>
+      </c>
+      <c r="B922" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C922" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D922" s="12" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="923" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A923" s="1">
+        <v>15</v>
+      </c>
+      <c r="B923" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="C923" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="D923" s="12" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="924" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A924" s="1">
+        <v>15</v>
+      </c>
+      <c r="B924" s="12" t="s">
+        <v>951</v>
+      </c>
+      <c r="C924" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="D924" s="12" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="925" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A925" s="1">
+        <v>15</v>
+      </c>
+      <c r="B925" s="12" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C925" s="12" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D925" s="12" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="926" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A926" s="1">
+        <v>15</v>
+      </c>
+      <c r="B926" s="12" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C926" s="12" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D926" s="12" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="927" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A927" s="1">
+        <v>15</v>
+      </c>
+      <c r="B927" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="C927" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D927" s="12" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="928" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A928" s="1">
+        <v>15</v>
+      </c>
+      <c r="B928" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="C928" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D928" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="929" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A929" s="1">
+        <v>15</v>
+      </c>
+      <c r="B929" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="C929" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="D929" s="12" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="930" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A930" s="1">
+        <v>15</v>
+      </c>
+      <c r="B930" s="12" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C930" s="12" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D930" s="12" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="931" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A931" s="1">
+        <v>15</v>
+      </c>
+      <c r="B931" s="12" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C931" s="12" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D931" s="12" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="932" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A932" s="1">
+        <v>15</v>
+      </c>
+      <c r="B932" s="12" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C932" s="12" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D932" s="12" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="933" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A933" s="1">
+        <v>15</v>
+      </c>
+      <c r="B933" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="C933" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D933" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="934" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A934" s="1">
+        <v>15</v>
+      </c>
+      <c r="B934" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C934" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D934" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="935" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A935" s="1">
+        <v>15</v>
+      </c>
+      <c r="B935" s="12" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C935" s="12" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D935" s="12" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="936" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A936" s="1">
+        <v>15</v>
+      </c>
+      <c r="B936" s="12" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C936" s="12" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D936" s="12" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="937" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A937" s="1">
+        <v>15</v>
+      </c>
+      <c r="B937" s="12" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C937" s="12" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D937" s="12" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="938" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A938" s="1">
+        <v>15</v>
+      </c>
+      <c r="B938" s="12" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C938" s="12" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D938" s="12" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="939" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A939" s="1">
+        <v>15</v>
+      </c>
+      <c r="B939" s="12" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C939" s="12" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D939" s="12" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="940" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A940" s="1">
+        <v>15</v>
+      </c>
+      <c r="B940" s="12" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C940" s="12" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D940" s="12" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="941" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A941" s="1">
+        <v>15</v>
+      </c>
+      <c r="B941" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C941" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D941" s="12" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="942" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A942" s="1">
+        <v>15</v>
+      </c>
+      <c r="B942" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="C942" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D942" s="12" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="943" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A943" s="1">
+        <v>15</v>
+      </c>
+      <c r="B943" s="12" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C943" s="12" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D943" s="12" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="944" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A944" s="1">
+        <v>15</v>
+      </c>
+      <c r="B944" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C944" s="12" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D944" s="12" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="945" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A945" s="1">
+        <v>15</v>
+      </c>
+      <c r="B945" s="12" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C945" s="12" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D945" s="12" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="946" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A946" s="1">
+        <v>15</v>
+      </c>
+      <c r="B946" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="C946" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D946" s="12" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="947" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A947" s="1">
+        <v>15</v>
+      </c>
+      <c r="B947" s="12" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C947" s="12" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D947" s="12" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="948" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A948" s="1">
+        <v>15</v>
+      </c>
+      <c r="B948" s="12" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C948" s="12" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D948" s="12" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="949" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A949" s="1">
+        <v>15</v>
+      </c>
+      <c r="B949" s="12" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C949" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D949" s="12" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="950" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A950" s="1">
+        <v>15</v>
+      </c>
+      <c r="B950" s="12" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C950" s="12" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D950" s="12" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="951" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A951" s="1">
+        <v>15</v>
+      </c>
+      <c r="B951" s="12" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C951" s="12" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D951" s="12" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="952" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A952" s="1">
+        <v>15</v>
+      </c>
+      <c r="B952" s="12" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C952" s="12" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D952" s="12" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="953" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A953" s="1">
+        <v>15</v>
+      </c>
+      <c r="B953" s="12" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C953" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D953" s="12" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="954" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A954" s="1">
+        <v>15</v>
+      </c>
+      <c r="B954" s="12" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C954" s="12" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D954" s="12" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="955" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A955" s="1">
+        <v>15</v>
+      </c>
+      <c r="B955" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C955" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D955" s="12" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="956" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A956" s="1">
+        <v>15</v>
+      </c>
+      <c r="B956" s="12" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C956" s="12" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D956" s="12" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="957" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A957" s="1">
+        <v>15</v>
+      </c>
+      <c r="B957" s="12" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C957" s="12" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D957" s="12" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="958" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A958" s="1">
+        <v>15</v>
+      </c>
+      <c r="B958" s="12" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C958" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D958" s="12" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="959" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A959" s="1">
+        <v>15</v>
+      </c>
+      <c r="B959" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C959" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D959" s="12" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="960" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A960" s="1">
+        <v>15</v>
+      </c>
+      <c r="B960" s="12" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C960" s="12" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D960" s="12" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="961" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A961" s="1">
+        <v>15</v>
+      </c>
+      <c r="B961" s="12" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C961" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D961" s="12" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="962" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A962" s="1">
+        <v>15</v>
+      </c>
+      <c r="B962" s="12" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C962" s="12" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D962" s="12" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="963" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A963" s="1">
+        <v>15</v>
+      </c>
+      <c r="B963" s="12" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C963" s="12" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D963" s="12" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="964" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A964" s="1">
+        <v>15</v>
+      </c>
+      <c r="B964" s="12" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C964" s="12" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D964" s="12" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="965" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A965" s="1">
+        <v>15</v>
+      </c>
+      <c r="B965" s="12" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C965" s="12" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D965" s="12" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="966" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A966" s="1">
+        <v>15</v>
+      </c>
+      <c r="B966" s="12" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C966" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D966" s="12" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="967" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A967" s="1">
+        <v>15</v>
+      </c>
+      <c r="B967" s="12" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C967" s="12" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D967" s="12" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="968" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A968" s="1">
+        <v>15</v>
+      </c>
+      <c r="B968" s="12" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C968" s="12" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D968" s="12" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="969" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A969" s="1">
+        <v>15</v>
+      </c>
+      <c r="B969" s="12" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C969" s="12" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D969" s="12" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="970" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A970" s="1">
+        <v>15</v>
+      </c>
+      <c r="B970" s="12" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C970" s="12" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D970" s="12" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="971" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A971" s="1">
+        <v>15</v>
+      </c>
+      <c r="B971" s="12" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C971" s="12" t="s">
+        <v>1957</v>
+      </c>
+      <c r="D971" s="12" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="972" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A972" s="1">
+        <v>15</v>
+      </c>
+      <c r="B972" s="12" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C972" s="12" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D972" s="12" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="973" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A973" s="1">
+        <v>15</v>
+      </c>
+      <c r="B973" s="12" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C973" s="12" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D973" s="12" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="974" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A974" s="1">
+        <v>15</v>
+      </c>
+      <c r="B974" s="12" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C974" s="12" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D974" s="12" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="975" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A975" s="1">
+        <v>15</v>
+      </c>
+      <c r="B975" s="12" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C975" s="12" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D975" s="12" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="976" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A976" s="1">
+        <v>15</v>
+      </c>
+      <c r="B976" s="12" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C976" s="12" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D976" s="12" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="977" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A977" s="1">
+        <v>15</v>
+      </c>
+      <c r="B977" s="12" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C977" s="12" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D977" s="12" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A978" s="1">
+        <v>15</v>
+      </c>
+      <c r="B978" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C978" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D978" s="12" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="979" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A979" s="1">
+        <v>15</v>
+      </c>
+      <c r="B979" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C979" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D979" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="980" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A980" s="1">
+        <v>15</v>
+      </c>
+      <c r="B980" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C980" s="12" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D980" s="12" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="981" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A981" s="1">
+        <v>15</v>
+      </c>
+      <c r="B981" s="12" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C981" s="12" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D981" s="12" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="982" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A982" s="1">
+        <v>15</v>
+      </c>
+      <c r="B982" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="C982" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="D982" s="12" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="983" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A983" s="1">
+        <v>15</v>
+      </c>
+      <c r="B983" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C983" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D983" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="984" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A984" s="1">
+        <v>15</v>
+      </c>
+      <c r="B984" s="12" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C984" s="12" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D984" s="12" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="985" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A985" s="1">
+        <v>15</v>
+      </c>
+      <c r="B985" s="12" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C985" s="12" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D985" s="12" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="986" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A986" s="1">
+        <v>15</v>
+      </c>
+      <c r="B986" s="12" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C986" s="12" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D986" s="12" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="987" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A987" s="1">
+        <v>15</v>
+      </c>
+      <c r="B987" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C987" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D987" s="12" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="988" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A988" s="1">
+        <v>15</v>
+      </c>
+      <c r="B988" s="12" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C988" s="12" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D988" s="12" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="989" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A989" s="1">
+        <v>15</v>
+      </c>
+      <c r="B989" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="C989" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D989" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="990" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A990" s="1">
+        <v>15</v>
+      </c>
+      <c r="B990" s="12" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C990" s="12" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D990" s="12" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="991" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A991" s="1">
+        <v>15</v>
+      </c>
+      <c r="B991" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="C991" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="D991" s="12" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="992" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A992" s="1">
+        <v>15</v>
+      </c>
+      <c r="B992" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C992" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D992" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="993" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A993" s="1">
+        <v>15</v>
+      </c>
+      <c r="B993" s="12" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C993" s="12" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D993" s="12" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="994" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A994" s="1">
+        <v>15</v>
+      </c>
+      <c r="B994" s="12" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C994" s="12" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D994" s="12" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="995" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A995" s="1">
+        <v>15</v>
+      </c>
+      <c r="B995" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="C995" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="D995" s="12" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="996" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A996" s="1">
+        <v>15</v>
+      </c>
+      <c r="B996" s="12" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C996" s="12" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D996" s="12" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="997" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A997" s="1">
+        <v>15</v>
+      </c>
+      <c r="B997" s="12" t="s">
+        <v>945</v>
+      </c>
+      <c r="C997" s="12" t="s">
+        <v>946</v>
+      </c>
+      <c r="D997" s="12" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="998" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A998" s="1">
+        <v>15</v>
+      </c>
+      <c r="B998" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C998" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D998" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="999" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A999" s="1">
+        <v>15</v>
+      </c>
+      <c r="B999" s="12" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C999" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D999" s="12" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1000" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1000" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C1000" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D1000" s="12" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1001" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1001" s="12" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C1001" s="12" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D1001" s="12" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1002" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1002" s="12" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C1002" s="12" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D1002" s="12" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1003" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1003" s="12" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C1003" s="12" t="s">
+        <v>2027</v>
+      </c>
+      <c r="D1003" s="12" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1004" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1004" s="12" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C1004" s="12" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D1004" s="12" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1005" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1005" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C1005" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D1005" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1006" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1006" s="12" t="s">
+        <v>2030</v>
+      </c>
+      <c r="C1006" s="12" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D1006" s="12" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1007" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1007" s="12" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C1007" s="12" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D1007" s="12" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1008" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1008" s="12" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C1008" s="12" t="s">
+        <v>2027</v>
+      </c>
+      <c r="D1008" s="12" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1009" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1009" s="12" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C1009" s="12" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D1009" s="12" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1010" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1010" s="12" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C1010" s="12" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D1010" s="12" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1011" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1011" s="12" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C1011" s="12" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D1011" s="12" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1012" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1012" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1012" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D1012" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1013" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1013" s="12" t="s">
+        <v>2039</v>
+      </c>
+      <c r="C1013" s="12" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D1013" s="12" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1014" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1014" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1014" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1014" s="12" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1015" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1015" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="C1015" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="D1015" s="12" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1016" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1016" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="C1016" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D1016" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1017" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1017" s="12" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C1017" s="12" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D1017" s="12" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1018" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1018" s="12" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C1018" s="12" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D1018" s="12" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1019" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1019" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C1019" s="12" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D1019" s="12" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1020" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1020" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1020" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1020" s="12" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1021" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1021" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="C1021" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="D1021" s="12" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1022" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1022" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="C1022" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D1022" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1023" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1023" s="12" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C1023" s="12" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D1023" s="12" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1024" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1024" s="12" t="s">
+        <v>922</v>
+      </c>
+      <c r="C1024" s="12" t="s">
+        <v>923</v>
+      </c>
+      <c r="D1024" s="12" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1025" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1025" s="12" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C1025" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D1025" s="12" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1026" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1026" s="12" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C1026" s="12" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D1026" s="12" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1027" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1027" s="12" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C1027" s="12" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D1027" s="12" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1028" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1028" s="12" t="s">
+        <v>2060</v>
+      </c>
+      <c r="C1028" s="12" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D1028" s="12" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1029" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1029" s="12" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C1029" s="12" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D1029" s="12" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1030" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1030" s="12" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C1030" s="12" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D1030" s="12" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1031" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1031" s="12" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C1031" s="12" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D1031" s="12" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1032" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1032" s="12" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C1032" s="12" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D1032" s="12" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1033" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1033" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1033" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1033" s="12" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1034" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1034" s="12" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C1034" s="12" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D1034" s="12" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1035" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1035" s="12" t="s">
+        <v>2030</v>
+      </c>
+      <c r="C1035" s="12" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D1035" s="12" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1036" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1036" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C1036" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D1036" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1037" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1037" s="12" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1037" s="12" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D1037" s="12" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1038" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1038" s="12" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C1038" s="12" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D1038" s="12" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1039" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1039" s="12" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C1039" s="12" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D1039" s="12" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1040" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1040" s="12" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C1040" s="12" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D1040" s="12" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1041" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1041" s="12" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C1041" s="12" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D1041" s="12" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1042" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1042" s="12" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C1042" s="12" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D1042" s="12" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1043" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1043" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C1043" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D1043" s="12" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1044" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1044" s="12" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C1044" s="12" t="s">
+        <v>2080</v>
+      </c>
+      <c r="D1044" s="12" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1045" s="1">
+        <v>15</v>
+      </c>
+      <c r="B1045" s="12" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1045" s="12" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D1045" s="12" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1046" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1046" s="12" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C1046" s="12" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D1046" s="12" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1047" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1047" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="C1047" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="D1047" s="12" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1048" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1048" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1048" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D1048" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1049" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1049" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1049" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1049" s="12" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1050" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1050" s="12" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1050" s="12" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D1050" s="12" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1051" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1051" s="12" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C1051" s="12" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D1051" s="12" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1052" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1052" s="12" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C1052" s="12" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D1052" s="12" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1053" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1053" s="12" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C1053" s="12" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D1053" s="12" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1054" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1054" s="12" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C1054" s="12" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D1054" s="12" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1055" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1055" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="C1055" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="D1055" s="12" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1056" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1056" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="C1056" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="D1056" s="12" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1057" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1057" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1057" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1057" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1058" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1058" s="12" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C1058" s="12" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D1058" s="12" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1059" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1059" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="C1059" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="D1059" s="12" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1060" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1060" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1060" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D1060" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1061" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1061" s="12" t="s">
+        <v>945</v>
+      </c>
+      <c r="C1061" s="12" t="s">
+        <v>946</v>
+      </c>
+      <c r="D1061" s="12" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1062" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1062" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C1062" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D1062" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1063" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1063" s="12" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C1063" s="12" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D1063" s="12" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1064" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1064" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1064" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="D1064" s="12" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1065" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1065" s="12" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C1065" s="12" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D1065" s="12" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1066" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1066" s="12" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1066" s="12" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D1066" s="12" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1067" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1067" s="12" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C1067" s="12" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D1067" s="12" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1068" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1068" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1068" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D1068" s="12" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1069" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1069" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1069" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1069" s="12" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1070" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1070" s="12" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C1070" s="12" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D1070" s="12" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1071" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1071" s="12" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C1071" s="12" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D1071" s="12" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1072" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1072" s="12" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C1072" s="12" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D1072" s="12" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1073" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1073" s="12" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1073" s="12" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D1073" s="12" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1074" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1074" s="12" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C1074" s="12" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D1074" s="12" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1075" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1075" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1075" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1075" s="12" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1076" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1076" s="12" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1076" s="12" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D1076" s="12" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1077" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1077" s="12" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C1077" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D1077" s="12" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1078" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1078" s="12" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C1078" s="12" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D1078" s="12" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1079" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1079" s="12" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C1079" s="12" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D1079" s="12" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1080" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1080" s="12" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C1080" s="12" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D1080" s="12" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1081" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1081" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1081" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1081" s="12" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1082" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1082" s="12" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C1082" s="12" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D1082" s="12" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1083" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1083" s="12" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C1083" s="12" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D1083" s="12" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1084" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1084" s="12" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C1084" s="12" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D1084" s="12" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1085" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1085" s="12" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C1085" s="12" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D1085" s="12" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1086" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1086" s="12" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C1086" s="12" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D1086" s="12" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1087" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1087" s="12" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1087" s="12" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D1087" s="12" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1088" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1088" s="12" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C1088" s="12" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D1088" s="12" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1089" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1089" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1089" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="D1089" s="12" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1090" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1090" s="12" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1090" s="12" t="s">
+        <v>2142</v>
+      </c>
+      <c r="D1090" s="12" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1091" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1091" s="12" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C1091" s="12" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D1091" s="12" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1092" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1092" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="C1092" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="D1092" s="12" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1093" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1093" s="12" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C1093" s="12" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D1093" s="12" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1094" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1094" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1094" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1094" s="12" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1095" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1095" s="12" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C1095" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D1095" s="12" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1096" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1096" s="12" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C1096" s="12" t="s">
+        <v>2154</v>
+      </c>
+      <c r="D1096" s="12" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1097" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1097" s="12" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C1097" s="12" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D1097" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1098" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1098" s="12" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C1098" s="12" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D1098" s="12" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1099" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1099" s="12" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C1099" s="12" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D1099" s="12" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1100" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1100" s="12" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C1100" s="12" t="s">
+        <v>2165</v>
+      </c>
+      <c r="D1100" s="12" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1101" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1101" s="12" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C1101" s="12" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D1101" s="12" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1102" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1102" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1102" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1102" s="12" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1103" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1103" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1103" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="D1103" s="12" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1104" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1104" s="12" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C1104" s="12" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D1104" s="12" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1105" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1105" s="12" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C1105" s="12" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D1105" s="12" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1106" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1106" s="12" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C1106" s="12" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D1106" s="12" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1107" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1107" s="12" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C1107" s="12" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D1107" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1108" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1108" s="12" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C1108" s="12" t="s">
+        <v>2175</v>
+      </c>
+      <c r="D1108" s="12" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1109" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1109" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1109" s="12" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D1109" s="12" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1110" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1110" s="12" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C1110" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D1110" s="12" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1111" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1111" s="12" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C1111" s="12" t="s">
+        <v>2184</v>
+      </c>
+      <c r="D1111" s="12" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1112" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1112" s="12" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C1112" s="12" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D1112" s="12" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1113" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1113" s="12" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C1113" s="12" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D1113" s="12" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1114" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1114" s="12" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C1114" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D1114" s="12" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1115" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1115" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C1115" s="12" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D1115" s="12" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1116" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1116" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C1116" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1116" s="12" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1117" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1117" s="12" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C1117" s="12" t="s">
+        <v>2175</v>
+      </c>
+      <c r="D1117" s="12" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1118" s="1">
+        <v>16</v>
+      </c>
+      <c r="B1118" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="C1118" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="D1118" s="12" t="s">
+        <v>868</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/kotoba_mokuzai.xlsx
+++ b/public/kotoba_mokuzai.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\mokuzai_flashcard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DEB2AA-4956-4E1A-8868-BD6790E5E2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263A5C2A-6175-41CD-A980-F96E49F943F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3355" uniqueCount="2188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4186" uniqueCount="2517">
   <si>
     <t>第１章</t>
   </si>
@@ -6584,6 +6584,993 @@
   </si>
   <si>
     <t>かくざい</t>
+  </si>
+  <si>
+    <t>kayu laminasi (glulam)</t>
+  </si>
+  <si>
+    <t>kayu laminasi</t>
+  </si>
+  <si>
+    <t>乾燥</t>
+  </si>
+  <si>
+    <t>かんそう</t>
+  </si>
+  <si>
+    <t>pengeringan; kering</t>
+  </si>
+  <si>
+    <t>ラミナ</t>
+  </si>
+  <si>
+    <t>lamina (lembaran kayu penyusun glulam)</t>
+  </si>
+  <si>
+    <t>ukuran, dimensi</t>
+  </si>
+  <si>
+    <t>精度</t>
+  </si>
+  <si>
+    <t>せいど</t>
+  </si>
+  <si>
+    <t>tingkat ketelitian, akurasi</t>
+  </si>
+  <si>
+    <t>安定性</t>
+  </si>
+  <si>
+    <t>あんていせい</t>
+  </si>
+  <si>
+    <t>kestabilan</t>
+  </si>
+  <si>
+    <t>特徴</t>
+  </si>
+  <si>
+    <t>とくちょう</t>
+  </si>
+  <si>
+    <t>ciri khas, karakteristik</t>
+  </si>
+  <si>
+    <t>mata kayu (knot)</t>
+  </si>
+  <si>
+    <t>取り除く</t>
+  </si>
+  <si>
+    <t>とりのぞく</t>
+  </si>
+  <si>
+    <t>menghilangkan</t>
+  </si>
+  <si>
+    <t>強度性能</t>
+  </si>
+  <si>
+    <t>きょうどせいのう</t>
+  </si>
+  <si>
+    <t>performa kekuatan</t>
+  </si>
+  <si>
+    <t>sedikit</t>
+  </si>
+  <si>
+    <t>安定する</t>
+  </si>
+  <si>
+    <t>あんていする</t>
+  </si>
+  <si>
+    <t>stabil</t>
+  </si>
+  <si>
+    <t>karakteristik</t>
+  </si>
+  <si>
+    <t>幅</t>
+  </si>
+  <si>
+    <t>はば</t>
+  </si>
+  <si>
+    <t>lebar</t>
+  </si>
+  <si>
+    <t>自由</t>
+  </si>
+  <si>
+    <t>じゆう</t>
+  </si>
+  <si>
+    <t>bebas</t>
+  </si>
+  <si>
+    <t>接着</t>
+  </si>
+  <si>
+    <t>せっちゃく</t>
+  </si>
+  <si>
+    <t>perekatan, pengeleman</t>
+  </si>
+  <si>
+    <t>サイズ</t>
+  </si>
+  <si>
+    <t>ukuran (size)</t>
+  </si>
+  <si>
+    <t>自由度</t>
+  </si>
+  <si>
+    <t>じゆうど</t>
+  </si>
+  <si>
+    <t>tingkat fleksibilitas</t>
+  </si>
+  <si>
+    <t>曲がる</t>
+  </si>
+  <si>
+    <t>まがる</t>
+  </si>
+  <si>
+    <t>melengkung</t>
+  </si>
+  <si>
+    <t>用語解説</t>
+  </si>
+  <si>
+    <t>ようごかいせつ</t>
+  </si>
+  <si>
+    <t>penjelasan istilah</t>
+  </si>
+  <si>
+    <t>構成する</t>
+  </si>
+  <si>
+    <t>こうせいする</t>
+  </si>
+  <si>
+    <t>menyusun, membentuk</t>
+  </si>
+  <si>
+    <t>挽板</t>
+  </si>
+  <si>
+    <t>papan hasil gergajian (lamina)</t>
+  </si>
+  <si>
+    <t>板材</t>
+  </si>
+  <si>
+    <t>いたざい</t>
+  </si>
+  <si>
+    <t>papan kayu</t>
+  </si>
+  <si>
+    <t>balok persegi kecil</t>
+  </si>
+  <si>
+    <t>arah lebar</t>
+  </si>
+  <si>
+    <t>perekatan</t>
+  </si>
+  <si>
+    <t>kayu laminasi struktural (structural glulam)</t>
+  </si>
+  <si>
+    <t>kayu laminasi struktural</t>
+  </si>
+  <si>
+    <t>balok</t>
+  </si>
+  <si>
+    <t>balok dasar, fondasi</t>
+  </si>
+  <si>
+    <t>耐力部材</t>
+  </si>
+  <si>
+    <t>たいりょくぶざい</t>
+  </si>
+  <si>
+    <t>komponen penahan beban</t>
+  </si>
+  <si>
+    <t>penampang</t>
+  </si>
+  <si>
+    <t>大断面</t>
+  </si>
+  <si>
+    <t>だいだんめん</t>
+  </si>
+  <si>
+    <t>penampang besar</t>
+  </si>
+  <si>
+    <t>断面積</t>
+  </si>
+  <si>
+    <t>だんめんせき</t>
+  </si>
+  <si>
+    <t>luas penampang</t>
+  </si>
+  <si>
+    <t>中断面</t>
+  </si>
+  <si>
+    <t>ちゅうだんめん</t>
+  </si>
+  <si>
+    <t>penampang sedang</t>
+  </si>
+  <si>
+    <t>又は</t>
+  </si>
+  <si>
+    <t>または</t>
+  </si>
+  <si>
+    <t>atau</t>
+  </si>
+  <si>
+    <t>中断面集成材</t>
+  </si>
+  <si>
+    <t>ちゅうだんめんしゅうせいざい</t>
+  </si>
+  <si>
+    <t>glulam penampang sedang</t>
+  </si>
+  <si>
+    <t>桁</t>
+  </si>
+  <si>
+    <t>けた</t>
+  </si>
+  <si>
+    <t>girder/balok memanjang</t>
+  </si>
+  <si>
+    <t>小断面集成材</t>
+  </si>
+  <si>
+    <t>しょうだんめんしゅうせいざい</t>
+  </si>
+  <si>
+    <t>glulam penampang kecil</t>
+  </si>
+  <si>
+    <t>balok dasar</t>
+  </si>
+  <si>
+    <t>小・中断面集成材</t>
+  </si>
+  <si>
+    <t>しょう・ちゅうだんめんしゅうせいざい</t>
+  </si>
+  <si>
+    <t>glulam penampang kecil dan sedang</t>
+  </si>
+  <si>
+    <t>住宅</t>
+  </si>
+  <si>
+    <t>じゅうたく</t>
+  </si>
+  <si>
+    <t>rumah tinggal</t>
+  </si>
+  <si>
+    <t>大断面集成材</t>
+  </si>
+  <si>
+    <t>だいだんめんしゅうせいざい</t>
+  </si>
+  <si>
+    <t>glulam penampang besar</t>
+  </si>
+  <si>
+    <t>体育館</t>
+  </si>
+  <si>
+    <t>たいいくかん</t>
+  </si>
+  <si>
+    <t>gedung olahraga</t>
+  </si>
+  <si>
+    <t>商業施設</t>
+  </si>
+  <si>
+    <t>しょうぎょうしせつ</t>
+  </si>
+  <si>
+    <t>fasilitas komersial</t>
+  </si>
+  <si>
+    <t>非住宅木造建築物</t>
+  </si>
+  <si>
+    <t>ひじゅうたくもくぞうけんちくぶつ</t>
+  </si>
+  <si>
+    <t>bangunan kayu non-perumahan</t>
+  </si>
+  <si>
+    <t>決める</t>
+  </si>
+  <si>
+    <t>きめる</t>
+  </si>
+  <si>
+    <t>menetapkan</t>
+  </si>
+  <si>
+    <t>強度等級</t>
+  </si>
+  <si>
+    <t>きょうどとうきゅう</t>
+  </si>
+  <si>
+    <t>kelas kekuatan</t>
+  </si>
+  <si>
+    <t>表示</t>
+  </si>
+  <si>
+    <t>ひょうじ</t>
+  </si>
+  <si>
+    <t>penandaan, tampilan</t>
+  </si>
+  <si>
+    <t>曲げヤング係数</t>
+  </si>
+  <si>
+    <t>まげヤングけいすう</t>
+  </si>
+  <si>
+    <t>modulus Young untuk pembengkokan</t>
+  </si>
+  <si>
+    <t>menunjukkan</t>
+  </si>
+  <si>
+    <t>数字</t>
+  </si>
+  <si>
+    <t>すうじ</t>
+  </si>
+  <si>
+    <t>angka</t>
+  </si>
+  <si>
+    <t>美観</t>
+  </si>
+  <si>
+    <t>びかん</t>
+  </si>
+  <si>
+    <t>keindahan tampilan</t>
+  </si>
+  <si>
+    <t>目的</t>
+  </si>
+  <si>
+    <t>もくてき</t>
+  </si>
+  <si>
+    <t>tujuan</t>
+  </si>
+  <si>
+    <t>表面</t>
+  </si>
+  <si>
+    <t>ひょうめん</t>
+  </si>
+  <si>
+    <t>化粧薄板</t>
+  </si>
+  <si>
+    <t>けしょううすいた</t>
+  </si>
+  <si>
+    <t>veneer dekoratif</t>
+  </si>
+  <si>
+    <t>貼り付ける</t>
+  </si>
+  <si>
+    <t>はりつける</t>
+  </si>
+  <si>
+    <t>menempelkan</t>
+  </si>
+  <si>
+    <t>化粧ばり構造用集成柱</t>
+  </si>
+  <si>
+    <t>けしょうばりこうぞうようしゅうせいばしら</t>
+  </si>
+  <si>
+    <t>kolom glulam struktural berlapis veneer dekoratif</t>
+  </si>
+  <si>
+    <t>和室</t>
+  </si>
+  <si>
+    <t>わしつ</t>
+  </si>
+  <si>
+    <t>ruang bergaya Jepang</t>
+  </si>
+  <si>
+    <t>造作用集成材</t>
+  </si>
+  <si>
+    <t>ぞうさくようしゅうせいざい</t>
+  </si>
+  <si>
+    <t>kayu laminasi untuk keperluan interior/finishing</t>
+  </si>
+  <si>
+    <t>kayu laminasi untuk keperluan interior</t>
+  </si>
+  <si>
+    <t>keindahan tampilan, estetika</t>
+  </si>
+  <si>
+    <t>備える</t>
+  </si>
+  <si>
+    <t>そなえる</t>
+  </si>
+  <si>
+    <t>memiliki, dilengkapi dengan</t>
+  </si>
+  <si>
+    <t>内部造作</t>
+  </si>
+  <si>
+    <t>ないぶぞうさく</t>
+  </si>
+  <si>
+    <t>pekerjaan interior/finishing bagian dalam bangunan</t>
+  </si>
+  <si>
+    <t>化粧ばり造作用集成材</t>
+  </si>
+  <si>
+    <t>けしょうばりぞうさくようしゅうせいざい</t>
+  </si>
+  <si>
+    <t>kayu laminasi interior yang dilapisi veneer dekoratif</t>
+  </si>
+  <si>
+    <t>kayu laminasi interior berlapis veneer dekoratif</t>
+  </si>
+  <si>
+    <t>溝切り</t>
+  </si>
+  <si>
+    <t>みぞきり</t>
+  </si>
+  <si>
+    <t>pembuatan alur/grooving</t>
+  </si>
+  <si>
+    <t>飾り</t>
+  </si>
+  <si>
+    <t>かざり</t>
+  </si>
+  <si>
+    <t>hiasan, dekorasi</t>
+  </si>
+  <si>
+    <t>施す</t>
+  </si>
+  <si>
+    <t>ほどこす</t>
+  </si>
+  <si>
+    <t>memberikan, menerapkan, membuat (dekorasi/perlakuan)</t>
+  </si>
+  <si>
+    <t>kayu lapis (plywood)</t>
+  </si>
+  <si>
+    <t>kayu lapis</t>
+  </si>
+  <si>
+    <t>広い</t>
+  </si>
+  <si>
+    <t>ひろい</t>
+  </si>
+  <si>
+    <t>luas</t>
+  </si>
+  <si>
+    <t>面積</t>
+  </si>
+  <si>
+    <t>めんせき</t>
+  </si>
+  <si>
+    <t>luas area</t>
+  </si>
+  <si>
+    <t>伸び縮み</t>
+  </si>
+  <si>
+    <t>のびちぢみ</t>
+  </si>
+  <si>
+    <t>pemuaian dan penyusutan</t>
+  </si>
+  <si>
+    <t>寸法安定性</t>
+  </si>
+  <si>
+    <t>すんぽうあんていせい</t>
+  </si>
+  <si>
+    <t>kestabilan dimensi</t>
+  </si>
+  <si>
+    <t>特長</t>
+  </si>
+  <si>
+    <t>karakteristik, keunggulan</t>
+  </si>
+  <si>
+    <t>建物</t>
+  </si>
+  <si>
+    <t>たてもの</t>
+  </si>
+  <si>
+    <t>関する</t>
+  </si>
+  <si>
+    <t>かんする</t>
+  </si>
+  <si>
+    <t>berkaitan dengan</t>
+  </si>
+  <si>
+    <t>楽器</t>
+  </si>
+  <si>
+    <t>がっき</t>
+  </si>
+  <si>
+    <t>alat musik</t>
+  </si>
+  <si>
+    <t>運動用具</t>
+  </si>
+  <si>
+    <t>うんどうようぐ</t>
+  </si>
+  <si>
+    <t>peralatan olahraga</t>
+  </si>
+  <si>
+    <t>kehidupan sehari-hari</t>
+  </si>
+  <si>
+    <t>鉄道</t>
+  </si>
+  <si>
+    <t>てつどう</t>
+  </si>
+  <si>
+    <t>kereta api</t>
+  </si>
+  <si>
+    <t>車両</t>
+  </si>
+  <si>
+    <t>しゃりょう</t>
+  </si>
+  <si>
+    <t>kendaraan/gerbong</t>
+  </si>
+  <si>
+    <t>荷台</t>
+  </si>
+  <si>
+    <t>にだい</t>
+  </si>
+  <si>
+    <t>bak kendaraan (truk)</t>
+  </si>
+  <si>
+    <t>乗物</t>
+  </si>
+  <si>
+    <t>のりもの</t>
+  </si>
+  <si>
+    <t>kendaraan</t>
+  </si>
+  <si>
+    <t>sangat beragam, luas</t>
+  </si>
+  <si>
+    <t>コンクリート型枠用合板</t>
+  </si>
+  <si>
+    <t>コンクリートかたわくようごうはん</t>
+  </si>
+  <si>
+    <t>plywood untuk bekisting beton</t>
+  </si>
+  <si>
+    <t>定める</t>
+  </si>
+  <si>
+    <t>さだめる</t>
+  </si>
+  <si>
+    <t>木工製品</t>
+  </si>
+  <si>
+    <t>もっこうせいひん</t>
+  </si>
+  <si>
+    <t>produk pertukangan kayu</t>
+  </si>
+  <si>
+    <t>広く</t>
+  </si>
+  <si>
+    <t>ひろく</t>
+  </si>
+  <si>
+    <t>secara luas</t>
+  </si>
+  <si>
+    <t>plywood</t>
+  </si>
+  <si>
+    <t>主</t>
+  </si>
+  <si>
+    <t>おも</t>
+  </si>
+  <si>
+    <t>原料</t>
+  </si>
+  <si>
+    <t>げんりょう</t>
+  </si>
+  <si>
+    <t>tipis</t>
+  </si>
+  <si>
+    <t>薄物合板</t>
+  </si>
+  <si>
+    <t>うすものごうはん</t>
+  </si>
+  <si>
+    <t>plywood tipis</t>
+  </si>
+  <si>
+    <t>plywood bekisting beton</t>
+  </si>
+  <si>
+    <t>tertentu, tetap</t>
+  </si>
+  <si>
+    <t>強度</t>
+  </si>
+  <si>
+    <t>きょうど</t>
+  </si>
+  <si>
+    <t>耐水性能</t>
+  </si>
+  <si>
+    <t>たいすいせいのう</t>
+  </si>
+  <si>
+    <t>ketahanan terhadap air</t>
+  </si>
+  <si>
+    <t>流し込む</t>
+  </si>
+  <si>
+    <t>ながしこむ</t>
+  </si>
+  <si>
+    <t>menuangkan</t>
+  </si>
+  <si>
+    <t>成形</t>
+  </si>
+  <si>
+    <t>せいけい</t>
+  </si>
+  <si>
+    <t>pembentukan, pencetakan</t>
+  </si>
+  <si>
+    <t>型枠</t>
+  </si>
+  <si>
+    <t>かたわく</t>
+  </si>
+  <si>
+    <t>cetakan/bekisting</t>
+  </si>
+  <si>
+    <t>建設</t>
+  </si>
+  <si>
+    <t>けんせつ</t>
+  </si>
+  <si>
+    <t>konstruksi</t>
+  </si>
+  <si>
+    <t>土木工事</t>
+  </si>
+  <si>
+    <t>どぼくこうじ</t>
+  </si>
+  <si>
+    <t>pekerjaan sipil</t>
+  </si>
+  <si>
+    <t>現場</t>
+  </si>
+  <si>
+    <t>げんば</t>
+  </si>
+  <si>
+    <t>lokasi kerja, lapangan</t>
+  </si>
+  <si>
+    <t>打設</t>
+  </si>
+  <si>
+    <t>だせつ</t>
+  </si>
+  <si>
+    <t>pengecoran beton</t>
+  </si>
+  <si>
+    <t>後</t>
+  </si>
+  <si>
+    <t>ご</t>
+  </si>
+  <si>
+    <t>setelah</t>
+  </si>
+  <si>
+    <t>滑らか</t>
+  </si>
+  <si>
+    <t>なめらか</t>
+  </si>
+  <si>
+    <t>halus, rata</t>
+  </si>
+  <si>
+    <t>付きにくい</t>
+  </si>
+  <si>
+    <t>つきにくい</t>
+  </si>
+  <si>
+    <t>sulit menempel</t>
+  </si>
+  <si>
+    <t>塗装</t>
+  </si>
+  <si>
+    <t>とそう</t>
+  </si>
+  <si>
+    <t>pelapisan cat, coating</t>
+  </si>
+  <si>
+    <t>仕上げ加工</t>
+  </si>
+  <si>
+    <t>しあげかこう</t>
+  </si>
+  <si>
+    <t>proses finishing</t>
+  </si>
+  <si>
+    <t>構造耐力上</t>
+  </si>
+  <si>
+    <t>こうぞうたいりょくじょう</t>
+  </si>
+  <si>
+    <t>dari segi kekuatan struktur</t>
+  </si>
+  <si>
+    <t>bagian, lokasi</t>
+  </si>
+  <si>
+    <t>下地材</t>
+  </si>
+  <si>
+    <t>したじざい</t>
+  </si>
+  <si>
+    <t>bahan dasar/lapisan dasar</t>
+  </si>
+  <si>
+    <t>国産針葉樹</t>
+  </si>
+  <si>
+    <t>こくさんしんようじゅ</t>
+  </si>
+  <si>
+    <t>pohon konifer produksi dalam negeri</t>
+  </si>
+  <si>
+    <t>普及</t>
+  </si>
+  <si>
+    <t>ふきゅう</t>
+  </si>
+  <si>
+    <t>penyebaran, penggunaan luas</t>
+  </si>
+  <si>
+    <t>khususnya</t>
+  </si>
+  <si>
+    <t>厚物構造用合板</t>
+  </si>
+  <si>
+    <t>あつものこうぞうようごうはん</t>
+  </si>
+  <si>
+    <t>plywood struktural tebal</t>
+  </si>
+  <si>
+    <t>balok penyangga lantai (floor joist)</t>
+  </si>
+  <si>
+    <t>省略</t>
+  </si>
+  <si>
+    <t>しょうりゃく</t>
+  </si>
+  <si>
+    <t>penghilangan, penyederhanaan</t>
+  </si>
+  <si>
+    <t>進む</t>
+  </si>
+  <si>
+    <t>すすむ</t>
+  </si>
+  <si>
+    <t>berkembang, maju</t>
+  </si>
+  <si>
+    <t>強度試験</t>
+  </si>
+  <si>
+    <t>きょうどしけん</t>
+  </si>
+  <si>
+    <t>uji kekuatan</t>
+  </si>
+  <si>
+    <t>kelas/tingkat</t>
+  </si>
+  <si>
+    <t>接着性能</t>
+  </si>
+  <si>
+    <t>せっちゃくせいのう</t>
+  </si>
+  <si>
+    <t>performa daya rekat</t>
+  </si>
+  <si>
+    <t>特類</t>
+  </si>
+  <si>
+    <t>とくるい</t>
+  </si>
+  <si>
+    <t>kelas khusus</t>
+  </si>
+  <si>
+    <t>kategori/kelas</t>
+  </si>
+  <si>
+    <t>secara umum</t>
+  </si>
+  <si>
+    <t>bahan lapisan dasar</t>
+  </si>
+  <si>
+    <t>kelas</t>
+  </si>
+  <si>
+    <t>gambar, ilustrasi</t>
+  </si>
+  <si>
+    <t>使用例</t>
+  </si>
+  <si>
+    <t>しようれい</t>
+  </si>
+  <si>
+    <t>contoh penggunaan</t>
+  </si>
+  <si>
+    <t>写真</t>
+  </si>
+  <si>
+    <t>しゃしん</t>
+  </si>
+  <si>
+    <t>foto</t>
+  </si>
+  <si>
+    <t>工業</t>
+  </si>
+  <si>
+    <t>こうぎょう</t>
+  </si>
+  <si>
+    <t>industri</t>
+  </si>
+  <si>
+    <t>組合</t>
+  </si>
+  <si>
+    <t>くみあい</t>
+  </si>
+  <si>
+    <t>asosiasi, serikat</t>
+  </si>
+  <si>
+    <t>連合会</t>
+  </si>
+  <si>
+    <t>れんごうかい</t>
+  </si>
+  <si>
+    <t>federasi, gabungan asosiasi</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>エイチピー</t>
+  </si>
+  <si>
+    <t>homepage (situs web)</t>
   </si>
 </sst>
 </file>
@@ -6908,7 +7895,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G1118"/>
+  <dimension ref="A1:G1395"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
@@ -22641,6 +23628,3884 @@
         <v>868</v>
       </c>
     </row>
+    <row r="1119" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1119" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1119" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1119" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1119" s="12" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1120" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1120" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1120" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1120" s="12" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1121" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1121" s="12" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C1121" s="12" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D1121" s="12" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1122" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1122" s="12" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C1122" s="12" t="s">
+        <v>2193</v>
+      </c>
+      <c r="D1122" s="12" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1123" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1123" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="C1123" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D1123" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1124" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1124" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="C1124" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="D1124" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1125" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1125" s="12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C1125" s="12" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D1125" s="12" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1126" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1126" s="12" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C1126" s="12" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D1126" s="12" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1127" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1127" s="12" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C1127" s="12" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D1127" s="12" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1128" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1128" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1128" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D1128" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1129" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1129" s="12" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C1129" s="12" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D1129" s="12" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1130" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1130" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="C1130" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="D1130" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1131" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1131" s="12" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C1131" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D1131" s="12" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1132" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1132" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C1132" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D1132" s="12" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1133" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1133" s="12" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C1133" s="12" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D1133" s="12" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1134" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1134" s="12" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C1134" s="12" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D1134" s="12" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1135" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1135" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1135" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1135" s="12" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1136" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1136" s="12" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C1136" s="12" t="s">
+        <v>2214</v>
+      </c>
+      <c r="D1136" s="12" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1137" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1137" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C1137" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D1137" s="12" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1138" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1138" s="12" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C1138" s="12" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D1138" s="12" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1139" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1139" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1139" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1139" s="12" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1140" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1140" s="12" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C1140" s="12" t="s">
+        <v>2218</v>
+      </c>
+      <c r="D1140" s="12" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1141" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1141" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1141" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="D1141" s="12" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1142" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1142" s="12" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C1142" s="12" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D1142" s="12" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1143" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1143" s="12" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C1143" s="12" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D1143" s="12" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1144" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1144" s="12" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C1144" s="12" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D1144" s="12" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1145" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1145" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="C1145" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="D1145" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1146" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1146" s="12" t="s">
+        <v>2226</v>
+      </c>
+      <c r="C1146" s="12" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D1146" s="12" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1147" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1147" s="12" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C1147" s="12" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D1147" s="12" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1148" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1148" s="12" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C1148" s="12" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D1148" s="12" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1149" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1149" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1149" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D1149" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1150" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1150" s="12" t="s">
+        <v>942</v>
+      </c>
+      <c r="C1150" s="12" t="s">
+        <v>943</v>
+      </c>
+      <c r="D1150" s="12" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1151" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1151" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C1151" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D1151" s="12" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1152" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1152" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1152" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1152" s="12" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1153" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1153" s="12" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C1153" s="12" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D1153" s="12" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1154" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1154" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C1154" s="12" t="s">
+        <v>1951</v>
+      </c>
+      <c r="D1154" s="12" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1155" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1155" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1155" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1155" s="12" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1156" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1156" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="C1156" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="D1156" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1157" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1157" s="12" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C1157" s="12" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D1157" s="12" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1158" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1158" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1158" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1158" s="12" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1159" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1159" s="12" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C1159" s="12" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D1159" s="12" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1160" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1160" s="12" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C1160" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D1160" s="12" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1161" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1161" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1161" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1161" s="12" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1162" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1162" s="12" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C1162" s="12" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D1162" s="12" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1163" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1163" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C1163" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D1163" s="12" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1164" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1164" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="C1164" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="D1164" s="12" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1165" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1165" s="12" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C1165" s="12" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D1165" s="12" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1166" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1166" s="12" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C1166" s="12" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D1166" s="12" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1167" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1167" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1167" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1167" s="12" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1168" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1168" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1168" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1168" s="12" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1169" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1169" s="12" t="s">
+        <v>951</v>
+      </c>
+      <c r="C1169" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="D1169" s="12" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1170" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1170" s="12" t="s">
+        <v>954</v>
+      </c>
+      <c r="C1170" s="12" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1170" s="12" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1171" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1171" s="12" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C1171" s="12" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D1171" s="12" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1172" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1172" s="12" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C1172" s="12" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D1172" s="12" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1173" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1173" s="12" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C1173" s="12" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D1173" s="12" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1174" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1174" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1174" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1174" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1175" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1175" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C1175" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D1175" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1176" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1176" s="12" t="s">
+        <v>753</v>
+      </c>
+      <c r="C1176" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="D1176" s="12" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1177" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1177" s="12" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C1177" s="12" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D1177" s="12" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1178" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1178" s="12" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C1178" s="12" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D1178" s="12" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1179" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1179" s="12" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C1179" s="12" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D1179" s="12" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1180" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1180" s="12" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C1180" s="12" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D1180" s="12" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1181" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1181" s="12" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C1181" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D1181" s="12" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1182" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1182" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C1182" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1182" s="12" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1183" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1183" s="12" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C1183" s="12" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D1183" s="12" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1184" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1184" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C1184" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1184" s="12" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1185" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1185" s="12" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C1185" s="12" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D1185" s="12" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1186" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1186" s="12" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C1186" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D1186" s="12" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1187" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1187" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C1187" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1187" s="12" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1188" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1188" s="12" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C1188" s="12" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D1188" s="12" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1189" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1189" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C1189" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1189" s="12" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1190" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1190" s="12" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C1190" s="12" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D1190" s="12" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1191" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1191" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1191" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="D1191" s="12" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1192" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1192" s="12" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C1192" s="12" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D1192" s="12" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1193" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1193" s="12" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C1193" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D1193" s="12" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1194" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1194" s="12" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C1194" s="12" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D1194" s="12" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1195" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1195" s="12" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C1195" s="12" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D1195" s="12" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1196" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1196" s="12" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C1196" s="12" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D1196" s="12" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1197" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1197" s="12" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C1197" s="12" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D1197" s="12" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1198" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1198" s="12" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C1198" s="12" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D1198" s="12" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1199" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1199" s="12" t="s">
+        <v>954</v>
+      </c>
+      <c r="C1199" s="12" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1199" s="12" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1200" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1200" s="12" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C1200" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D1200" s="12" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1201" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1201" s="12" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C1201" s="12" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D1201" s="12" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1202" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1202" s="12" t="s">
+        <v>951</v>
+      </c>
+      <c r="C1202" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="D1202" s="12" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1203" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1203" s="12" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C1203" s="12" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D1203" s="12" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1204" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1204" s="12" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C1204" s="12" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D1204" s="12" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1205" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1205" s="12" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C1205" s="12" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D1205" s="12" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1206" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1206" s="12" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C1206" s="12" t="s">
+        <v>2285</v>
+      </c>
+      <c r="D1206" s="12" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1207" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1207" s="12" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C1207" s="12" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D1207" s="12" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1208" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1208" s="12" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C1208" s="12" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D1208" s="12" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1209" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1209" s="12" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C1209" s="12" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D1209" s="12" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1210" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1210" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1210" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1210" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1211" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1211" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1211" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1211" s="12" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1212" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1212" s="12" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C1212" s="12" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D1212" s="12" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1213" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1213" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C1213" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D1213" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1214" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1214" s="12" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C1214" s="12" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D1214" s="12" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1215" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1215" s="12" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C1215" s="12" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D1215" s="12" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1216" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1216" s="12" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C1216" s="12" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D1216" s="12" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1217" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1217" s="12" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C1217" s="12" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D1217" s="12" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1218" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1218" s="12" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C1218" s="12" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D1218" s="12" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1219" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1219" s="12" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C1219" s="12" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D1219" s="12" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1220" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1220" s="12" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C1220" s="12" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D1220" s="12" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1221" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1221" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C1221" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D1221" s="12" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1222" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1222" s="12" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C1222" s="12" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D1222" s="12" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1223" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1223" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1223" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D1223" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1224" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1224" s="12" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C1224" s="12" t="s">
+        <v>2313</v>
+      </c>
+      <c r="D1224" s="12" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1225" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1225" s="12" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C1225" s="12" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D1225" s="12" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1226" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1226" s="12" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C1226" s="12" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D1226" s="12" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1227" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1227" s="12" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C1227" s="12" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D1227" s="12" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1228" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1228" s="12" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1228" s="12" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D1228" s="12" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1229" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1229" s="12" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C1229" s="12" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D1229" s="12" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1230" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1230" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="C1230" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="D1230" s="12" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1231" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1231" s="12" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C1231" s="12" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D1231" s="12" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1232" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1232" s="12" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C1232" s="12" t="s">
+        <v>2330</v>
+      </c>
+      <c r="D1232" s="12" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1233" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1233" s="12" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C1233" s="12" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D1233" s="12" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1234" s="1">
+        <v>18</v>
+      </c>
+      <c r="B1234" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1234" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1234" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1235" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1235" s="12" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C1235" s="12" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D1235" s="12" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1236" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1236" s="12" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C1236" s="12" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D1236" s="12" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1237" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1237" s="12" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C1237" s="12" t="s">
+        <v>2313</v>
+      </c>
+      <c r="D1237" s="12" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1238" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1238" s="12" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C1238" s="12" t="s">
+        <v>2338</v>
+      </c>
+      <c r="D1238" s="12" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1239" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1239" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1239" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1239" s="12" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1240" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1240" s="12" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C1240" s="12" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D1240" s="12" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1241" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1241" s="12" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C1241" s="12" t="s">
+        <v>2341</v>
+      </c>
+      <c r="D1241" s="12" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1242" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1242" s="12" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C1242" s="12" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D1242" s="12" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1243" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1243" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1243" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1243" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1244" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1244" s="12" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C1244" s="12" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D1244" s="12" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1245" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1245" s="12" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C1245" s="12" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D1245" s="12" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1246" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1246" s="12" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C1246" s="12" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D1246" s="12" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1247" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1247" s="12" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1247" s="12" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D1247" s="12" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1248" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1248" s="12" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C1248" s="12" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D1248" s="12" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1249" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1249" s="12" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C1249" s="12" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D1249" s="12" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1250" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1250" s="12" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C1250" s="12" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D1250" s="12" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1251" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1251" s="12" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C1251" s="12" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D1251" s="12" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1252" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1252" s="12" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C1252" s="12" t="s">
+        <v>2348</v>
+      </c>
+      <c r="D1252" s="12" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1253" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1253" s="12" t="s">
+        <v>2350</v>
+      </c>
+      <c r="C1253" s="12" t="s">
+        <v>2351</v>
+      </c>
+      <c r="D1253" s="12" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1254" s="1">
+        <v>19</v>
+      </c>
+      <c r="B1254" s="12" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C1254" s="12" t="s">
+        <v>2354</v>
+      </c>
+      <c r="D1254" s="12" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1255" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1255" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1255" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="D1255" s="12" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1256" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1256" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1256" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="D1256" s="12" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1257" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1257" s="12" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C1257" s="12" t="s">
+        <v>2359</v>
+      </c>
+      <c r="D1257" s="12" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1258" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1258" s="12" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C1258" s="12" t="s">
+        <v>2362</v>
+      </c>
+      <c r="D1258" s="12" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1259" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1259" s="12" t="s">
+        <v>948</v>
+      </c>
+      <c r="C1259" s="12" t="s">
+        <v>949</v>
+      </c>
+      <c r="D1259" s="12" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1260" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1260" s="12" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C1260" s="12" t="s">
+        <v>2365</v>
+      </c>
+      <c r="D1260" s="12" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1261" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1261" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1261" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1261" s="12" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1262" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1262" s="12" t="s">
+        <v>2367</v>
+      </c>
+      <c r="C1262" s="12" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D1262" s="12" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1263" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1263" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1263" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D1263" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1264" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1264" s="12" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C1264" s="12" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D1264" s="12" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1265" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1265" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C1265" s="12" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D1265" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1266" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1266" s="12" t="s">
+        <v>948</v>
+      </c>
+      <c r="C1266" s="12" t="s">
+        <v>949</v>
+      </c>
+      <c r="D1266" s="12" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1267" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1267" s="12" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C1267" s="12" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D1267" s="12" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1268" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1268" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C1268" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D1268" s="12" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1269" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1269" s="12" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C1269" s="12" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D1269" s="12" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1270" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1270" s="12" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C1270" s="12" t="s">
+        <v>2373</v>
+      </c>
+      <c r="D1270" s="12" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1271" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1271" s="12" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C1271" s="12" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D1271" s="12" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1272" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1272" s="12" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C1272" s="12" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D1272" s="12" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1273" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1273" s="12" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C1273" s="12" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D1273" s="12" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1274" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1274" s="12" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C1274" s="12" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D1274" s="12" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1275" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1275" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1275" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1275" s="12" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1276" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1276" s="12" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C1276" s="12" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D1276" s="12" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1277" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1277" s="12" t="s">
+        <v>2384</v>
+      </c>
+      <c r="C1277" s="12" t="s">
+        <v>2385</v>
+      </c>
+      <c r="D1277" s="12" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1278" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1278" s="12" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C1278" s="12" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D1278" s="12" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1279" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1279" s="12" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C1279" s="12" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D1279" s="12" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1280" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1280" s="12" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C1280" s="12" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D1280" s="12" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1281" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1281" s="12" t="s">
+        <v>2393</v>
+      </c>
+      <c r="C1281" s="12" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D1281" s="12" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1282" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1282" s="12" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C1282" s="12" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D1282" s="12" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1283" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1283" s="12" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C1283" s="12" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D1283" s="12" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1284" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1284" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C1284" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D1284" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1285" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1285" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C1285" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D1285" s="12" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1286" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1286" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="C1286" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="D1286" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1287" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1287" s="12" t="s">
+        <v>2397</v>
+      </c>
+      <c r="C1287" s="12" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D1287" s="12" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1288" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1288" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="C1288" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="D1288" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1289" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1289" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1289" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D1289" s="12" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1290" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1290" s="12" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C1290" s="12" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D1290" s="12" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1291" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1291" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="C1291" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="D1291" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1292" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1292" s="12" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C1292" s="12" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D1292" s="12" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1293" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1293" s="12" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C1293" s="12" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D1293" s="12" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1294" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1294" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1294" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="D1294" s="12" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1295" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1295" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C1295" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D1295" s="12" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1296" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1296" s="12" t="s">
+        <v>2405</v>
+      </c>
+      <c r="C1296" s="12" t="s">
+        <v>2406</v>
+      </c>
+      <c r="D1296" s="12" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1297" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1297" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1297" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1297" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1298" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1298" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1298" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="D1298" s="12" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1299" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1299" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="C1299" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="D1299" s="12" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1300" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1300" s="12" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C1300" s="12" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D1300" s="12" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1301" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1301" s="12" t="s">
+        <v>2411</v>
+      </c>
+      <c r="C1301" s="12" t="s">
+        <v>2412</v>
+      </c>
+      <c r="D1301" s="12" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1302" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1302" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1302" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="D1302" s="12" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1303" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1303" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="C1303" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="D1303" s="12" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1304" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1304" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1304" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="D1304" s="12" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1305" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1305" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C1305" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D1305" s="12" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1306" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1306" s="12" t="s">
+        <v>934</v>
+      </c>
+      <c r="C1306" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="D1306" s="12" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1307" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1307" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="C1307" s="12" t="s">
+        <v>889</v>
+      </c>
+      <c r="D1307" s="12" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1308" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1308" s="12" t="s">
+        <v>2414</v>
+      </c>
+      <c r="C1308" s="12" t="s">
+        <v>2415</v>
+      </c>
+      <c r="D1308" s="12" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1309" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1309" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="C1309" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="D1309" s="12" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1310" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1310" s="12" t="s">
+        <v>2397</v>
+      </c>
+      <c r="C1310" s="12" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D1310" s="12" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1311" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1311" s="12" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1311" s="12" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D1311" s="12" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1312" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1312" s="12" t="s">
+        <v>2419</v>
+      </c>
+      <c r="C1312" s="12" t="s">
+        <v>2420</v>
+      </c>
+      <c r="D1312" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1313" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1313" s="12" t="s">
+        <v>2421</v>
+      </c>
+      <c r="C1313" s="12" t="s">
+        <v>2422</v>
+      </c>
+      <c r="D1313" s="12" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1314" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1314" s="12" t="s">
+        <v>2424</v>
+      </c>
+      <c r="C1314" s="12" t="s">
+        <v>2425</v>
+      </c>
+      <c r="D1314" s="12" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1315" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1315" s="12" t="s">
+        <v>2427</v>
+      </c>
+      <c r="C1315" s="12" t="s">
+        <v>2428</v>
+      </c>
+      <c r="D1315" s="12" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1316" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1316" s="12" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C1316" s="12" t="s">
+        <v>2431</v>
+      </c>
+      <c r="D1316" s="12" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1317" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1317" s="12" t="s">
+        <v>2433</v>
+      </c>
+      <c r="C1317" s="12" t="s">
+        <v>2434</v>
+      </c>
+      <c r="D1317" s="12" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1318" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1318" s="12" t="s">
+        <v>2436</v>
+      </c>
+      <c r="C1318" s="12" t="s">
+        <v>2437</v>
+      </c>
+      <c r="D1318" s="12" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1319" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1319" s="12" t="s">
+        <v>2439</v>
+      </c>
+      <c r="C1319" s="12" t="s">
+        <v>2440</v>
+      </c>
+      <c r="D1319" s="12" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1320" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1320" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="C1320" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="D1320" s="12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1321" s="1">
+        <v>20</v>
+      </c>
+      <c r="B1321" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1321" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1321" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1322" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1322" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1322" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1322" s="12" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1323" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1323" s="12" t="s">
+        <v>2442</v>
+      </c>
+      <c r="C1323" s="12" t="s">
+        <v>2443</v>
+      </c>
+      <c r="D1323" s="12" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1324" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1324" s="12" t="s">
+        <v>2445</v>
+      </c>
+      <c r="C1324" s="12" t="s">
+        <v>2446</v>
+      </c>
+      <c r="D1324" s="12" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1325" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1325" s="12" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C1325" s="12" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D1325" s="12" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1326" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1326" s="12" t="s">
+        <v>2448</v>
+      </c>
+      <c r="C1326" s="12" t="s">
+        <v>2449</v>
+      </c>
+      <c r="D1326" s="12" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1327" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1327" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1327" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="D1327" s="12" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1328" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1328" s="12" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C1328" s="12" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D1328" s="12" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1329" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1329" s="12" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C1329" s="12" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D1329" s="12" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1330" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1330" s="12" t="s">
+        <v>2454</v>
+      </c>
+      <c r="C1330" s="12" t="s">
+        <v>2455</v>
+      </c>
+      <c r="D1330" s="12" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1331" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1331" s="12" t="s">
+        <v>2457</v>
+      </c>
+      <c r="C1331" s="12" t="s">
+        <v>2458</v>
+      </c>
+      <c r="D1331" s="12" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1332" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1332" s="12" t="s">
+        <v>2397</v>
+      </c>
+      <c r="C1332" s="12" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D1332" s="12" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1333" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1333" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="C1333" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="D1333" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1334" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1334" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1334" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1334" s="12" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1335" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1335" s="12" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C1335" s="12" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D1335" s="12" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1336" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1336" s="12" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C1336" s="12" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D1336" s="12" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1337" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1337" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C1337" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D1337" s="12" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1338" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1338" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1338" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1338" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1339" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1339" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1339" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="D1339" s="12" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1340" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1340" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="C1340" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="D1340" s="12" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1341" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1341" s="12" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C1341" s="12" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D1341" s="12" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1342" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1342" s="12" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C1342" s="12" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D1342" s="12" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1343" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1343" s="12" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1343" s="12" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D1343" s="12" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1344" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1344" s="12" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C1344" s="12" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D1344" s="12" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1345" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1345" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1345" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1345" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1346" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1346" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1346" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D1346" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1347" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1347" s="12" t="s">
+        <v>2467</v>
+      </c>
+      <c r="C1347" s="12" t="s">
+        <v>2468</v>
+      </c>
+      <c r="D1347" s="12" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1348" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1348" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1348" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1348" s="12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1349" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1349" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="C1349" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="D1349" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1350" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1350" s="12" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C1350" s="12" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D1350" s="12" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1351" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1351" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="C1351" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="D1351" s="12" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1352" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1352" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1352" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="D1352" s="12" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1353" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1353" s="12" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C1353" s="12" t="s">
+        <v>2471</v>
+      </c>
+      <c r="D1353" s="12" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1354" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1354" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1354" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="D1354" s="12" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1355" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1355" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1355" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="D1355" s="12" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1356" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1356" s="12" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C1356" s="12" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D1356" s="12" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1357" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1357" s="12" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C1357" s="12" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D1357" s="12" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1358" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1358" s="12" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C1358" s="12" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D1358" s="12" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1359" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1359" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1359" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1359" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1360" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1360" s="12" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C1360" s="12" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D1360" s="12" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1361" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1361" s="12" t="s">
+        <v>2474</v>
+      </c>
+      <c r="C1361" s="12" t="s">
+        <v>2475</v>
+      </c>
+      <c r="D1361" s="12" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1362" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1362" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="C1362" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="D1362" s="12" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1363" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1363" s="12" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C1363" s="12" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D1363" s="12" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1364" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1364" s="12" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C1364" s="12" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D1364" s="12" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1365" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1365" s="12" t="s">
+        <v>2478</v>
+      </c>
+      <c r="C1365" s="12" t="s">
+        <v>2479</v>
+      </c>
+      <c r="D1365" s="12" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1366" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1366" s="12" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C1366" s="12" t="s">
+        <v>2471</v>
+      </c>
+      <c r="D1366" s="12" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1367" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1367" s="12" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C1367" s="12" t="s">
+        <v>2482</v>
+      </c>
+      <c r="D1367" s="12" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1368" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1368" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C1368" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D1368" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1369" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1369" s="12" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C1369" s="12" t="s">
+        <v>2485</v>
+      </c>
+      <c r="D1369" s="12" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1370" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1370" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1370" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D1370" s="12" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1371" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1371" s="12" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C1371" s="12" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D1371" s="12" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1372" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1372" s="12" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C1372" s="12" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D1372" s="12" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1373" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1373" s="12" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C1373" s="12" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D1373" s="12" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1374" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1374" s="12" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C1374" s="12" t="s">
+        <v>2489</v>
+      </c>
+      <c r="D1374" s="12" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1375" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1375" s="12" t="s">
+        <v>2491</v>
+      </c>
+      <c r="C1375" s="12" t="s">
+        <v>2492</v>
+      </c>
+      <c r="D1375" s="12" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1376" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1376" s="12" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C1376" s="12" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D1376" s="12" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1377" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1377" s="12" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C1377" s="12" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D1377" s="12" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1378" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1378" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1378" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="D1378" s="12" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1379" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1379" s="12" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C1379" s="12" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D1379" s="12" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1380" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1380" s="12" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C1380" s="12" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D1380" s="12" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1381" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1381" s="12" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1381" s="12" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D1381" s="12" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1382" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1382" s="12" t="s">
+        <v>2464</v>
+      </c>
+      <c r="C1382" s="12" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D1382" s="12" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1383" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1383" s="12" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C1383" s="12" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D1383" s="12" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1384" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1384" s="12" t="s">
+        <v>2491</v>
+      </c>
+      <c r="C1384" s="12" t="s">
+        <v>2492</v>
+      </c>
+      <c r="D1384" s="12" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1385" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1385" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1385" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1385" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1386" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1386" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1386" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1386" s="12" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1387" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1387" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="C1387" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="D1387" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1388" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1388" s="12" t="s">
+        <v>2499</v>
+      </c>
+      <c r="C1388" s="12" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D1388" s="12" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1389" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1389" s="12" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C1389" s="12" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D1389" s="12" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1390" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1390" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1390" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="D1390" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1391" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1391" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1391" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="D1391" s="12" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1392" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1392" s="12" t="s">
+        <v>2505</v>
+      </c>
+      <c r="C1392" s="12" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D1392" s="12" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1393" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1393" s="12" t="s">
+        <v>2508</v>
+      </c>
+      <c r="C1393" s="12" t="s">
+        <v>2509</v>
+      </c>
+      <c r="D1393" s="12" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1394" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1394" s="12" t="s">
+        <v>2511</v>
+      </c>
+      <c r="C1394" s="12" t="s">
+        <v>2512</v>
+      </c>
+      <c r="D1394" s="12" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1395" s="1">
+        <v>21</v>
+      </c>
+      <c r="B1395" s="12" t="s">
+        <v>2514</v>
+      </c>
+      <c r="C1395" s="12" t="s">
+        <v>2515</v>
+      </c>
+      <c r="D1395" s="12" t="s">
+        <v>2516</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/kotoba_mokuzai.xlsx
+++ b/public/kotoba_mokuzai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\mokuzai_flashcard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263A5C2A-6175-41CD-A980-F96E49F943F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84205073-6064-48EB-9A8B-634C2A15C34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4186" uniqueCount="2517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5416" uniqueCount="3153">
   <si>
     <t>第１章</t>
   </si>
@@ -7571,6 +7571,1914 @@
   </si>
   <si>
     <t>homepage (situs web)</t>
+  </si>
+  <si>
+    <t>Laminated Veneer Lumber (kayu laminasi venir)</t>
+  </si>
+  <si>
+    <t>venir (lembaran kayu tipis)</t>
+  </si>
+  <si>
+    <t>数層</t>
+  </si>
+  <si>
+    <t>すうそう</t>
+  </si>
+  <si>
+    <t>beberapa lapisan</t>
+  </si>
+  <si>
+    <t>数十層</t>
+  </si>
+  <si>
+    <t>すうじゅうそう</t>
+  </si>
+  <si>
+    <t>puluhan lapisan</t>
+  </si>
+  <si>
+    <t>menumpuk, melapiskan</t>
+  </si>
+  <si>
+    <t>厚い</t>
+  </si>
+  <si>
+    <t>あつい</t>
+  </si>
+  <si>
+    <t>tebal</t>
+  </si>
+  <si>
+    <t>bahan struktural memanjang (material sumbu/kerangka)</t>
+  </si>
+  <si>
+    <t>tingkat kebebasan/fleksibilitas</t>
+  </si>
+  <si>
+    <t>lebar, luas</t>
+  </si>
+  <si>
+    <t>生産</t>
+  </si>
+  <si>
+    <t>せいさん</t>
+  </si>
+  <si>
+    <t>karakteristik, ciri khas</t>
+  </si>
+  <si>
+    <t>JAS</t>
+  </si>
+  <si>
+    <t>Japanese Agricultural Standards</t>
+  </si>
+  <si>
+    <t>penggunaan, aplikasi</t>
+  </si>
+  <si>
+    <t>構造用単板積層材</t>
+  </si>
+  <si>
+    <t>こうぞうようたんぱんせきそうざい</t>
+  </si>
+  <si>
+    <t>LVL untuk keperluan struktur</t>
+  </si>
+  <si>
+    <t>造作用単板積層材</t>
+  </si>
+  <si>
+    <t>ぞうさくようたんぱんせきそうざい</t>
+  </si>
+  <si>
+    <t>LVL untuk keperluan interior/pekerjaan finishing</t>
+  </si>
+  <si>
+    <t>struktur/bangunan</t>
+  </si>
+  <si>
+    <t>直交する</t>
+  </si>
+  <si>
+    <t>ちょっこうする</t>
+  </si>
+  <si>
+    <t>saling tegak lurus</t>
+  </si>
+  <si>
+    <t>入れる</t>
+  </si>
+  <si>
+    <t>いれる</t>
+  </si>
+  <si>
+    <t>memasukkan</t>
+  </si>
+  <si>
+    <t>最外層</t>
+  </si>
+  <si>
+    <t>さいがいそう</t>
+  </si>
+  <si>
+    <t>lapisan paling luar</t>
+  </si>
+  <si>
+    <t>層目</t>
+  </si>
+  <si>
+    <t>そうめ</t>
+  </si>
+  <si>
+    <t>lapisan ke-...</t>
+  </si>
+  <si>
+    <t>A種構造用単板積層材</t>
+  </si>
+  <si>
+    <t>エーしゅこうぞうようたんぱんせきそうざい</t>
+  </si>
+  <si>
+    <t>LVL struktural tipe A</t>
+  </si>
+  <si>
+    <t>以外</t>
+  </si>
+  <si>
+    <t>いがい</t>
+  </si>
+  <si>
+    <t>selain, selain itu</t>
+  </si>
+  <si>
+    <t>B種構造用単板積層材</t>
+  </si>
+  <si>
+    <t>ビーしゅこうぞうようたんぱんせきそうざい</t>
+  </si>
+  <si>
+    <t>LVL struktural tipe B</t>
+  </si>
+  <si>
+    <t>一社</t>
+  </si>
+  <si>
+    <t>いっしゃ</t>
+  </si>
+  <si>
+    <t>singkatan dari 一般社団法人 (asosiasi berbadan hukum)</t>
+  </si>
+  <si>
+    <t>seluruh Jepang</t>
+  </si>
+  <si>
+    <t>協会</t>
+  </si>
+  <si>
+    <t>きょうかい</t>
+  </si>
+  <si>
+    <t>asosiasi</t>
+  </si>
+  <si>
+    <t>入れ方</t>
+  </si>
+  <si>
+    <t>いれかた</t>
+  </si>
+  <si>
+    <t>cara memasukkan, cara penyusunan</t>
+  </si>
+  <si>
+    <t>細かい</t>
+  </si>
+  <si>
+    <t>こまかい</t>
+  </si>
+  <si>
+    <t>rinci, detail</t>
+  </si>
+  <si>
+    <t>menetapkan, menentukan</t>
+  </si>
+  <si>
+    <t>面材</t>
+  </si>
+  <si>
+    <t>めんざい</t>
+  </si>
+  <si>
+    <t>material lembaran/panel</t>
+  </si>
+  <si>
+    <t>利用する</t>
+  </si>
+  <si>
+    <t>りようする</t>
+  </si>
+  <si>
+    <t>memanfaatkan, menggunakan</t>
+  </si>
+  <si>
+    <t>gambar</t>
+  </si>
+  <si>
+    <t>丸森保育園</t>
+  </si>
+  <si>
+    <t>まるもりほいくえん</t>
+  </si>
+  <si>
+    <t>TK Marumori</t>
+  </si>
+  <si>
+    <t>トラス</t>
+  </si>
+  <si>
+    <t>truss (rangka batang)</t>
+  </si>
+  <si>
+    <t>小菅村体育館</t>
+  </si>
+  <si>
+    <t>こすげむらたいいくかん</t>
+  </si>
+  <si>
+    <t>Gedung olahraga Desa Kosuge</t>
+  </si>
+  <si>
+    <t>LVL untuk pekerjaan interior/finishing</t>
+  </si>
+  <si>
+    <t>非構造用</t>
+  </si>
+  <si>
+    <t>ひこうぞうよう</t>
+  </si>
+  <si>
+    <t>non-struktural</t>
+  </si>
+  <si>
+    <t>建具</t>
+  </si>
+  <si>
+    <t>たてぐ</t>
+  </si>
+  <si>
+    <t>kusen, pintu, jendela, perlengkapan bangunan dari kayu</t>
+  </si>
+  <si>
+    <t>基材</t>
+  </si>
+  <si>
+    <t>きざい</t>
+  </si>
+  <si>
+    <t>bahan dasar, material dasar</t>
+  </si>
+  <si>
+    <t>pekerjaan interior bagian dalam</t>
+  </si>
+  <si>
+    <t>展示</t>
+  </si>
+  <si>
+    <t>てんじ</t>
+  </si>
+  <si>
+    <t>pameran</t>
+  </si>
+  <si>
+    <t>ブース</t>
+  </si>
+  <si>
+    <t>booth, stan</t>
+  </si>
+  <si>
+    <t>積層面</t>
+  </si>
+  <si>
+    <t>せきそうめん</t>
+  </si>
+  <si>
+    <t>permukaan laminasi</t>
+  </si>
+  <si>
+    <t>Bしゅこうぞうようたんぱんせきそうざい</t>
+  </si>
+  <si>
+    <t>ツキ板</t>
+  </si>
+  <si>
+    <t>ツキいた</t>
+  </si>
+  <si>
+    <t>veneer dekoratif (lembaran venir untuk finishing)</t>
+  </si>
+  <si>
+    <t>kusen, pintu, jendela, perlengkapan bangunan</t>
+  </si>
+  <si>
+    <t>建築内装</t>
+  </si>
+  <si>
+    <t>けんちくないそう</t>
+  </si>
+  <si>
+    <t>interior bangunan</t>
+  </si>
+  <si>
+    <t>表面装飾</t>
+  </si>
+  <si>
+    <t>ひょうめんそうしょく</t>
+  </si>
+  <si>
+    <t>dekorasi permukaan</t>
+  </si>
+  <si>
+    <t>化粧用</t>
+  </si>
+  <si>
+    <t>けしょうよう</t>
+  </si>
+  <si>
+    <t>untuk finishing/dekoratif</t>
+  </si>
+  <si>
+    <t>用いる</t>
+  </si>
+  <si>
+    <t>もちいる</t>
+  </si>
+  <si>
+    <t>menggunakan (formal)</t>
+  </si>
+  <si>
+    <t>化粧単板</t>
+  </si>
+  <si>
+    <t>けしょうたんぱん</t>
+  </si>
+  <si>
+    <t>venir dekoratif</t>
+  </si>
+  <si>
+    <t>bahan, material</t>
+  </si>
+  <si>
+    <t>melaminasi, merekatkan dua atau lebih material</t>
+  </si>
+  <si>
+    <t>完成する</t>
+  </si>
+  <si>
+    <t>かんせいする</t>
+  </si>
+  <si>
+    <t>selesai, menjadi produk jadi</t>
+  </si>
+  <si>
+    <t>応じる</t>
+  </si>
+  <si>
+    <t>おうじる</t>
+  </si>
+  <si>
+    <t>menyesuaikan dengan</t>
+  </si>
+  <si>
+    <t>木質材料</t>
+  </si>
+  <si>
+    <t>もくしつざいりょう</t>
+  </si>
+  <si>
+    <t>material berbahan kayu</t>
+  </si>
+  <si>
+    <t>ラワン合板</t>
+  </si>
+  <si>
+    <t>ラワンごうはん</t>
+  </si>
+  <si>
+    <t>plywood lauan</t>
+  </si>
+  <si>
+    <t>MDF</t>
+  </si>
+  <si>
+    <t>Medium Density Fiberboard</t>
+  </si>
+  <si>
+    <t>パーティクルボード</t>
+  </si>
+  <si>
+    <t>particle board</t>
+  </si>
+  <si>
+    <t>表面平滑性</t>
+  </si>
+  <si>
+    <t>ひょうめんへいかつせい</t>
+  </si>
+  <si>
+    <t>kehalusan permukaan</t>
+  </si>
+  <si>
+    <t>yang lain</t>
+  </si>
+  <si>
+    <t>古くから</t>
+  </si>
+  <si>
+    <t>ふるくから</t>
+  </si>
+  <si>
+    <t>sejak dahulu</t>
+  </si>
+  <si>
+    <t>一般内装</t>
+  </si>
+  <si>
+    <t>いっぱんないそう</t>
+  </si>
+  <si>
+    <t>interior umum</t>
+  </si>
+  <si>
+    <t>金属板</t>
+  </si>
+  <si>
+    <t>きんぞくばん</t>
+  </si>
+  <si>
+    <t>pelat logam</t>
+  </si>
+  <si>
+    <t>繊維質</t>
+  </si>
+  <si>
+    <t>せんいしつ</t>
+  </si>
+  <si>
+    <t>berserat</t>
+  </si>
+  <si>
+    <t>シート</t>
+  </si>
+  <si>
+    <t>lembaran (sheet)</t>
+  </si>
+  <si>
+    <t>挟む</t>
+  </si>
+  <si>
+    <t>はさむ</t>
+  </si>
+  <si>
+    <t>menyisipkan, menjepit</t>
+  </si>
+  <si>
+    <t>特殊</t>
+  </si>
+  <si>
+    <t>とくしゅ</t>
+  </si>
+  <si>
+    <t>khusus</t>
+  </si>
+  <si>
+    <t>接着剤</t>
+  </si>
+  <si>
+    <t>せっちゃくざい</t>
+  </si>
+  <si>
+    <t>perekat</t>
+  </si>
+  <si>
+    <t>接着する</t>
+  </si>
+  <si>
+    <t>せっちゃくする</t>
+  </si>
+  <si>
+    <t>merekatkan</t>
+  </si>
+  <si>
+    <t>形状安定性</t>
+  </si>
+  <si>
+    <t>けいじょうあんていせい</t>
+  </si>
+  <si>
+    <t>kestabilan bentuk</t>
+  </si>
+  <si>
+    <t>成形性</t>
+  </si>
+  <si>
+    <t>せいけいせい</t>
+  </si>
+  <si>
+    <t>kemudahan dibentuk (formability)</t>
+  </si>
+  <si>
+    <t>優れる</t>
+  </si>
+  <si>
+    <t>すぐれる</t>
+  </si>
+  <si>
+    <t>unggul, sangat baik</t>
+  </si>
+  <si>
+    <t>一部</t>
+  </si>
+  <si>
+    <t>いちぶ</t>
+  </si>
+  <si>
+    <t>sebagian</t>
+  </si>
+  <si>
+    <t>不燃性</t>
+  </si>
+  <si>
+    <t>ふねんせい</t>
+  </si>
+  <si>
+    <t>sifat tidak mudah terbakar</t>
+  </si>
+  <si>
+    <t>燃える</t>
+  </si>
+  <si>
+    <t>もえる</t>
+  </si>
+  <si>
+    <t>terbakar</t>
+  </si>
+  <si>
+    <t>内装材</t>
+  </si>
+  <si>
+    <t>ないそうざい</t>
+  </si>
+  <si>
+    <t>bahan interior</t>
+  </si>
+  <si>
+    <t>エレベーター</t>
+  </si>
+  <si>
+    <t>lift</t>
+  </si>
+  <si>
+    <t>鉄道車両</t>
+  </si>
+  <si>
+    <t>てつどうしゃりょう</t>
+  </si>
+  <si>
+    <t>gerbong/kereta api</t>
+  </si>
+  <si>
+    <t>ガラス</t>
+  </si>
+  <si>
+    <t>kaca</t>
+  </si>
+  <si>
+    <t>板ガラス</t>
+  </si>
+  <si>
+    <t>いたガラス</t>
+  </si>
+  <si>
+    <t>kaca lembaran (flat glass)</t>
+  </si>
+  <si>
+    <t>覆う</t>
+  </si>
+  <si>
+    <t>おおう</t>
+  </si>
+  <si>
+    <t>menutupi, melapisi</t>
+  </si>
+  <si>
+    <t>serat/pola kayu</t>
+  </si>
+  <si>
+    <t>鮮明</t>
+  </si>
+  <si>
+    <t>せんめい</t>
+  </si>
+  <si>
+    <t>jelas, tajam</t>
+  </si>
+  <si>
+    <t>表現する</t>
+  </si>
+  <si>
+    <t>ひょうげんする</t>
+  </si>
+  <si>
+    <t>menampilkan, mengekspresikan</t>
+  </si>
+  <si>
+    <t>透光性</t>
+  </si>
+  <si>
+    <t>とうこうせい</t>
+  </si>
+  <si>
+    <t>sifat tembus cahaya</t>
+  </si>
+  <si>
+    <t>耐久性</t>
+  </si>
+  <si>
+    <t>たいきゅうせい</t>
+  </si>
+  <si>
+    <t>daya tahan, ketahanan</t>
+  </si>
+  <si>
+    <t>内装壁面</t>
+  </si>
+  <si>
+    <t>ないそうへきめん</t>
+  </si>
+  <si>
+    <t>dinding interior</t>
+  </si>
+  <si>
+    <t>照明器具</t>
+  </si>
+  <si>
+    <t>しょうめいきぐ</t>
+  </si>
+  <si>
+    <t>peralatan penerangan, lampu</t>
+  </si>
+  <si>
+    <t>不織布</t>
+  </si>
+  <si>
+    <t>ふしょくふ</t>
+  </si>
+  <si>
+    <t>kain nonwoven (kain tanpa tenun)</t>
+  </si>
+  <si>
+    <t>和紙</t>
+  </si>
+  <si>
+    <t>わし</t>
+  </si>
+  <si>
+    <t>kertas tradisional Jepang</t>
+  </si>
+  <si>
+    <t>上がる</t>
+  </si>
+  <si>
+    <t>あがる</t>
+  </si>
+  <si>
+    <t>meningkat</t>
+  </si>
+  <si>
+    <t>破れる</t>
+  </si>
+  <si>
+    <t>やぶれる</t>
+  </si>
+  <si>
+    <t>robek</t>
+  </si>
+  <si>
+    <t>裂ける</t>
+  </si>
+  <si>
+    <t>さける</t>
+  </si>
+  <si>
+    <t>sobek, terbelah</t>
+  </si>
+  <si>
+    <t>material</t>
+  </si>
+  <si>
+    <t>後から</t>
+  </si>
+  <si>
+    <t>あとから</t>
+  </si>
+  <si>
+    <t>setelahnya</t>
+  </si>
+  <si>
+    <t>柔軟性</t>
+  </si>
+  <si>
+    <t>じゅうなんせい</t>
+  </si>
+  <si>
+    <t>fleksibilitas</t>
+  </si>
+  <si>
+    <t>曲面加工</t>
+  </si>
+  <si>
+    <t>きょくめんかこう</t>
+  </si>
+  <si>
+    <t>pemrosesan permukaan lengkung</t>
+  </si>
+  <si>
+    <t>適する</t>
+  </si>
+  <si>
+    <t>てきする</t>
+  </si>
+  <si>
+    <t>cocok untuk</t>
+  </si>
+  <si>
+    <t>住宅部材</t>
+  </si>
+  <si>
+    <t>じゅうたくぶざい</t>
+  </si>
+  <si>
+    <t>komponen rumah</t>
+  </si>
+  <si>
+    <t>装飾品</t>
+  </si>
+  <si>
+    <t>そうしょくひん</t>
+  </si>
+  <si>
+    <t>barang dekorasi</t>
+  </si>
+  <si>
+    <t>自動車</t>
+  </si>
+  <si>
+    <t>じどうしゃ</t>
+  </si>
+  <si>
+    <t>mobil</t>
+  </si>
+  <si>
+    <t>不燃板</t>
+  </si>
+  <si>
+    <t>ふねんばん</t>
+  </si>
+  <si>
+    <t>papan tahan api</t>
+  </si>
+  <si>
+    <t>火山性ガラス質複層板</t>
+  </si>
+  <si>
+    <t>かざんせいガラスしつふくそうばん</t>
+  </si>
+  <si>
+    <t>papan berlapis berbahan kaca vulkanik</t>
+  </si>
+  <si>
+    <t>繊維強化セメント板</t>
+  </si>
+  <si>
+    <t>せんいきょうかセメントばん</t>
+  </si>
+  <si>
+    <t>papan semen diperkuat serat (fiber reinforced cement board)</t>
+  </si>
+  <si>
+    <t>material dasar</t>
+  </si>
+  <si>
+    <t>建築基準法</t>
+  </si>
+  <si>
+    <t>けんちくきじゅんほう</t>
+  </si>
+  <si>
+    <t>Undang-Undang Standar Bangunan Jepang</t>
+  </si>
+  <si>
+    <t>内装制限</t>
+  </si>
+  <si>
+    <t>ないそうせいげん</t>
+  </si>
+  <si>
+    <t>pembatasan interior</t>
+  </si>
+  <si>
+    <t>空間</t>
+  </si>
+  <si>
+    <t>くうかん</t>
+  </si>
+  <si>
+    <t>ruang</t>
+  </si>
+  <si>
+    <t>フローリング</t>
+  </si>
+  <si>
+    <t>lantai kayu (flooring)</t>
+  </si>
+  <si>
+    <t>単層</t>
+  </si>
+  <si>
+    <t>たんそう</t>
+  </si>
+  <si>
+    <t>satu lapis</t>
+  </si>
+  <si>
+    <t>複合</t>
+  </si>
+  <si>
+    <t>ふくごう</t>
+  </si>
+  <si>
+    <t>komposit, gabungan</t>
+  </si>
+  <si>
+    <t>papan kayu hasil gergajian (sawn board)</t>
+  </si>
+  <si>
+    <t>構成層</t>
+  </si>
+  <si>
+    <t>こうせいそう</t>
+  </si>
+  <si>
+    <t>lapisan penyusun</t>
+  </si>
+  <si>
+    <t>selain</t>
+  </si>
+  <si>
+    <t>単層フローリング</t>
+  </si>
+  <si>
+    <t>たんそうフローリング</t>
+  </si>
+  <si>
+    <t>flooring satu lapis</t>
+  </si>
+  <si>
+    <t>経年使用</t>
+  </si>
+  <si>
+    <t>けいねんしよう</t>
+  </si>
+  <si>
+    <t>penggunaan dalam jangka waktu lama</t>
+  </si>
+  <si>
+    <t>劣化</t>
+  </si>
+  <si>
+    <t>れっか</t>
+  </si>
+  <si>
+    <t>penurunan kualitas, degradasi</t>
+  </si>
+  <si>
+    <t>研磨する</t>
+  </si>
+  <si>
+    <t>けんまする</t>
+  </si>
+  <si>
+    <t>mengamplas, memoles</t>
+  </si>
+  <si>
+    <t>再塗装</t>
+  </si>
+  <si>
+    <t>さいとそう</t>
+  </si>
+  <si>
+    <t>pengecatan ulang</t>
+  </si>
+  <si>
+    <t>長期的</t>
+  </si>
+  <si>
+    <t>ちょうきてき</t>
+  </si>
+  <si>
+    <t>jangka panjang</t>
+  </si>
+  <si>
+    <t>使用する</t>
+  </si>
+  <si>
+    <t>しようする</t>
+  </si>
+  <si>
+    <t>学校</t>
+  </si>
+  <si>
+    <t>がっこう</t>
+  </si>
+  <si>
+    <t>sekolah</t>
+  </si>
+  <si>
+    <t>文教施設</t>
+  </si>
+  <si>
+    <t>ぶんきょうしせつ</t>
+  </si>
+  <si>
+    <t>fasilitas pendidikan</t>
+  </si>
+  <si>
+    <t>利用例</t>
+  </si>
+  <si>
+    <t>りようれい</t>
+  </si>
+  <si>
+    <t>singkatan dari 一般社団法人</t>
+  </si>
+  <si>
+    <t>工業会</t>
+  </si>
+  <si>
+    <t>こうぎょうかい</t>
+  </si>
+  <si>
+    <t>asosiasi industri</t>
+  </si>
+  <si>
+    <t>ガイド</t>
+  </si>
+  <si>
+    <t>panduan</t>
+  </si>
+  <si>
+    <t>フローリングボード</t>
+  </si>
+  <si>
+    <t>flooring board</t>
+  </si>
+  <si>
+    <t>枚</t>
+  </si>
+  <si>
+    <t>まい</t>
+  </si>
+  <si>
+    <t>lembar (counter)</t>
+  </si>
+  <si>
+    <t>dua atau lebih / lebih dari</t>
+  </si>
+  <si>
+    <t>並べる</t>
+  </si>
+  <si>
+    <t>ならべる</t>
+  </si>
+  <si>
+    <t>menyusun berjajar</t>
+  </si>
+  <si>
+    <t>接合する</t>
+  </si>
+  <si>
+    <t>せつごうする</t>
+  </si>
+  <si>
+    <t>menyambung, menggabungkan</t>
+  </si>
+  <si>
+    <t>フローリングブロック</t>
+  </si>
+  <si>
+    <t>flooring block</t>
+  </si>
+  <si>
+    <t>最長辺</t>
+  </si>
+  <si>
+    <t>さいちょうへん</t>
+  </si>
+  <si>
+    <t>sisi terpanjang</t>
+  </si>
+  <si>
+    <t>kurang dari atau sama dengan</t>
+  </si>
+  <si>
+    <t>小片</t>
+  </si>
+  <si>
+    <t>しょうへん</t>
+  </si>
+  <si>
+    <t>potongan kecil</t>
+  </si>
+  <si>
+    <t>個</t>
+  </si>
+  <si>
+    <t>こ</t>
+  </si>
+  <si>
+    <t>buah (counter)</t>
+  </si>
+  <si>
+    <t>紙</t>
+  </si>
+  <si>
+    <t>かみ</t>
+  </si>
+  <si>
+    <t>kertas</t>
+  </si>
+  <si>
+    <t>組み合わせる</t>
+  </si>
+  <si>
+    <t>くみあわせる</t>
+  </si>
+  <si>
+    <t>menggabungkan, menyusun</t>
+  </si>
+  <si>
+    <t>モザイクパーケット</t>
+  </si>
+  <si>
+    <t>mosaic parquet</t>
+  </si>
+  <si>
+    <t>複合フローリング</t>
+  </si>
+  <si>
+    <t>ふくごうフローリング</t>
+  </si>
+  <si>
+    <t>lantai kayu komposit</t>
+  </si>
+  <si>
+    <t>lantai kayu satu lapis</t>
+  </si>
+  <si>
+    <t>化粧材</t>
+  </si>
+  <si>
+    <t>けしょうざい</t>
+  </si>
+  <si>
+    <t>bahan pelapis dekoratif</t>
+  </si>
+  <si>
+    <t>組み合わせ</t>
+  </si>
+  <si>
+    <t>くみあわせ</t>
+  </si>
+  <si>
+    <t>kombinasi</t>
+  </si>
+  <si>
+    <t>販売する</t>
+  </si>
+  <si>
+    <t>はんばいする</t>
+  </si>
+  <si>
+    <t>menjual, memasarkan</t>
+  </si>
+  <si>
+    <t>生産する</t>
+  </si>
+  <si>
+    <t>せいさんする</t>
+  </si>
+  <si>
+    <t>memproduksi</t>
+  </si>
+  <si>
+    <t>貼る</t>
+  </si>
+  <si>
+    <t>上</t>
+  </si>
+  <si>
+    <t>atas</t>
+  </si>
+  <si>
+    <t>天然木</t>
+  </si>
+  <si>
+    <t>てんねんぼく</t>
+  </si>
+  <si>
+    <t>kayu alami</t>
+  </si>
+  <si>
+    <t>オレフィンシート</t>
+  </si>
+  <si>
+    <t>lembaran olefin (olefin sheet)</t>
+  </si>
+  <si>
+    <t>表面化粧</t>
+  </si>
+  <si>
+    <t>ひょうめんけしょう</t>
+  </si>
+  <si>
+    <t>finishing/dekorasi permukaan</t>
+  </si>
+  <si>
+    <t>kadar air, kelembapan</t>
+  </si>
+  <si>
+    <t>変形</t>
+  </si>
+  <si>
+    <t>へんけい</t>
+  </si>
+  <si>
+    <t>deformasi, perubahan bentuk</t>
+  </si>
+  <si>
+    <t>価格</t>
+  </si>
+  <si>
+    <t>かかく</t>
+  </si>
+  <si>
+    <t>harga</t>
+  </si>
+  <si>
+    <t>安い</t>
+  </si>
+  <si>
+    <t>やすい</t>
+  </si>
+  <si>
+    <t>murah</t>
+  </si>
+  <si>
+    <t>マンション</t>
+  </si>
+  <si>
+    <t>apartemen</t>
+  </si>
+  <si>
+    <t>オフィス</t>
+  </si>
+  <si>
+    <t>kantor</t>
+  </si>
+  <si>
+    <t>針葉樹合板</t>
+  </si>
+  <si>
+    <t>しんようじゅごうはん</t>
+  </si>
+  <si>
+    <t>plywood dari kayu jenis konifer</t>
+  </si>
+  <si>
+    <t>チップ</t>
+  </si>
+  <si>
+    <t>出る</t>
+  </si>
+  <si>
+    <t>でる</t>
+  </si>
+  <si>
+    <t>keluar, dihasilkan</t>
+  </si>
+  <si>
+    <t>sisa kayu di area hutan (logging residue)</t>
+  </si>
+  <si>
+    <t>製紙用</t>
+  </si>
+  <si>
+    <t>せいしよう</t>
+  </si>
+  <si>
+    <t>untuk pembuatan kertas</t>
+  </si>
+  <si>
+    <t>燃料用</t>
+  </si>
+  <si>
+    <t>ねんりょうよう</t>
+  </si>
+  <si>
+    <t>untuk bahan bakar</t>
+  </si>
+  <si>
+    <t>家屋</t>
+  </si>
+  <si>
+    <t>かおく</t>
+  </si>
+  <si>
+    <t>rumah/bangunan</t>
+  </si>
+  <si>
+    <t>kayu hasil pembongkaran bangunan</t>
+  </si>
+  <si>
+    <t>limbah kayu</t>
+  </si>
+  <si>
+    <t>ボイラー</t>
+  </si>
+  <si>
+    <t>boiler</t>
+  </si>
+  <si>
+    <t>燃料</t>
+  </si>
+  <si>
+    <t>ねんりょう</t>
+  </si>
+  <si>
+    <t>bahan bakar</t>
+  </si>
+  <si>
+    <t>木質ボード</t>
+  </si>
+  <si>
+    <t>もくしつボード</t>
+  </si>
+  <si>
+    <t>papan berbahan kayu</t>
+  </si>
+  <si>
+    <t>製紙工場</t>
+  </si>
+  <si>
+    <t>せいしこうじょう</t>
+  </si>
+  <si>
+    <t>pabrik kertas</t>
+  </si>
+  <si>
+    <t>パルプ</t>
+  </si>
+  <si>
+    <t>pulp</t>
+  </si>
+  <si>
+    <t>ボード用原料</t>
+  </si>
+  <si>
+    <t>ボードようげんりょう</t>
+  </si>
+  <si>
+    <t>bahan baku untuk papan</t>
+  </si>
+  <si>
+    <t>木質ボード工場</t>
+  </si>
+  <si>
+    <t>もくしつボードこうじょう</t>
+  </si>
+  <si>
+    <t>pabrik papan berbahan kayu</t>
+  </si>
+  <si>
+    <t>繊維板</t>
+  </si>
+  <si>
+    <t>せんいばん</t>
+  </si>
+  <si>
+    <t>papan serat (fiberboard)</t>
+  </si>
+  <si>
+    <t>もくしつバイオマス</t>
+  </si>
+  <si>
+    <t>biomassa kayu</t>
+  </si>
+  <si>
+    <t>発電所</t>
+  </si>
+  <si>
+    <t>はつでんしょ</t>
+  </si>
+  <si>
+    <t>pembangkit listrik</t>
+  </si>
+  <si>
+    <t>再生可能エネルギー</t>
+  </si>
+  <si>
+    <t>さいせいかのうエネルギー</t>
+  </si>
+  <si>
+    <t>energi terbarukan</t>
+  </si>
+  <si>
+    <t>稼働</t>
+  </si>
+  <si>
+    <t>かどう</t>
+  </si>
+  <si>
+    <t>増加する</t>
+  </si>
+  <si>
+    <t>ぞうかする</t>
+  </si>
+  <si>
+    <t>需要</t>
+  </si>
+  <si>
+    <t>じゅよう</t>
+  </si>
+  <si>
+    <t>permintaan</t>
+  </si>
+  <si>
+    <t>地面</t>
+  </si>
+  <si>
+    <t>じめん</t>
+  </si>
+  <si>
+    <t>permukaan tanah</t>
+  </si>
+  <si>
+    <t>敷く</t>
+  </si>
+  <si>
+    <t>しく</t>
+  </si>
+  <si>
+    <t>menghamparkan, menggelar</t>
+  </si>
+  <si>
+    <t>優れた</t>
+  </si>
+  <si>
+    <t>すぐれた</t>
+  </si>
+  <si>
+    <t>クッション性</t>
+  </si>
+  <si>
+    <t>クッションせい</t>
+  </si>
+  <si>
+    <t>sifat peredam/bantalan</t>
+  </si>
+  <si>
+    <t>得られる</t>
+  </si>
+  <si>
+    <t>えられる</t>
+  </si>
+  <si>
+    <t>diperoleh</t>
+  </si>
+  <si>
+    <t>ガーデニング</t>
+  </si>
+  <si>
+    <t>berkebun (gardening)</t>
+  </si>
+  <si>
+    <t>マルチ材</t>
+  </si>
+  <si>
+    <t>マルチざい</t>
+  </si>
+  <si>
+    <t>bahan mulsa</t>
+  </si>
+  <si>
+    <t>公園</t>
+  </si>
+  <si>
+    <t>こうえん</t>
+  </si>
+  <si>
+    <t>taman</t>
+  </si>
+  <si>
+    <t>遊歩道</t>
+  </si>
+  <si>
+    <t>ゆうほどう</t>
+  </si>
+  <si>
+    <t>jalur pejalan kaki</t>
+  </si>
+  <si>
+    <t>競走馬</t>
+  </si>
+  <si>
+    <t>きょうそうば</t>
+  </si>
+  <si>
+    <t>kuda pacu</t>
+  </si>
+  <si>
+    <t>トレーニングコース</t>
+  </si>
+  <si>
+    <t>lintasan latihan</t>
+  </si>
+  <si>
+    <t>プレカット</t>
+  </si>
+  <si>
+    <t>precut (pemotongan dan pemrosesan kayu di pabrik sebelum dikirim ke lokasi konstruksi)</t>
+  </si>
+  <si>
+    <t>設計情報</t>
+  </si>
+  <si>
+    <t>せっけいじょうほう</t>
+  </si>
+  <si>
+    <t>informasi/desain perancangan</t>
+  </si>
+  <si>
+    <t>加工情報</t>
+  </si>
+  <si>
+    <t>かこうじょうほう</t>
+  </si>
+  <si>
+    <t>informasi pemrosesan</t>
+  </si>
+  <si>
+    <t>変換する</t>
+  </si>
+  <si>
+    <t>へんかんする</t>
+  </si>
+  <si>
+    <t>mengubah, mengonversi</t>
+  </si>
+  <si>
+    <t>コンピュータ</t>
+  </si>
+  <si>
+    <t>komputer</t>
+  </si>
+  <si>
+    <t>制御する</t>
+  </si>
+  <si>
+    <t>せいぎょする</t>
+  </si>
+  <si>
+    <t>mengendalikan, mengontrol</t>
+  </si>
+  <si>
+    <t>加工する</t>
+  </si>
+  <si>
+    <t>かこうする</t>
+  </si>
+  <si>
+    <t>memproses, mengolah</t>
+  </si>
+  <si>
+    <t>持って行く</t>
+  </si>
+  <si>
+    <t>もっていく</t>
+  </si>
+  <si>
+    <t>membawa</t>
+  </si>
+  <si>
+    <t>高精度</t>
+  </si>
+  <si>
+    <t>こうせいど</t>
+  </si>
+  <si>
+    <t>presisi tinggi</t>
+  </si>
+  <si>
+    <t>高品質</t>
+  </si>
+  <si>
+    <t>こうひんしつ</t>
+  </si>
+  <si>
+    <t>kualitas tinggi</t>
+  </si>
+  <si>
+    <t>安定して</t>
+  </si>
+  <si>
+    <t>あんていして</t>
+  </si>
+  <si>
+    <t>secara stabil</t>
+  </si>
+  <si>
+    <t>工期</t>
+  </si>
+  <si>
+    <t>こうき</t>
+  </si>
+  <si>
+    <t>masa/waktu pelaksanaan konstruksi</t>
+  </si>
+  <si>
+    <t>短い</t>
+  </si>
+  <si>
+    <t>みじかい</t>
+  </si>
+  <si>
+    <t>pendek</t>
+  </si>
+  <si>
+    <t>木くず</t>
+  </si>
+  <si>
+    <t>きくず</t>
+  </si>
+  <si>
+    <t>serbuk/serpihan kayu</t>
+  </si>
+  <si>
+    <t>ゴミ</t>
+  </si>
+  <si>
+    <t>sampah</t>
+  </si>
+  <si>
+    <t>timbul, dihasilkan</t>
+  </si>
+  <si>
+    <t>減らせる</t>
+  </si>
+  <si>
+    <t>へらせる</t>
+  </si>
+  <si>
+    <t>dapat mengurangi</t>
+  </si>
+  <si>
+    <t>メリット</t>
+  </si>
+  <si>
+    <t>keuntungan, manfaat</t>
+  </si>
+  <si>
+    <t>penyebaran, penggunaan secara luas</t>
+  </si>
+  <si>
+    <t>material precut</t>
+  </si>
+  <si>
+    <t>組み上げる</t>
+  </si>
+  <si>
+    <t>くみあげる</t>
+  </si>
+  <si>
+    <t>merakit, menyusun hingga selesai</t>
+  </si>
+  <si>
+    <t>rumah konstruksi kayu</t>
+  </si>
+  <si>
+    <t>各製品</t>
+  </si>
+  <si>
+    <t>かくせいひん</t>
+  </si>
+  <si>
+    <t>setiap produk</t>
+  </si>
+  <si>
+    <t>製造工程</t>
+  </si>
+  <si>
+    <t>せいぞうこうてい</t>
+  </si>
+  <si>
+    <t>proses manufaktur</t>
+  </si>
+  <si>
+    <t>penggergajian kayu / lumber processing</t>
+  </si>
+  <si>
+    <t>工程</t>
+  </si>
+  <si>
+    <t>こうてい</t>
+  </si>
+  <si>
+    <t>proses, tahapan</t>
+  </si>
+  <si>
+    <t>pabrik penggergajian</t>
+  </si>
+  <si>
+    <t>規模</t>
+  </si>
+  <si>
+    <t>きぼ</t>
+  </si>
+  <si>
+    <t>skala</t>
+  </si>
+  <si>
+    <t>大きく</t>
+  </si>
+  <si>
+    <t>おおきく</t>
+  </si>
+  <si>
+    <t>secara besar</t>
+  </si>
+  <si>
+    <t>はく皮</t>
+  </si>
+  <si>
+    <t>はくひ</t>
+  </si>
+  <si>
+    <t>pengupasan kulit kayu (debarking)</t>
+  </si>
+  <si>
+    <t>menghilangkan, membuang</t>
+  </si>
+  <si>
+    <t>土砂</t>
+  </si>
+  <si>
+    <t>どしゃ</t>
+  </si>
+  <si>
+    <t>tanah dan pasir</t>
+  </si>
+  <si>
+    <t>鋸歯</t>
+  </si>
+  <si>
+    <t>のこば</t>
+  </si>
+  <si>
+    <t>傷む</t>
+  </si>
+  <si>
+    <t>いたむ</t>
+  </si>
+  <si>
+    <t>rusak, aus</t>
+  </si>
+  <si>
+    <t>mencegah</t>
+  </si>
+  <si>
+    <t>木取り</t>
+  </si>
+  <si>
+    <t>きどり</t>
+  </si>
+  <si>
+    <t>penentuan pola pemotongan kayu</t>
+  </si>
+  <si>
+    <t>易い</t>
+  </si>
+  <si>
+    <t>mudah</t>
+  </si>
+  <si>
+    <t>残材</t>
+  </si>
+  <si>
+    <t>ざんざい</t>
+  </si>
+  <si>
+    <t>sisa material</t>
+  </si>
+  <si>
+    <t>混ざる</t>
+  </si>
+  <si>
+    <t>まざる</t>
+  </si>
+  <si>
+    <t>bercampur</t>
+  </si>
+  <si>
+    <t>バーカ</t>
+  </si>
+  <si>
+    <t>barker (mesin pengupas kulit kayu)</t>
+  </si>
+  <si>
+    <t>位置</t>
+  </si>
+  <si>
+    <t>いち</t>
+  </si>
+  <si>
+    <t>posisi</t>
+  </si>
+  <si>
+    <t>menggergaji, membelah kayu</t>
+  </si>
+  <si>
+    <t>決定する</t>
+  </si>
+  <si>
+    <t>けっていする</t>
+  </si>
+  <si>
+    <t>menentukan</t>
+  </si>
+  <si>
+    <t>従う</t>
+  </si>
+  <si>
+    <t>したがう</t>
+  </si>
+  <si>
+    <t>mengikuti</t>
+  </si>
+  <si>
+    <t>歩止り</t>
+  </si>
+  <si>
+    <t>ぶどまり</t>
+  </si>
+  <si>
+    <t>rendemen (yield produksi)</t>
+  </si>
+  <si>
+    <t>材積</t>
+  </si>
+  <si>
+    <t>ざいせき</t>
+  </si>
+  <si>
+    <t>volume kayu</t>
+  </si>
+  <si>
+    <t>persentase, rasio</t>
+  </si>
+  <si>
+    <t>pekerjaan, proses kerja</t>
+  </si>
+  <si>
+    <t>一つ</t>
+  </si>
+  <si>
+    <t>ひとつ</t>
+  </si>
+  <si>
+    <t>salah satu</t>
+  </si>
+  <si>
+    <t>径</t>
+  </si>
+  <si>
+    <t>けい</t>
+  </si>
+  <si>
+    <t>品質</t>
+  </si>
+  <si>
+    <t>ひんしつ</t>
+  </si>
+  <si>
+    <t>kualitas</t>
+  </si>
+  <si>
+    <t>要求される</t>
+  </si>
+  <si>
+    <t>ようきゅうされる</t>
+  </si>
+  <si>
+    <t>yang diminta/disyaratkan</t>
+  </si>
+  <si>
+    <t>考慮する</t>
+  </si>
+  <si>
+    <t>こうりょする</t>
+  </si>
+  <si>
+    <t>mempertimbangkan</t>
+  </si>
+  <si>
+    <t>metode</t>
+  </si>
+  <si>
+    <t>主要</t>
+  </si>
+  <si>
+    <t>しゅよう</t>
+  </si>
+  <si>
+    <t>半製品</t>
+  </si>
+  <si>
+    <t>はんせいひん</t>
+  </si>
+  <si>
+    <t>produk setengah jadi</t>
+  </si>
+  <si>
+    <t>仕掛材</t>
+  </si>
+  <si>
+    <t>しかかりざい</t>
+  </si>
+  <si>
+    <t>bahan setengah jadi (work-in-process)</t>
+  </si>
+  <si>
+    <t>大割り</t>
+  </si>
+  <si>
+    <t>おおわり</t>
+  </si>
+  <si>
+    <t>pemotongan awal (primary breakdown)</t>
+  </si>
+  <si>
+    <t>中割り</t>
+  </si>
+  <si>
+    <t>ちゅうわり</t>
+  </si>
+  <si>
+    <t>pemotongan menengah</t>
+  </si>
+  <si>
+    <t>小割り</t>
+  </si>
+  <si>
+    <t>こわり</t>
+  </si>
+  <si>
+    <t>pemotongan akhir</t>
+  </si>
+  <si>
+    <t>実際</t>
+  </si>
+  <si>
+    <t>じっさい</t>
+  </si>
+  <si>
+    <t>sebenarnya, dalam praktik</t>
+  </si>
+  <si>
+    <t>lokasi kerja</t>
+  </si>
+  <si>
+    <t>明確</t>
+  </si>
+  <si>
+    <t>めいかく</t>
+  </si>
+  <si>
+    <t>区別する</t>
+  </si>
+  <si>
+    <t>くべつする</t>
+  </si>
+  <si>
+    <t>membedakan</t>
   </si>
 </sst>
 </file>
@@ -7895,7 +9803,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G1395"/>
+  <dimension ref="A1:G1805"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
@@ -27506,6 +29414,5746 @@
         <v>2516</v>
       </c>
     </row>
+    <row r="1396" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1396" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1396" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="C1396" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="D1396" s="12" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1397" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1397" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1397" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="D1397" s="12" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1398" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1398" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="C1398" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D1398" s="12" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1399" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1399" s="12" t="s">
+        <v>2519</v>
+      </c>
+      <c r="C1399" s="12" t="s">
+        <v>2520</v>
+      </c>
+      <c r="D1399" s="12" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1400" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1400" s="12" t="s">
+        <v>2522</v>
+      </c>
+      <c r="C1400" s="12" t="s">
+        <v>2523</v>
+      </c>
+      <c r="D1400" s="12" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1401" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1401" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="C1401" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="D1401" s="12" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1402" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1402" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="C1402" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="D1402" s="12" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1403" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1403" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1403" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="D1403" s="12" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1404" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1404" s="12" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C1404" s="12" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D1404" s="12" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1405" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1405" s="12" t="s">
+        <v>2526</v>
+      </c>
+      <c r="C1405" s="12" t="s">
+        <v>2527</v>
+      </c>
+      <c r="D1405" s="12" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1406" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1406" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1406" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1406" s="12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1407" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1407" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="C1407" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="D1407" s="12" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1408" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1408" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="C1408" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D1408" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1409" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1409" s="12" t="s">
+        <v>2419</v>
+      </c>
+      <c r="C1409" s="12" t="s">
+        <v>2420</v>
+      </c>
+      <c r="D1409" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1410" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1410" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1410" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1410" s="12" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1411" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1411" s="12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C1411" s="12" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D1411" s="12" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1412" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1412" s="12" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C1412" s="12" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D1412" s="12" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1413" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1413" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1413" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D1413" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1414" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1414" s="12" t="s">
+        <v>942</v>
+      </c>
+      <c r="C1414" s="12" t="s">
+        <v>943</v>
+      </c>
+      <c r="D1414" s="12" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1415" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1415" s="12" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C1415" s="12" t="s">
+        <v>2218</v>
+      </c>
+      <c r="D1415" s="12" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1416" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1416" s="12" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C1416" s="12" t="s">
+        <v>2359</v>
+      </c>
+      <c r="D1416" s="12" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1417" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1417" s="12" t="s">
+        <v>2532</v>
+      </c>
+      <c r="C1417" s="12" t="s">
+        <v>2533</v>
+      </c>
+      <c r="D1417" s="12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1418" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1418" s="12" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C1418" s="12" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D1418" s="12" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1419" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1419" s="12" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C1419" s="12" t="s">
+        <v>2535</v>
+      </c>
+      <c r="D1419" s="12" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1420" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1420" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C1420" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D1420" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1421" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1421" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C1421" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D1421" s="12" t="s">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1422" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1422" s="12" t="s">
+        <v>2538</v>
+      </c>
+      <c r="C1422" s="12" t="s">
+        <v>2539</v>
+      </c>
+      <c r="D1422" s="12" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1423" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1423" s="12" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C1423" s="12" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D1423" s="12" t="s">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1424" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1424" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1424" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D1424" s="12" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1425" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1425" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="C1425" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="D1425" s="12" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1426" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1426" s="12" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C1426" s="12" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D1426" s="12" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1427" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1427" s="12" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C1427" s="12" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D1427" s="12" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1428" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1428" s="12" t="s">
+        <v>2545</v>
+      </c>
+      <c r="C1428" s="12" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D1428" s="12" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1429" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1429" s="12" t="s">
+        <v>2548</v>
+      </c>
+      <c r="C1429" s="12" t="s">
+        <v>2549</v>
+      </c>
+      <c r="D1429" s="12" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1430" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1430" s="12" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C1430" s="12" t="s">
+        <v>2552</v>
+      </c>
+      <c r="D1430" s="12" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1431" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1431" s="12" t="s">
+        <v>2554</v>
+      </c>
+      <c r="C1431" s="12" t="s">
+        <v>2555</v>
+      </c>
+      <c r="D1431" s="12" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1432" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1432" s="12" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C1432" s="12" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D1432" s="12" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1433" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1433" s="12" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C1433" s="12" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D1433" s="12" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1434" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1434" s="12" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C1434" s="12" t="s">
+        <v>2564</v>
+      </c>
+      <c r="D1434" s="12" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1435" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1435" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1435" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1435" s="12" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1436" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1436" s="12" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C1436" s="12" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D1436" s="12" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1437" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1437" s="12" t="s">
+        <v>2566</v>
+      </c>
+      <c r="C1437" s="12" t="s">
+        <v>2567</v>
+      </c>
+      <c r="D1437" s="12" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1438" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1438" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="C1438" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="D1438" s="12" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1439" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1439" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="C1439" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="D1439" s="12" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1440" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1440" s="12" t="s">
+        <v>2570</v>
+      </c>
+      <c r="C1440" s="12" t="s">
+        <v>2571</v>
+      </c>
+      <c r="D1440" s="12" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1441" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1441" s="12" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C1441" s="12" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D1441" s="12" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1442" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1442" s="12" t="s">
+        <v>2545</v>
+      </c>
+      <c r="C1442" s="12" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D1442" s="12" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1443" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1443" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="C1443" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D1443" s="12" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1444" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1444" s="12" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C1444" s="12" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D1444" s="12" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1445" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1445" s="12" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C1445" s="12" t="s">
+        <v>2577</v>
+      </c>
+      <c r="D1445" s="12" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1446" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1446" s="12" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C1446" s="12" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D1446" s="12" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1447" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1447" s="12" t="s">
+        <v>2367</v>
+      </c>
+      <c r="C1447" s="12" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D1447" s="12" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1448" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1448" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1448" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D1448" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1449" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1449" s="12" t="s">
+        <v>2580</v>
+      </c>
+      <c r="C1449" s="12" t="s">
+        <v>2581</v>
+      </c>
+      <c r="D1449" s="12" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1450" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1450" s="12" t="s">
+        <v>2583</v>
+      </c>
+      <c r="C1450" s="12" t="s">
+        <v>2584</v>
+      </c>
+      <c r="D1450" s="12" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1451" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1451" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1451" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1451" s="12" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1452" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1452" s="12" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C1452" s="12" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D1452" s="12" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1453" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1453" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="C1453" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="D1453" s="12" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1454" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1454" s="12" t="s">
+        <v>2499</v>
+      </c>
+      <c r="C1454" s="12" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D1454" s="12" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1455" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1455" s="12" t="s">
+        <v>954</v>
+      </c>
+      <c r="C1455" s="12" t="s">
+        <v>955</v>
+      </c>
+      <c r="D1455" s="12" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1456" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1456" s="12" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C1456" s="12" t="s">
+        <v>2588</v>
+      </c>
+      <c r="D1456" s="12" t="s">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1457" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1457" s="12" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1457" s="12" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D1457" s="12" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1458" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1458" s="12" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C1458" s="12" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D1458" s="12" t="s">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1459" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1459" s="12" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C1459" s="12" t="s">
+        <v>2593</v>
+      </c>
+      <c r="D1459" s="12" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1460" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1460" s="12" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C1460" s="12" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D1460" s="12" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1461" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1461" s="12" t="s">
+        <v>2566</v>
+      </c>
+      <c r="C1461" s="12" t="s">
+        <v>2567</v>
+      </c>
+      <c r="D1461" s="12" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1462" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1462" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="C1462" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="D1462" s="12" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1463" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1463" s="12" t="s">
+        <v>2570</v>
+      </c>
+      <c r="C1463" s="12" t="s">
+        <v>2571</v>
+      </c>
+      <c r="D1463" s="12" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1464" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1464" s="12" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C1464" s="12" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D1464" s="12" t="s">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1465" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1465" s="12" t="s">
+        <v>2596</v>
+      </c>
+      <c r="C1465" s="12" t="s">
+        <v>2597</v>
+      </c>
+      <c r="D1465" s="12" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1466" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1466" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="C1466" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="D1466" s="12" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1467" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1467" s="12" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C1467" s="12" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D1467" s="12" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1468" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1468" s="12" t="s">
+        <v>2599</v>
+      </c>
+      <c r="C1468" s="12" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D1468" s="12" t="s">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1469" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1469" s="12" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C1469" s="12" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D1469" s="12" t="s">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1470" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1470" s="12" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C1470" s="12" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D1470" s="12" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1471" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1471" s="12" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C1471" s="12" t="s">
+        <v>2341</v>
+      </c>
+      <c r="D1471" s="12" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1472" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1472" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1472" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1472" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1473" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1473" s="12" t="s">
+        <v>2606</v>
+      </c>
+      <c r="C1473" s="12" t="s">
+        <v>2607</v>
+      </c>
+      <c r="D1473" s="12" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1474" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1474" s="12" t="s">
+        <v>2609</v>
+      </c>
+      <c r="C1474" s="12" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D1474" s="12" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1475" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1475" s="12" t="s">
+        <v>2611</v>
+      </c>
+      <c r="C1475" s="12" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D1475" s="12" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1476" s="1">
+        <v>23</v>
+      </c>
+      <c r="B1476" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="C1476" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="D1476" s="12" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1477" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1477" s="12" t="s">
+        <v>2615</v>
+      </c>
+      <c r="C1477" s="12" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D1477" s="12" t="s">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1478" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1478" s="12" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C1478" s="12" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D1478" s="12" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1479" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1479" s="12" t="s">
+        <v>2599</v>
+      </c>
+      <c r="C1479" s="12" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D1479" s="12" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1480" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1480" s="12" t="s">
+        <v>2619</v>
+      </c>
+      <c r="C1480" s="12" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D1480" s="12" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1481" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1481" s="12" t="s">
+        <v>2622</v>
+      </c>
+      <c r="C1481" s="12" t="s">
+        <v>2623</v>
+      </c>
+      <c r="D1481" s="12" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1482" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1482" s="12" t="s">
+        <v>2625</v>
+      </c>
+      <c r="C1482" s="12" t="s">
+        <v>2626</v>
+      </c>
+      <c r="D1482" s="12" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1483" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1483" s="12" t="s">
+        <v>2628</v>
+      </c>
+      <c r="C1483" s="12" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D1483" s="12" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1484" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1484" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="C1484" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D1484" s="12" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1485" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1485" s="12" t="s">
+        <v>2631</v>
+      </c>
+      <c r="C1485" s="12" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D1485" s="12" t="s">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1486" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1486" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="C1486" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="D1486" s="12" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1487" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1487" s="12" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C1487" s="12" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D1487" s="12" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1488" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1488" s="12" t="s">
+        <v>2583</v>
+      </c>
+      <c r="C1488" s="12" t="s">
+        <v>2584</v>
+      </c>
+      <c r="D1488" s="12" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1489" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1489" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1489" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D1489" s="12" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1490" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1490" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="C1490" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="D1490" s="12" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1491" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1491" s="12" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C1491" s="12" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D1491" s="12" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1492" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1492" s="12" t="s">
+        <v>2636</v>
+      </c>
+      <c r="C1492" s="12" t="s">
+        <v>2637</v>
+      </c>
+      <c r="D1492" s="12" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1493" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1493" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C1493" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D1493" s="12" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1494" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1494" s="12" t="s">
+        <v>2639</v>
+      </c>
+      <c r="C1494" s="12" t="s">
+        <v>2640</v>
+      </c>
+      <c r="D1494" s="12" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1495" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1495" s="12" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C1495" s="12" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D1495" s="12" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1496" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1496" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="C1496" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D1496" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1497" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1497" s="12" t="s">
+        <v>2642</v>
+      </c>
+      <c r="C1497" s="12" t="s">
+        <v>2643</v>
+      </c>
+      <c r="D1497" s="12" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1498" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1498" s="12" t="s">
+        <v>2645</v>
+      </c>
+      <c r="C1498" s="12" t="s">
+        <v>2646</v>
+      </c>
+      <c r="D1498" s="12" t="s">
+        <v>2647</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1499" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1499" s="12" t="s">
+        <v>2648</v>
+      </c>
+      <c r="C1499" s="12" t="s">
+        <v>2648</v>
+      </c>
+      <c r="D1499" s="12" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1500" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1500" s="12" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C1500" s="12" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D1500" s="12" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1501" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1501" s="12" t="s">
+        <v>2652</v>
+      </c>
+      <c r="C1501" s="12" t="s">
+        <v>2653</v>
+      </c>
+      <c r="D1501" s="12" t="s">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1502" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1502" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1502" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D1502" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1503" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1503" s="12" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1503" s="12" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D1503" s="12" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1504" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1504" s="12" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C1504" s="12" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D1504" s="12" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1505" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1505" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1505" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1505" s="12" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1506" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1506" s="12" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C1506" s="12" t="s">
+        <v>2657</v>
+      </c>
+      <c r="D1506" s="12" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1507" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1507" s="12" t="s">
+        <v>617</v>
+      </c>
+      <c r="C1507" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1507" s="12" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1508" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1508" s="12" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C1508" s="12" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D1508" s="12" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1509" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1509" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1509" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1509" s="12" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1510" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1510" s="12" t="s">
+        <v>2662</v>
+      </c>
+      <c r="C1510" s="12" t="s">
+        <v>2663</v>
+      </c>
+      <c r="D1510" s="12" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1511" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1511" s="12" t="s">
+        <v>2665</v>
+      </c>
+      <c r="C1511" s="12" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D1511" s="12" t="s">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1512" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1512" s="12" t="s">
+        <v>2668</v>
+      </c>
+      <c r="C1512" s="12" t="s">
+        <v>2668</v>
+      </c>
+      <c r="D1512" s="12" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1513" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1513" s="12" t="s">
+        <v>2670</v>
+      </c>
+      <c r="C1513" s="12" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D1513" s="12" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1514" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1514" s="12" t="s">
+        <v>2673</v>
+      </c>
+      <c r="C1514" s="12" t="s">
+        <v>2674</v>
+      </c>
+      <c r="D1514" s="12" t="s">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1515" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1515" s="12" t="s">
+        <v>2676</v>
+      </c>
+      <c r="C1515" s="12" t="s">
+        <v>2677</v>
+      </c>
+      <c r="D1515" s="12" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1516" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1516" s="12" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C1516" s="12" t="s">
+        <v>2680</v>
+      </c>
+      <c r="D1516" s="12" t="s">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1517" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1517" s="12" t="s">
+        <v>2367</v>
+      </c>
+      <c r="C1517" s="12" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D1517" s="12" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1518" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1518" s="12" t="s">
+        <v>2682</v>
+      </c>
+      <c r="C1518" s="12" t="s">
+        <v>2683</v>
+      </c>
+      <c r="D1518" s="12" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1519" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1519" s="12" t="s">
+        <v>2685</v>
+      </c>
+      <c r="C1519" s="12" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D1519" s="12" t="s">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1520" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1520" s="12" t="s">
+        <v>2688</v>
+      </c>
+      <c r="C1520" s="12" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D1520" s="12" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1521" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1521" s="12" t="s">
+        <v>2691</v>
+      </c>
+      <c r="C1521" s="12" t="s">
+        <v>2692</v>
+      </c>
+      <c r="D1521" s="12" t="s">
+        <v>2693</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1522" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1522" s="12" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C1522" s="12" t="s">
+        <v>2695</v>
+      </c>
+      <c r="D1522" s="12" t="s">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1523" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1523" s="12" t="s">
+        <v>2697</v>
+      </c>
+      <c r="C1523" s="12" t="s">
+        <v>2698</v>
+      </c>
+      <c r="D1523" s="12" t="s">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1524" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1524" s="12" t="s">
+        <v>2700</v>
+      </c>
+      <c r="C1524" s="12" t="s">
+        <v>2701</v>
+      </c>
+      <c r="D1524" s="12" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1525" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1525" s="12" t="s">
+        <v>2619</v>
+      </c>
+      <c r="C1525" s="12" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D1525" s="12" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1526" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1526" s="12" t="s">
+        <v>2703</v>
+      </c>
+      <c r="C1526" s="12" t="s">
+        <v>2703</v>
+      </c>
+      <c r="D1526" s="12" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1527" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1527" s="12" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C1527" s="12" t="s">
+        <v>2706</v>
+      </c>
+      <c r="D1527" s="12" t="s">
+        <v>2707</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1528" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1528" s="12" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C1528" s="12" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D1528" s="12" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1529" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1529" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1529" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1529" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1530" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1530" s="12" t="s">
+        <v>2708</v>
+      </c>
+      <c r="C1530" s="12" t="s">
+        <v>2708</v>
+      </c>
+      <c r="D1530" s="12" t="s">
+        <v>2709</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1531" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1531" s="12" t="s">
+        <v>2615</v>
+      </c>
+      <c r="C1531" s="12" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D1531" s="12" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1532" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1532" s="12" t="s">
+        <v>2710</v>
+      </c>
+      <c r="C1532" s="12" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D1532" s="12" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1533" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1533" s="12" t="s">
+        <v>2713</v>
+      </c>
+      <c r="C1533" s="12" t="s">
+        <v>2714</v>
+      </c>
+      <c r="D1533" s="12" t="s">
+        <v>2715</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1534" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1534" s="12" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C1534" s="12" t="s">
+        <v>2680</v>
+      </c>
+      <c r="D1534" s="12" t="s">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1535" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1535" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="C1535" s="12" t="s">
+        <v>970</v>
+      </c>
+      <c r="D1535" s="12" t="s">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1536" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1536" s="12" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C1536" s="12" t="s">
+        <v>2718</v>
+      </c>
+      <c r="D1536" s="12" t="s">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1537" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1537" s="12" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C1537" s="12" t="s">
+        <v>2721</v>
+      </c>
+      <c r="D1537" s="12" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1538" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1538" s="12" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C1538" s="12" t="s">
+        <v>2724</v>
+      </c>
+      <c r="D1538" s="12" t="s">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1539" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1539" s="12" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C1539" s="12" t="s">
+        <v>2727</v>
+      </c>
+      <c r="D1539" s="12" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1540" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1540" s="12" t="s">
+        <v>2688</v>
+      </c>
+      <c r="C1540" s="12" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D1540" s="12" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1541" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1541" s="12" t="s">
+        <v>617</v>
+      </c>
+      <c r="C1541" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1541" s="12" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1542" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1542" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C1542" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D1542" s="12" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1543" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1543" s="12" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C1543" s="12" t="s">
+        <v>2730</v>
+      </c>
+      <c r="D1543" s="12" t="s">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1544" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1544" s="12" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C1544" s="12" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D1544" s="12" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1545" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1545" s="12" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C1545" s="12" t="s">
+        <v>2733</v>
+      </c>
+      <c r="D1545" s="12" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1546" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1546" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1546" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1546" s="12" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1547" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1547" s="12" t="s">
+        <v>2735</v>
+      </c>
+      <c r="C1547" s="12" t="s">
+        <v>2736</v>
+      </c>
+      <c r="D1547" s="12" t="s">
+        <v>2737</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1548" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1548" s="12" t="s">
+        <v>2738</v>
+      </c>
+      <c r="C1548" s="12" t="s">
+        <v>2739</v>
+      </c>
+      <c r="D1548" s="12" t="s">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1549" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1549" s="12" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C1549" s="12" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D1549" s="12" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1550" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1550" s="12" t="s">
+        <v>2419</v>
+      </c>
+      <c r="C1550" s="12" t="s">
+        <v>2420</v>
+      </c>
+      <c r="D1550" s="12" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1551" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1551" s="12" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C1551" s="12" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D1551" s="12" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1552" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1552" s="12" t="s">
+        <v>2744</v>
+      </c>
+      <c r="C1552" s="12" t="s">
+        <v>2745</v>
+      </c>
+      <c r="D1552" s="12" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1553" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1553" s="12" t="s">
+        <v>2747</v>
+      </c>
+      <c r="C1553" s="12" t="s">
+        <v>2748</v>
+      </c>
+      <c r="D1553" s="12" t="s">
+        <v>2749</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1554" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1554" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C1554" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D1554" s="12" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1555" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1555" s="12" t="s">
+        <v>2751</v>
+      </c>
+      <c r="C1555" s="12" t="s">
+        <v>2752</v>
+      </c>
+      <c r="D1555" s="12" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1556" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1556" s="12" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C1556" s="12" t="s">
+        <v>2755</v>
+      </c>
+      <c r="D1556" s="12" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1557" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1557" s="12" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C1557" s="12" t="s">
+        <v>2758</v>
+      </c>
+      <c r="D1557" s="12" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1558" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1558" s="12" t="s">
+        <v>2760</v>
+      </c>
+      <c r="C1558" s="12" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D1558" s="12" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1559" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1559" s="12" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C1559" s="12" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D1559" s="12" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1560" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1560" s="12" t="s">
+        <v>2763</v>
+      </c>
+      <c r="C1560" s="12" t="s">
+        <v>2764</v>
+      </c>
+      <c r="D1560" s="12" t="s">
+        <v>2765</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1561" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1561" s="12" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C1561" s="12" t="s">
+        <v>2767</v>
+      </c>
+      <c r="D1561" s="12" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1562" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1562" s="12" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C1562" s="12" t="s">
+        <v>2770</v>
+      </c>
+      <c r="D1562" s="12" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1563" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1563" s="12" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C1563" s="12" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D1563" s="12" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1564" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1564" s="12" t="s">
+        <v>2772</v>
+      </c>
+      <c r="C1564" s="12" t="s">
+        <v>2773</v>
+      </c>
+      <c r="D1564" s="12" t="s">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1565" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1565" s="12" t="s">
+        <v>2775</v>
+      </c>
+      <c r="C1565" s="12" t="s">
+        <v>2776</v>
+      </c>
+      <c r="D1565" s="12" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1566" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1566" s="12" t="s">
+        <v>2778</v>
+      </c>
+      <c r="C1566" s="12" t="s">
+        <v>2779</v>
+      </c>
+      <c r="D1566" s="12" t="s">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1567" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1567" s="12" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C1567" s="12" t="s">
+        <v>2695</v>
+      </c>
+      <c r="D1567" s="12" t="s">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1568" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1568" s="12" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C1568" s="12" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D1568" s="12" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1569" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1569" s="12" t="s">
+        <v>2782</v>
+      </c>
+      <c r="C1569" s="12" t="s">
+        <v>2783</v>
+      </c>
+      <c r="D1569" s="12" t="s">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1570" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1570" s="12" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C1570" s="12" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D1570" s="12" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1571" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1571" s="12" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C1571" s="12" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D1571" s="12" t="s">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1572" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1572" s="12" t="s">
+        <v>2583</v>
+      </c>
+      <c r="C1572" s="12" t="s">
+        <v>2584</v>
+      </c>
+      <c r="D1572" s="12" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1573" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1573" s="12" t="s">
+        <v>2791</v>
+      </c>
+      <c r="C1573" s="12" t="s">
+        <v>2791</v>
+      </c>
+      <c r="D1573" s="12" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1574" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1574" s="12" t="s">
+        <v>2535</v>
+      </c>
+      <c r="C1574" s="12" t="s">
+        <v>2535</v>
+      </c>
+      <c r="D1574" s="12" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1575" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1575" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C1575" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D1575" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1576" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1576" s="12" t="s">
+        <v>2793</v>
+      </c>
+      <c r="C1576" s="12" t="s">
+        <v>2794</v>
+      </c>
+      <c r="D1576" s="12" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1577" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1577" s="12" t="s">
+        <v>2796</v>
+      </c>
+      <c r="C1577" s="12" t="s">
+        <v>2797</v>
+      </c>
+      <c r="D1577" s="12" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1578" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1578" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1578" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D1578" s="12" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1579" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1579" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C1579" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D1579" s="12" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1580" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1580" s="12" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C1580" s="12" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D1580" s="12" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1581" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1581" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1581" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="D1581" s="12" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1582" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1582" s="12" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C1582" s="12" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D1582" s="12" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1583" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1583" s="12" t="s">
+        <v>2800</v>
+      </c>
+      <c r="C1583" s="12" t="s">
+        <v>2801</v>
+      </c>
+      <c r="D1583" s="12" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1584" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1584" s="12" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C1584" s="12" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D1584" s="12" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1585" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1585" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="C1585" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="D1585" s="12" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1586" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1586" s="12" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C1586" s="12" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D1586" s="12" t="s">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1587" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1587" s="12" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C1587" s="12" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D1587" s="12" t="s">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1588" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1588" s="12" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C1588" s="12" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D1588" s="12" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1589" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1589" s="12" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C1589" s="12" t="s">
+        <v>2811</v>
+      </c>
+      <c r="D1589" s="12" t="s">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1590" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1590" s="12" t="s">
+        <v>2813</v>
+      </c>
+      <c r="C1590" s="12" t="s">
+        <v>2814</v>
+      </c>
+      <c r="D1590" s="12" t="s">
+        <v>2815</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1591" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1591" s="12" t="s">
+        <v>2816</v>
+      </c>
+      <c r="C1591" s="12" t="s">
+        <v>2817</v>
+      </c>
+      <c r="D1591" s="12" t="s">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1592" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1592" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C1592" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="D1592" s="12" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1593" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1593" s="12" t="s">
+        <v>2819</v>
+      </c>
+      <c r="C1593" s="12" t="s">
+        <v>2820</v>
+      </c>
+      <c r="D1593" s="12" t="s">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1594" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1594" s="12" t="s">
+        <v>2822</v>
+      </c>
+      <c r="C1594" s="12" t="s">
+        <v>2823</v>
+      </c>
+      <c r="D1594" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1595" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1595" s="12" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C1595" s="12" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D1595" s="12" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1596" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1596" s="12" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C1596" s="12" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D1596" s="12" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1597" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1597" s="12" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C1597" s="12" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D1597" s="12" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1598" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1598" s="12" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C1598" s="12" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D1598" s="12" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1599" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1599" s="12" t="s">
+        <v>2827</v>
+      </c>
+      <c r="C1599" s="12" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D1599" s="12" t="s">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1600" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1600" s="12" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C1600" s="12" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D1600" s="12" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1601" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1601" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1601" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1601" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1602" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1602" s="12" t="s">
+        <v>2830</v>
+      </c>
+      <c r="C1602" s="12" t="s">
+        <v>2831</v>
+      </c>
+      <c r="D1602" s="12" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1603" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1603" s="12" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C1603" s="12" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D1603" s="12" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1604" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1604" s="12" t="s">
+        <v>2566</v>
+      </c>
+      <c r="C1604" s="12" t="s">
+        <v>2567</v>
+      </c>
+      <c r="D1604" s="12" t="s">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1605" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1605" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1605" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="D1605" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1606" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1606" s="12" t="s">
+        <v>2833</v>
+      </c>
+      <c r="C1606" s="12" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D1606" s="12" t="s">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1607" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1607" s="12" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C1607" s="12" t="s">
+        <v>2836</v>
+      </c>
+      <c r="D1607" s="12" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1608" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1608" s="12" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C1608" s="12" t="s">
+        <v>2838</v>
+      </c>
+      <c r="D1608" s="12" t="s">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1609" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1609" s="12" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C1609" s="12" t="s">
+        <v>2841</v>
+      </c>
+      <c r="D1609" s="12" t="s">
+        <v>2842</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1610" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1610" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C1610" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1610" s="12" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1611" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1611" s="12" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C1611" s="12" t="s">
+        <v>2845</v>
+      </c>
+      <c r="D1611" s="12" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1612" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1612" s="12" t="s">
+        <v>2847</v>
+      </c>
+      <c r="C1612" s="12" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D1612" s="12" t="s">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1613" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1613" s="12" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C1613" s="12" t="s">
+        <v>2850</v>
+      </c>
+      <c r="D1613" s="12" t="s">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1614" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1614" s="12" t="s">
+        <v>2852</v>
+      </c>
+      <c r="C1614" s="12" t="s">
+        <v>2853</v>
+      </c>
+      <c r="D1614" s="12" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1615" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1615" s="12" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C1615" s="12" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D1615" s="12" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1616" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1616" s="12" t="s">
+        <v>2856</v>
+      </c>
+      <c r="C1616" s="12" t="s">
+        <v>2857</v>
+      </c>
+      <c r="D1616" s="12" t="s">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1617" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1617" s="12" t="s">
+        <v>2859</v>
+      </c>
+      <c r="C1617" s="12" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D1617" s="12" t="s">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1618" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1618" s="12" t="s">
+        <v>2862</v>
+      </c>
+      <c r="C1618" s="12" t="s">
+        <v>2863</v>
+      </c>
+      <c r="D1618" s="12" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1619" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1619" s="12" t="s">
+        <v>2822</v>
+      </c>
+      <c r="C1619" s="12" t="s">
+        <v>2823</v>
+      </c>
+      <c r="D1619" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1620" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1620" s="12" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C1620" s="12" t="s">
+        <v>2866</v>
+      </c>
+      <c r="D1620" s="12" t="s">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1621" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1621" s="12" t="s">
+        <v>2868</v>
+      </c>
+      <c r="C1621" s="12" t="s">
+        <v>2868</v>
+      </c>
+      <c r="D1621" s="12" t="s">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1622" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1622" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1622" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1622" s="12" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1623" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1623" s="12" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C1623" s="12" t="s">
+        <v>2850</v>
+      </c>
+      <c r="D1623" s="12" t="s">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1624" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1624" s="12" t="s">
+        <v>2868</v>
+      </c>
+      <c r="C1624" s="12" t="s">
+        <v>2868</v>
+      </c>
+      <c r="D1624" s="12" t="s">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1625" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1625" s="12" t="s">
+        <v>2870</v>
+      </c>
+      <c r="C1625" s="12" t="s">
+        <v>2871</v>
+      </c>
+      <c r="D1625" s="12" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1626" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1626" s="12" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C1626" s="12" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D1626" s="12" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1627" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1627" s="12" t="s">
+        <v>2560</v>
+      </c>
+      <c r="C1627" s="12" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D1627" s="12" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1628" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1628" s="12" t="s">
+        <v>2602</v>
+      </c>
+      <c r="C1628" s="12" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D1628" s="12" t="s">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1629" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1629" s="12" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C1629" s="12" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D1629" s="12" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1630" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1630" s="12" t="s">
+        <v>2874</v>
+      </c>
+      <c r="C1630" s="12" t="s">
+        <v>2875</v>
+      </c>
+      <c r="D1630" s="12" t="s">
+        <v>2876</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1631" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1631" s="12" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C1631" s="12" t="s">
+        <v>2878</v>
+      </c>
+      <c r="D1631" s="12" t="s">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1632" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1632" s="12" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C1632" s="12" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D1632" s="12" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1633" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1633" s="12" t="s">
+        <v>2880</v>
+      </c>
+      <c r="C1633" s="12" t="s">
+        <v>2881</v>
+      </c>
+      <c r="D1633" s="12" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1634" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1634" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1634" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="D1634" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1635" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1635" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1635" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1635" s="12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1636" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1636" s="12" t="s">
+        <v>2883</v>
+      </c>
+      <c r="C1636" s="12" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D1636" s="12" t="s">
+        <v>2885</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1637" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1637" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1637" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="D1637" s="12" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1638" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1638" s="12" t="s">
+        <v>2886</v>
+      </c>
+      <c r="C1638" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="D1638" s="12" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1639" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1639" s="12" t="s">
+        <v>2887</v>
+      </c>
+      <c r="C1639" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1639" s="12" t="s">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1640" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1640" s="12" t="s">
+        <v>2889</v>
+      </c>
+      <c r="C1640" s="12" t="s">
+        <v>2890</v>
+      </c>
+      <c r="D1640" s="12" t="s">
+        <v>2891</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1641" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1641" s="12" t="s">
+        <v>2615</v>
+      </c>
+      <c r="C1641" s="12" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D1641" s="12" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1642" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1642" s="12" t="s">
+        <v>2892</v>
+      </c>
+      <c r="C1642" s="12" t="s">
+        <v>2892</v>
+      </c>
+      <c r="D1642" s="12" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1643" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1643" s="12" t="s">
+        <v>2894</v>
+      </c>
+      <c r="C1643" s="12" t="s">
+        <v>2895</v>
+      </c>
+      <c r="D1643" s="12" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1644" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1644" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C1644" s="12" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D1644" s="12" t="s">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1645" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1645" s="12" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C1645" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D1645" s="12" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1646" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1646" s="12" t="s">
+        <v>2898</v>
+      </c>
+      <c r="C1646" s="12" t="s">
+        <v>2899</v>
+      </c>
+      <c r="D1646" s="12" t="s">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1647" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1647" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1647" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1647" s="12" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1648" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1648" s="12" t="s">
+        <v>2367</v>
+      </c>
+      <c r="C1648" s="12" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D1648" s="12" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1649" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1649" s="12" t="s">
+        <v>2688</v>
+      </c>
+      <c r="C1649" s="12" t="s">
+        <v>2689</v>
+      </c>
+      <c r="D1649" s="12" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1650" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1650" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1650" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="D1650" s="12" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1651" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1651" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1651" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1651" s="12" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1652" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1652" s="12" t="s">
+        <v>2901</v>
+      </c>
+      <c r="C1652" s="12" t="s">
+        <v>2902</v>
+      </c>
+      <c r="D1652" s="12" t="s">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1653" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1653" s="12" t="s">
+        <v>2904</v>
+      </c>
+      <c r="C1653" s="12" t="s">
+        <v>2905</v>
+      </c>
+      <c r="D1653" s="12" t="s">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1654" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1654" s="12" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C1654" s="12" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D1654" s="12" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1655" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1655" s="12" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C1655" s="12" t="s">
+        <v>2907</v>
+      </c>
+      <c r="D1655" s="12" t="s">
+        <v>2908</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1656" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1656" s="12" t="s">
+        <v>2909</v>
+      </c>
+      <c r="C1656" s="12" t="s">
+        <v>2909</v>
+      </c>
+      <c r="D1656" s="12" t="s">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1657" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1657" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1657" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1657" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1658" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1658" s="12" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C1658" s="12" t="s">
+        <v>2912</v>
+      </c>
+      <c r="D1658" s="12" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1659" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1659" s="12" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C1659" s="12" t="s">
+        <v>2912</v>
+      </c>
+      <c r="D1659" s="12" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1660" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1660" s="12" t="s">
+        <v>2914</v>
+      </c>
+      <c r="C1660" s="12" t="s">
+        <v>2914</v>
+      </c>
+      <c r="D1660" s="12" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1661" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1661" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1661" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1661" s="12" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1662" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1662" s="12" t="s">
+        <v>2411</v>
+      </c>
+      <c r="C1662" s="12" t="s">
+        <v>2412</v>
+      </c>
+      <c r="D1662" s="12" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1663" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1663" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C1663" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D1663" s="12" t="s">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1664" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1664" s="12" t="s">
+        <v>934</v>
+      </c>
+      <c r="C1664" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="D1664" s="12" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1665" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1665" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="C1665" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="D1665" s="12" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1666" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1666" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C1666" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1666" s="12" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1667" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1667" s="12" t="s">
+        <v>2915</v>
+      </c>
+      <c r="C1667" s="12" t="s">
+        <v>2916</v>
+      </c>
+      <c r="D1667" s="12" t="s">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1668" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1668" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="C1668" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="D1668" s="12" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1669" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1669" s="12" t="s">
+        <v>665</v>
+      </c>
+      <c r="C1669" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="D1669" s="12" t="s">
+        <v>2918</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1670" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1670" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="C1670" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="D1670" s="12" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1671" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1671" s="12" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C1671" s="12" t="s">
+        <v>2920</v>
+      </c>
+      <c r="D1671" s="12" t="s">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1672" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1672" s="12" t="s">
+        <v>2922</v>
+      </c>
+      <c r="C1672" s="12" t="s">
+        <v>2923</v>
+      </c>
+      <c r="D1672" s="12" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1673" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1673" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1673" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1673" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1674" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1674" s="12" t="s">
+        <v>957</v>
+      </c>
+      <c r="C1674" s="12" t="s">
+        <v>958</v>
+      </c>
+      <c r="D1674" s="12" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1675" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1675" s="12" t="s">
+        <v>2925</v>
+      </c>
+      <c r="C1675" s="12" t="s">
+        <v>2926</v>
+      </c>
+      <c r="D1675" s="12" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1676" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1676" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="C1676" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="D1676" s="12" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1677" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1677" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="C1677" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="D1677" s="12" t="s">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1678" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1678" s="12" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C1678" s="12" t="s">
+        <v>2930</v>
+      </c>
+      <c r="D1678" s="12" t="s">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1679" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1679" s="12" t="s">
+        <v>2932</v>
+      </c>
+      <c r="C1679" s="12" t="s">
+        <v>2933</v>
+      </c>
+      <c r="D1679" s="12" t="s">
+        <v>2934</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1680" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1680" s="12" t="s">
+        <v>2935</v>
+      </c>
+      <c r="C1680" s="12" t="s">
+        <v>2936</v>
+      </c>
+      <c r="D1680" s="12" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1681" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1681" s="12" t="s">
+        <v>2938</v>
+      </c>
+      <c r="C1681" s="12" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D1681" s="12" t="s">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1682" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1682" s="12" t="s">
+        <v>2862</v>
+      </c>
+      <c r="C1682" s="12" t="s">
+        <v>2863</v>
+      </c>
+      <c r="D1682" s="12" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1683" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1683" s="12" t="s">
+        <v>2883</v>
+      </c>
+      <c r="C1683" s="12" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D1683" s="12" t="s">
+        <v>2885</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1684" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1684" s="12" t="s">
+        <v>2941</v>
+      </c>
+      <c r="C1684" s="12" t="s">
+        <v>2941</v>
+      </c>
+      <c r="D1684" s="12" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1685" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1685" s="12" t="s">
+        <v>2943</v>
+      </c>
+      <c r="C1685" s="12" t="s">
+        <v>2944</v>
+      </c>
+      <c r="D1685" s="12" t="s">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1686" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1686" s="12" t="s">
+        <v>2946</v>
+      </c>
+      <c r="C1686" s="12" t="s">
+        <v>2947</v>
+      </c>
+      <c r="D1686" s="12" t="s">
+        <v>2948</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1687" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1687" s="12" t="s">
+        <v>2949</v>
+      </c>
+      <c r="C1687" s="12" t="s">
+        <v>2950</v>
+      </c>
+      <c r="D1687" s="12" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1688" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1688" s="12" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C1688" s="12" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D1688" s="12" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1689" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1689" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1689" s="12" t="s">
+        <v>2952</v>
+      </c>
+      <c r="D1689" s="12" t="s">
+        <v>2953</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1690" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1690" s="12" t="s">
+        <v>2954</v>
+      </c>
+      <c r="C1690" s="12" t="s">
+        <v>2955</v>
+      </c>
+      <c r="D1690" s="12" t="s">
+        <v>2956</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1691" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1691" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="C1691" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1691" s="12" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1692" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1692" s="12" t="s">
+        <v>2957</v>
+      </c>
+      <c r="C1692" s="12" t="s">
+        <v>2958</v>
+      </c>
+      <c r="D1692" s="12" t="s">
+        <v>2959</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1693" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1693" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="C1693" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="D1693" s="12" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1694" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1694" s="12" t="s">
+        <v>2960</v>
+      </c>
+      <c r="C1694" s="12" t="s">
+        <v>2961</v>
+      </c>
+      <c r="D1694" s="12" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1695" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1695" s="12" t="s">
+        <v>2962</v>
+      </c>
+      <c r="C1695" s="12" t="s">
+        <v>2963</v>
+      </c>
+      <c r="D1695" s="12" t="s">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1696" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1696" s="12" t="s">
+        <v>2964</v>
+      </c>
+      <c r="C1696" s="12" t="s">
+        <v>2965</v>
+      </c>
+      <c r="D1696" s="12" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1697" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1697" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1697" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1697" s="12" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1698" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1698" s="12" t="s">
+        <v>2967</v>
+      </c>
+      <c r="C1698" s="12" t="s">
+        <v>2968</v>
+      </c>
+      <c r="D1698" s="12" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1699" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1699" s="12" t="s">
+        <v>2970</v>
+      </c>
+      <c r="C1699" s="12" t="s">
+        <v>2971</v>
+      </c>
+      <c r="D1699" s="12" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1700" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1700" s="12" t="s">
+        <v>2973</v>
+      </c>
+      <c r="C1700" s="12" t="s">
+        <v>2974</v>
+      </c>
+      <c r="D1700" s="12" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1701" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1701" s="12" t="s">
+        <v>2975</v>
+      </c>
+      <c r="C1701" s="12" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D1701" s="12" t="s">
+        <v>2977</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1702" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1702" s="12" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C1702" s="12" t="s">
+        <v>2979</v>
+      </c>
+      <c r="D1702" s="12" t="s">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1703" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1703" s="12" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C1703" s="12" t="s">
+        <v>2981</v>
+      </c>
+      <c r="D1703" s="12" t="s">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1704" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1704" s="12" t="s">
+        <v>2983</v>
+      </c>
+      <c r="C1704" s="12" t="s">
+        <v>2984</v>
+      </c>
+      <c r="D1704" s="12" t="s">
+        <v>2985</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1705" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1705" s="12" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C1705" s="12" t="s">
+        <v>2987</v>
+      </c>
+      <c r="D1705" s="12" t="s">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1706" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1706" s="12" t="s">
+        <v>2989</v>
+      </c>
+      <c r="C1706" s="12" t="s">
+        <v>2990</v>
+      </c>
+      <c r="D1706" s="12" t="s">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1707" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1707" s="12" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C1707" s="12" t="s">
+        <v>2993</v>
+      </c>
+      <c r="D1707" s="12" t="s">
+        <v>2994</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1708" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1708" s="12" t="s">
+        <v>2995</v>
+      </c>
+      <c r="C1708" s="12" t="s">
+        <v>2995</v>
+      </c>
+      <c r="D1708" s="12" t="s">
+        <v>2996</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1709" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1709" s="12" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1709" s="12" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D1709" s="12" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1710" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1710" s="12" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C1710" s="12" t="s">
+        <v>2997</v>
+      </c>
+      <c r="D1710" s="12" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1711" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1711" s="12" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C1711" s="12" t="s">
+        <v>2373</v>
+      </c>
+      <c r="D1711" s="12" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1712" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1712" s="12" t="s">
+        <v>2999</v>
+      </c>
+      <c r="C1712" s="12" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1712" s="12" t="s">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1713" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1713" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1713" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1713" s="12" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1714" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1714" s="12" t="s">
+        <v>3002</v>
+      </c>
+      <c r="C1714" s="12" t="s">
+        <v>3003</v>
+      </c>
+      <c r="D1714" s="12" t="s">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1715" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1715" s="12" t="s">
+        <v>3005</v>
+      </c>
+      <c r="C1715" s="12" t="s">
+        <v>3006</v>
+      </c>
+      <c r="D1715" s="12" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1716" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1716" s="12" t="s">
+        <v>3008</v>
+      </c>
+      <c r="C1716" s="12" t="s">
+        <v>3008</v>
+      </c>
+      <c r="D1716" s="12" t="s">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1717" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1717" s="12" t="s">
+        <v>3010</v>
+      </c>
+      <c r="C1717" s="12" t="s">
+        <v>3011</v>
+      </c>
+      <c r="D1717" s="12" t="s">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1718" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1718" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C1718" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D1718" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1719" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1719" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="C1719" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D1719" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1720" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1720" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="C1720" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="D1720" s="12" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1721" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1721" s="12" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C1721" s="12" t="s">
+        <v>3014</v>
+      </c>
+      <c r="D1721" s="12" t="s">
+        <v>3015</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1722" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1722" s="12" t="s">
+        <v>717</v>
+      </c>
+      <c r="C1722" s="12" t="s">
+        <v>718</v>
+      </c>
+      <c r="D1722" s="12" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1723" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1723" s="12" t="s">
+        <v>3016</v>
+      </c>
+      <c r="C1723" s="12" t="s">
+        <v>3017</v>
+      </c>
+      <c r="D1723" s="12" t="s">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1724" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1724" s="12" t="s">
+        <v>3019</v>
+      </c>
+      <c r="C1724" s="12" t="s">
+        <v>3020</v>
+      </c>
+      <c r="D1724" s="12" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1725" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1725" s="12" t="s">
+        <v>3022</v>
+      </c>
+      <c r="C1725" s="12" t="s">
+        <v>3023</v>
+      </c>
+      <c r="D1725" s="12" t="s">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1726" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1726" s="12" t="s">
+        <v>702</v>
+      </c>
+      <c r="C1726" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="D1726" s="12" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1727" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1727" s="12" t="s">
+        <v>3025</v>
+      </c>
+      <c r="C1727" s="12" t="s">
+        <v>3026</v>
+      </c>
+      <c r="D1727" s="12" t="s">
+        <v>3027</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1728" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1728" s="12" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C1728" s="12" t="s">
+        <v>2979</v>
+      </c>
+      <c r="D1728" s="12" t="s">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1729" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1729" s="12" t="s">
+        <v>3028</v>
+      </c>
+      <c r="C1729" s="12" t="s">
+        <v>3029</v>
+      </c>
+      <c r="D1729" s="12" t="s">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1730" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1730" s="12" t="s">
+        <v>3031</v>
+      </c>
+      <c r="C1730" s="12" t="s">
+        <v>3032</v>
+      </c>
+      <c r="D1730" s="12" t="s">
+        <v>3033</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1731" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1731" s="12" t="s">
+        <v>3034</v>
+      </c>
+      <c r="C1731" s="12" t="s">
+        <v>3035</v>
+      </c>
+      <c r="D1731" s="12" t="s">
+        <v>3036</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1732" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1732" s="12" t="s">
+        <v>3037</v>
+      </c>
+      <c r="C1732" s="12" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D1732" s="12" t="s">
+        <v>3038</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1733" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1733" s="12" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C1733" s="12" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D1733" s="12" t="s">
+        <v>3039</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1734" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1734" s="12" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C1734" s="12" t="s">
+        <v>3041</v>
+      </c>
+      <c r="D1734" s="12" t="s">
+        <v>3042</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1735" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1735" s="12" t="s">
+        <v>3043</v>
+      </c>
+      <c r="C1735" s="12" t="s">
+        <v>3043</v>
+      </c>
+      <c r="D1735" s="12" t="s">
+        <v>3044</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1736" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1736" s="12" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C1736" s="12" t="s">
+        <v>2471</v>
+      </c>
+      <c r="D1736" s="12" t="s">
+        <v>3045</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1737" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1737" s="12" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C1737" s="12" t="s">
+        <v>2482</v>
+      </c>
+      <c r="D1737" s="12" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1738" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1738" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1738" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1738" s="12" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1739" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1739" s="12" t="s">
+        <v>730</v>
+      </c>
+      <c r="C1739" s="12" t="s">
+        <v>731</v>
+      </c>
+      <c r="D1739" s="12" t="s">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1740" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1740" s="12" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C1740" s="12" t="s">
+        <v>3048</v>
+      </c>
+      <c r="D1740" s="12" t="s">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1741" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1741" s="12" t="s">
+        <v>2502</v>
+      </c>
+      <c r="C1741" s="12" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D1741" s="12" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1742" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1742" s="12" t="s">
+        <v>2566</v>
+      </c>
+      <c r="C1742" s="12" t="s">
+        <v>2567</v>
+      </c>
+      <c r="D1742" s="12" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1743" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1743" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="C1743" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="D1743" s="12" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1744" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1744" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="C1744" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="D1744" s="12" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1745" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1745" s="12" t="s">
+        <v>2570</v>
+      </c>
+      <c r="C1745" s="12" t="s">
+        <v>2571</v>
+      </c>
+      <c r="D1745" s="12" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1746" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1746" s="12" t="s">
+        <v>3051</v>
+      </c>
+      <c r="C1746" s="12" t="s">
+        <v>3052</v>
+      </c>
+      <c r="D1746" s="12" t="s">
+        <v>3053</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1747" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1747" s="12" t="s">
+        <v>3054</v>
+      </c>
+      <c r="C1747" s="12" t="s">
+        <v>3055</v>
+      </c>
+      <c r="D1747" s="12" t="s">
+        <v>3056</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1748" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1748" s="12" t="s">
+        <v>945</v>
+      </c>
+      <c r="C1748" s="12" t="s">
+        <v>946</v>
+      </c>
+      <c r="D1748" s="12" t="s">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1749" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1749" s="12" t="s">
+        <v>3058</v>
+      </c>
+      <c r="C1749" s="12" t="s">
+        <v>3059</v>
+      </c>
+      <c r="D1749" s="12" t="s">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1750" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1750" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C1750" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1750" s="12" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1751" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1751" s="12" t="s">
+        <v>3062</v>
+      </c>
+      <c r="C1751" s="12" t="s">
+        <v>3063</v>
+      </c>
+      <c r="D1751" s="12" t="s">
+        <v>3064</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1752" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1752" s="12" t="s">
+        <v>2822</v>
+      </c>
+      <c r="C1752" s="12" t="s">
+        <v>2823</v>
+      </c>
+      <c r="D1752" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1753" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1753" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1753" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="D1753" s="12" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1754" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1754" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1754" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="D1754" s="12" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1755" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1755" s="12" t="s">
+        <v>2883</v>
+      </c>
+      <c r="C1755" s="12" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D1755" s="12" t="s">
+        <v>2885</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1756" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1756" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1756" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1756" s="12" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1757" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1757" s="12" t="s">
+        <v>3065</v>
+      </c>
+      <c r="C1757" s="12" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D1757" s="12" t="s">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1758" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1758" s="12" t="s">
+        <v>934</v>
+      </c>
+      <c r="C1758" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="D1758" s="12" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1759" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1759" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1759" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="D1759" s="12" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1760" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1760" s="12" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C1760" s="12" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D1760" s="12" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1761" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1761" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C1761" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="D1761" s="12" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1762" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1762" s="12" t="s">
+        <v>3068</v>
+      </c>
+      <c r="C1762" s="12" t="s">
+        <v>3069</v>
+      </c>
+      <c r="D1762" s="12" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1763" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1763" s="12" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C1763" s="12" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D1763" s="12" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1764" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1764" s="12" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C1764" s="12" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D1764" s="12" t="s">
+        <v>3071</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1765" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1765" s="12" t="s">
+        <v>3072</v>
+      </c>
+      <c r="C1765" s="12" t="s">
+        <v>3073</v>
+      </c>
+      <c r="D1765" s="12" t="s">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1766" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1766" s="12" t="s">
+        <v>3075</v>
+      </c>
+      <c r="C1766" s="12" t="s">
+        <v>3076</v>
+      </c>
+      <c r="D1766" s="12" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1767" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1767" s="12" t="s">
+        <v>3077</v>
+      </c>
+      <c r="C1767" s="12" t="s">
+        <v>3078</v>
+      </c>
+      <c r="D1767" s="12" t="s">
+        <v>3079</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1768" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1768" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1768" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1768" s="12" t="s">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1769" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1769" s="12" t="s">
+        <v>3081</v>
+      </c>
+      <c r="C1769" s="12" t="s">
+        <v>3082</v>
+      </c>
+      <c r="D1769" s="12" t="s">
+        <v>3083</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1770" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1770" s="12" t="s">
+        <v>3084</v>
+      </c>
+      <c r="C1770" s="12" t="s">
+        <v>2905</v>
+      </c>
+      <c r="D1770" s="12" t="s">
+        <v>3085</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1771" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1771" s="12" t="s">
+        <v>3086</v>
+      </c>
+      <c r="C1771" s="12" t="s">
+        <v>3087</v>
+      </c>
+      <c r="D1771" s="12" t="s">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1772" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1772" s="12" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C1772" s="12" t="s">
+        <v>3090</v>
+      </c>
+      <c r="D1772" s="12" t="s">
+        <v>3091</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1773" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1773" s="12" t="s">
+        <v>3092</v>
+      </c>
+      <c r="C1773" s="12" t="s">
+        <v>3092</v>
+      </c>
+      <c r="D1773" s="12" t="s">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1774" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1774" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="C1774" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="D1774" s="12" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1775" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1775" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="C1775" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="D1775" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1776" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1776" s="12" t="s">
+        <v>3094</v>
+      </c>
+      <c r="C1776" s="12" t="s">
+        <v>3095</v>
+      </c>
+      <c r="D1776" s="12" t="s">
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1777" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1777" s="12" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C1777" s="12" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D1777" s="12" t="s">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1778" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1778" s="12" t="s">
+        <v>3098</v>
+      </c>
+      <c r="C1778" s="12" t="s">
+        <v>3099</v>
+      </c>
+      <c r="D1778" s="12" t="s">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1779" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1779" s="12" t="s">
+        <v>3101</v>
+      </c>
+      <c r="C1779" s="12" t="s">
+        <v>3102</v>
+      </c>
+      <c r="D1779" s="12" t="s">
+        <v>3103</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1780" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1780" s="12" t="s">
+        <v>3104</v>
+      </c>
+      <c r="C1780" s="12" t="s">
+        <v>3105</v>
+      </c>
+      <c r="D1780" s="12" t="s">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1781" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1781" s="12" t="s">
+        <v>3107</v>
+      </c>
+      <c r="C1781" s="12" t="s">
+        <v>3108</v>
+      </c>
+      <c r="D1781" s="12" t="s">
+        <v>3109</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1782" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1782" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1782" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1782" s="12" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1783" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1783" s="12" t="s">
+        <v>978</v>
+      </c>
+      <c r="C1783" s="12" t="s">
+        <v>979</v>
+      </c>
+      <c r="D1783" s="12" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1784" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1784" s="12" t="s">
+        <v>733</v>
+      </c>
+      <c r="C1784" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="D1784" s="12" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1785" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1785" s="12" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C1785" s="12" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D1785" s="12" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1786" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1786" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C1786" s="12" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1786" s="12" t="s">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1787" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1787" s="12" t="s">
+        <v>3112</v>
+      </c>
+      <c r="C1787" s="12" t="s">
+        <v>3113</v>
+      </c>
+      <c r="D1787" s="12" t="s">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1788" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1788" s="12" t="s">
+        <v>3115</v>
+      </c>
+      <c r="C1788" s="12" t="s">
+        <v>3116</v>
+      </c>
+      <c r="D1788" s="12" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1789" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1789" s="12" t="s">
+        <v>3117</v>
+      </c>
+      <c r="C1789" s="12" t="s">
+        <v>3118</v>
+      </c>
+      <c r="D1789" s="12" t="s">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1790" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1790" s="12" t="s">
+        <v>3120</v>
+      </c>
+      <c r="C1790" s="12" t="s">
+        <v>3121</v>
+      </c>
+      <c r="D1790" s="12" t="s">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1791" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1791" s="12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C1791" s="12" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D1791" s="12" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1792" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1792" s="12" t="s">
+        <v>3123</v>
+      </c>
+      <c r="C1792" s="12" t="s">
+        <v>3124</v>
+      </c>
+      <c r="D1792" s="12" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1793" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1793" s="12" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C1793" s="12" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D1793" s="12" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1794" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1794" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="C1794" s="12" t="s">
+        <v>896</v>
+      </c>
+      <c r="D1794" s="12" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1795" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1795" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="C1795" s="12" t="s">
+        <v>820</v>
+      </c>
+      <c r="D1795" s="12" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1796" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1796" s="12" t="s">
+        <v>3127</v>
+      </c>
+      <c r="C1796" s="12" t="s">
+        <v>3128</v>
+      </c>
+      <c r="D1796" s="12" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1797" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1797" s="12" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1797" s="12" t="s">
+        <v>3130</v>
+      </c>
+      <c r="D1797" s="12" t="s">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1798" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1798" s="12" t="s">
+        <v>3132</v>
+      </c>
+      <c r="C1798" s="12" t="s">
+        <v>3133</v>
+      </c>
+      <c r="D1798" s="12" t="s">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1799" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1799" s="12" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C1799" s="12" t="s">
+        <v>3136</v>
+      </c>
+      <c r="D1799" s="12" t="s">
+        <v>3137</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1800" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1800" s="12" t="s">
+        <v>3138</v>
+      </c>
+      <c r="C1800" s="12" t="s">
+        <v>3139</v>
+      </c>
+      <c r="D1800" s="12" t="s">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1801" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1801" s="12" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1801" s="12" t="s">
+        <v>3142</v>
+      </c>
+      <c r="D1801" s="12" t="s">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1802" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1802" s="12" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C1802" s="12" t="s">
+        <v>3145</v>
+      </c>
+      <c r="D1802" s="12" t="s">
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1803" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1803" s="12" t="s">
+        <v>2439</v>
+      </c>
+      <c r="C1803" s="12" t="s">
+        <v>2440</v>
+      </c>
+      <c r="D1803" s="12" t="s">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1804" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1804" s="12" t="s">
+        <v>3148</v>
+      </c>
+      <c r="C1804" s="12" t="s">
+        <v>3149</v>
+      </c>
+      <c r="D1804" s="12" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1805" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1805" s="12" t="s">
+        <v>3150</v>
+      </c>
+      <c r="C1805" s="12" t="s">
+        <v>3151</v>
+      </c>
+      <c r="D1805" s="12" t="s">
+        <v>3152</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
